--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="82">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>sabrina</t>
+  </si>
+  <si>
+    <t>Fiorent</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -794,7 +797,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -822,7 +825,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -850,7 +853,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -878,7 +881,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -934,7 +937,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2874,16 +2877,22 @@
         <v>15</v>
       </c>
       <c r="F32" s="23"/>
-      <c r="G32" s="21">
+      <c r="G32" s="23">
         <v>21.0</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="24">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="I32" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="23"/>
       <c r="M32" s="53">
         <v>21.0</v>
       </c>
@@ -2967,7 +2976,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>sabrina</t>
-  </si>
-  <si>
-    <t>Fiorent</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -587,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -754,6 +751,9 @@
     </xf>
     <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,7 +797,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -825,7 +825,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -853,7 +853,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -881,7 +881,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -909,7 +909,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -937,7 +937,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2877,22 +2877,16 @@
         <v>15</v>
       </c>
       <c r="F32" s="23"/>
-      <c r="G32" s="23">
+      <c r="G32" s="21">
         <v>21.0</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="22">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" s="23"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="21"/>
       <c r="M32" s="53">
         <v>21.0</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
@@ -3304,7 +3298,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="58"/>
+      <c r="AD39" s="59"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3358,7 +3352,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="58"/>
+      <c r="AD40" s="59"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3412,7 +3406,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="58"/>
+      <c r="AD41" s="59"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3466,61 +3460,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="58"/>
+      <c r="AD42" s="59"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="59">
+      <c r="A43" s="60">
         <v>32.0</v>
       </c>
-      <c r="B43" s="60">
+      <c r="B43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59">
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60">
         <v>32.0</v>
       </c>
-      <c r="H43" s="60">
+      <c r="H43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="61">
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="62">
         <v>32.0</v>
       </c>
-      <c r="N43" s="62">
+      <c r="N43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="63" t="s">
+      <c r="O43" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="64"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="59">
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="60">
         <v>32.0</v>
       </c>
-      <c r="T43" s="60">
+      <c r="T43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="59"/>
-      <c r="X43" s="59"/>
-      <c r="Y43" s="59">
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="60"/>
+      <c r="Y43" s="60">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="60">
+      <c r="Z43" s="61">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="59"/>
-      <c r="AB43" s="59"/>
-      <c r="AC43" s="59"/>
-      <c r="AD43" s="66"/>
+      <c r="AA43" s="60"/>
+      <c r="AB43" s="60"/>
+      <c r="AC43" s="60"/>
+      <c r="AD43" s="67"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="82">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Akhmad binangun</t>
+  </si>
+  <si>
+    <t>- lala</t>
   </si>
   <si>
     <t>sabrina</t>
@@ -797,7 +800,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -825,7 +828,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -853,7 +856,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -881,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -909,7 +912,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -937,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2839,26 +2842,32 @@
       <c r="P31" s="56"/>
       <c r="Q31" s="56"/>
       <c r="R31" s="57"/>
-      <c r="S31" s="21">
+      <c r="S31" s="26">
         <v>20.0</v>
       </c>
-      <c r="T31" s="22">
+      <c r="T31" s="27">
         <v>0.6944444444444444</v>
       </c>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21">
+      <c r="U31" s="26"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="26"/>
+      <c r="Y31" s="23">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="22">
+      <c r="Z31" s="24">
         <v>0.6944444444444444</v>
       </c>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
+      <c r="AA31" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB31" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC31" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD31" s="23"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="23">
@@ -2868,7 +2877,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32" s="25" t="s">
         <v>14</v>
@@ -2970,7 +2979,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -800,7 +800,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -828,7 +828,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -856,7 +856,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -884,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3164,9 +3164,9 @@
       <c r="H37" s="22">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
       <c r="L37" s="21"/>
       <c r="M37" s="53">
         <v>26.0</v>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -800,7 +800,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -828,7 +828,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -856,7 +856,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -884,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3164,9 +3164,9 @@
       <c r="H37" s="22">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
       <c r="L37" s="21"/>
       <c r="M37" s="53">
         <v>26.0</v>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="83">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Uji</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -856,7 +859,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -884,7 +887,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -912,7 +915,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +943,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3158,16 +3161,24 @@
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="21">
+      <c r="G37" s="23">
         <v>26.0</v>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="24">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="I37" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="M37" s="53">
         <v>26.0</v>
       </c>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="84">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>sabrina</t>
+  </si>
+  <si>
+    <t>dinan</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -803,7 +806,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -831,7 +834,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -887,7 +890,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -915,7 +918,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -943,7 +946,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2933,16 +2936,22 @@
       <c r="AD32" s="21"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="21">
+      <c r="A33" s="23">
         <v>22.0</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="24">
         <v>0.7222222222222222</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="C33" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="23"/>
       <c r="G33" s="21">
         <v>22.0</v>
       </c>
@@ -2982,7 +2991,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
@@ -3168,7 +3177,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J37" s="25" t="s">
         <v>14</v>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="84">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -262,7 +262,7 @@
     <t>sabrina</t>
   </si>
   <si>
-    <t>dinan</t>
+    <t>Utia</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -834,7 +834,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -862,7 +862,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -890,7 +890,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -918,7 +918,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -946,7 +946,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2951,7 +2951,9 @@
       <c r="E33" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="23"/>
+      <c r="F33" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="G33" s="21">
         <v>22.0</v>
       </c>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="84">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -67,6 +67,9 @@
     <t>IN</t>
   </si>
   <si>
+    <t>dp 100</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Aninditya Mulia</t>
   </si>
   <si>
@@ -76,9 +79,6 @@
     <t>elni</t>
   </si>
   <si>
-    <t>dp 100</t>
-  </si>
-  <si>
     <t>Mufti</t>
   </si>
   <si>
@@ -109,79 +109,79 @@
     <t>Afrindanti</t>
   </si>
   <si>
+    <t>cantika</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tuti Priyani</t>
+  </si>
+  <si>
+    <t>Wisnu Pamungkas</t>
+  </si>
+  <si>
+    <t>Audi nisa</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Claresta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fadila</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Rahayu Purnama</t>
+  </si>
+  <si>
+    <t>Graduatiom</t>
+  </si>
+  <si>
+    <t>Qotrunnada Maulidia</t>
+  </si>
+  <si>
+    <t>Nasywaa</t>
+  </si>
+  <si>
+    <t>Dian</t>
+  </si>
+  <si>
+    <t>Ilut</t>
+  </si>
+  <si>
+    <t>By. IN</t>
+  </si>
+  <si>
+    <t>nabila hasna</t>
+  </si>
+  <si>
+    <t>Logi</t>
+  </si>
+  <si>
+    <t>Aulia Hani</t>
+  </si>
+  <si>
+    <t>Windi</t>
+  </si>
+  <si>
+    <t>Shabrina Amalia</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>Wafi Wafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tika Dwi</t>
+  </si>
+  <si>
+    <t>Devinta Khoerunnisa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> oktriana</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>cantika</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuti Priyani</t>
-  </si>
-  <si>
-    <t>Wisnu Pamungkas</t>
-  </si>
-  <si>
-    <t>Audi nisa</t>
-  </si>
-  <si>
-    <t>Claresta</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fadila</t>
-  </si>
-  <si>
-    <t>Rani</t>
-  </si>
-  <si>
-    <t>Rahayu Purnama</t>
-  </si>
-  <si>
-    <t>Graduatiom</t>
-  </si>
-  <si>
-    <t>Qotrunnada Maulidia</t>
-  </si>
-  <si>
-    <t>Nasywaa</t>
-  </si>
-  <si>
-    <t>Dian</t>
-  </si>
-  <si>
-    <t>Ilut</t>
-  </si>
-  <si>
-    <t>By. IN</t>
-  </si>
-  <si>
-    <t>nabila hasna</t>
-  </si>
-  <si>
-    <t>Logi</t>
-  </si>
-  <si>
-    <t>Aulia Hani</t>
-  </si>
-  <si>
-    <t>Windi</t>
-  </si>
-  <si>
-    <t>Shabrina Amalia</t>
-  </si>
-  <si>
-    <t>Nana</t>
-  </si>
-  <si>
-    <t>Wafi Wafa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tika Dwi</t>
-  </si>
-  <si>
-    <t>Devinta Khoerunnisa</t>
   </si>
   <si>
     <t>N. A. Salsabila</t>
@@ -723,7 +723,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -862,7 +862,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -890,7 +890,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -946,7 +946,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1735,7 +1735,9 @@
       <c r="E18" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="G18" s="23">
         <v>7.0</v>
       </c>
@@ -1743,13 +1745,13 @@
         <v>0.5</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="23"/>
       <c r="M18" s="23">
@@ -1759,7 +1761,7 @@
         <v>0.5</v>
       </c>
       <c r="O18" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P18" s="25" t="s">
         <v>14</v>
@@ -1768,7 +1770,7 @@
         <v>15</v>
       </c>
       <c r="R18" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S18" s="26">
         <v>7.0</v>
@@ -1793,10 +1795,10 @@
         <v>21</v>
       </c>
       <c r="AC18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD18" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -1816,7 +1818,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G19" s="28">
         <v>8.0</v>
@@ -1834,7 +1836,7 @@
         <v>15</v>
       </c>
       <c r="L19" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M19" s="23">
         <v>8.0</v>
@@ -1849,10 +1851,10 @@
         <v>26</v>
       </c>
       <c r="Q19" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R19" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S19" s="23">
         <v>8.0</v>
@@ -1870,7 +1872,7 @@
         <v>15</v>
       </c>
       <c r="X19" s="32" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y19" s="33">
         <v>8.0</v>
@@ -1900,24 +1902,18 @@
         <v>15</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="23">
+        <v>16</v>
+      </c>
+      <c r="G20" s="26">
         <v>9.0</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="27">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L20" s="23"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="26"/>
       <c r="M20" s="23">
         <v>9.0</v>
       </c>
@@ -1925,7 +1921,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="O20" s="36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P20" s="37" t="s">
         <v>14</v>
@@ -1934,7 +1930,7 @@
         <v>15</v>
       </c>
       <c r="R20" s="37" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S20" s="23">
         <v>9.0</v>
@@ -1943,16 +1939,16 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="U20" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="V20" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W20" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X20" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y20" s="23">
         <v>9.0</v>
@@ -1961,7 +1957,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="AA20" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB20" s="25" t="s">
         <v>28</v>
@@ -1970,7 +1966,7 @@
         <v>15</v>
       </c>
       <c r="AD20" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1981,16 +1977,16 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G21" s="23">
         <v>10.0</v>
@@ -1999,7 +1995,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="I21" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J21" s="38" t="s">
         <v>21</v>
@@ -2008,7 +2004,7 @@
         <v>15</v>
       </c>
       <c r="L21" s="38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M21" s="23">
         <v>10.0</v>
@@ -2017,16 +2013,16 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="O21" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P21" s="42" t="s">
         <v>14</v>
       </c>
       <c r="Q21" s="25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R21" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S21" s="23">
         <v>10.0</v>
@@ -2035,7 +2031,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="U21" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V21" s="43" t="s">
         <v>14</v>
@@ -2043,7 +2039,9 @@
       <c r="W21" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="44"/>
+      <c r="X21" s="44" t="s">
+        <v>16</v>
+      </c>
       <c r="Y21" s="26">
         <v>10.0</v>
       </c>
@@ -2063,15 +2061,17 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="C22" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="25" t="s">
-        <v>40</v>
-      </c>
       <c r="E22" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="G22" s="23">
         <v>11.0</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J22" s="25" t="s">
         <v>14</v>
@@ -2088,7 +2088,7 @@
         <v>15</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M22" s="23">
         <v>11.0</v>
@@ -2097,7 +2097,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="O22" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P22" s="42" t="s">
         <v>14</v>
@@ -2106,7 +2106,7 @@
         <v>15</v>
       </c>
       <c r="R22" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S22" s="23">
         <v>11.0</v>
@@ -2115,7 +2115,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="U22" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V22" s="25" t="s">
         <v>14</v>
@@ -2124,7 +2124,7 @@
         <v>15</v>
       </c>
       <c r="X22" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y22" s="26">
         <v>11.0</v>
@@ -2145,13 +2145,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="23">
@@ -2161,16 +2161,16 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J23" s="45" t="s">
         <v>14</v>
       </c>
       <c r="K23" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M23" s="23">
         <v>12.0</v>
@@ -2179,16 +2179,16 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="O23" s="46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P23" s="42" t="s">
         <v>14</v>
       </c>
       <c r="Q23" s="25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R23" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S23" s="23">
         <v>12.0</v>
@@ -2197,16 +2197,16 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="U23" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V23" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W23" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X23" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y23" s="26">
         <v>12.0</v>
@@ -2227,13 +2227,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" s="25"/>
       <c r="G24" s="23">
@@ -2243,16 +2243,16 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M24" s="23">
         <v>13.0</v>
@@ -2261,7 +2261,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="O24" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P24" s="25" t="s">
         <v>28</v>
@@ -2270,7 +2270,7 @@
         <v>15</v>
       </c>
       <c r="R24" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S24" s="23">
         <v>13.0</v>
@@ -2279,16 +2279,16 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W24" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X24" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y24" s="26">
         <v>13.0</v>
@@ -2309,7 +2309,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>28</v>
@@ -2317,7 +2317,9 @@
       <c r="E25" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="23"/>
+      <c r="F25" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="G25" s="23">
         <v>14.0</v>
       </c>
@@ -2325,16 +2327,16 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M25" s="23">
         <v>14.0</v>
@@ -2343,15 +2345,17 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="P25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="Q25" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="R25" s="23"/>
+        <v>34</v>
+      </c>
+      <c r="R25" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="S25" s="26">
         <v>14.0</v>
       </c>
@@ -2375,10 +2379,10 @@
         <v>14</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD25" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2389,7 +2393,7 @@
         <v>0.625</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" s="25" t="s">
         <v>14</v>
@@ -2398,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G26" s="23">
         <v>15.0</v>
@@ -2413,10 +2417,10 @@
         <v>57</v>
       </c>
       <c r="K26" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M26" s="23">
         <v>15.0</v>
@@ -2431,10 +2435,10 @@
         <v>14</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R26" s="41" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S26" s="26">
         <v>15.0</v>
@@ -2459,10 +2463,10 @@
         <v>14</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD26" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -2479,9 +2483,11 @@
         <v>14</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="G27" s="23">
         <v>16.0</v>
       </c>
@@ -2495,10 +2501,10 @@
         <v>14</v>
       </c>
       <c r="K27" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M27" s="23">
         <v>16.0</v>
@@ -2513,10 +2519,10 @@
         <v>14</v>
       </c>
       <c r="Q27" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R27" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S27" s="48">
         <v>16.0</v>
@@ -2541,10 +2547,10 @@
         <v>14</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD27" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2564,7 +2570,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G28" s="23">
         <v>17.0</v>
@@ -2582,7 +2588,7 @@
         <v>15</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M28" s="23">
         <v>17.0</v>
@@ -2600,7 +2606,7 @@
         <v>15</v>
       </c>
       <c r="R28" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S28" s="26">
         <v>17.0</v>
@@ -2628,7 +2634,7 @@
         <v>15</v>
       </c>
       <c r="AD28" s="52" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2648,7 +2654,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G29" s="23">
         <v>18.0</v>
@@ -2666,7 +2672,7 @@
         <v>15</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M29" s="23">
         <v>18.0</v>
@@ -2681,10 +2687,10 @@
         <v>14</v>
       </c>
       <c r="Q29" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R29" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S29" s="26">
         <v>18.0</v>
@@ -2712,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="AD29" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -2732,7 +2738,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G30" s="23">
         <v>19.0</v>
@@ -2747,10 +2753,10 @@
         <v>14</v>
       </c>
       <c r="K30" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M30" s="53">
         <v>19.0</v>
@@ -2780,7 +2786,7 @@
         <v>15</v>
       </c>
       <c r="X30" s="38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y30" s="23">
         <v>19.0</v>
@@ -2798,7 +2804,7 @@
         <v>15</v>
       </c>
       <c r="AD30" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -2818,7 +2824,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G31" s="23">
         <v>20.0</v>
@@ -2833,9 +2839,11 @@
         <v>14</v>
       </c>
       <c r="K31" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="L31" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="L31" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="M31" s="53">
         <v>20.0</v>
       </c>
@@ -2871,9 +2879,11 @@
         <v>14</v>
       </c>
       <c r="AC31" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD31" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="AD31" s="25" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="23">
@@ -2891,7 +2901,9 @@
       <c r="E32" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="25" t="s">
+        <v>16</v>
+      </c>
       <c r="G32" s="21">
         <v>21.0</v>
       </c>
@@ -2949,10 +2961,10 @@
         <v>14</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G33" s="21">
         <v>22.0</v>
@@ -3185,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="K37" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L37" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M37" s="53">
         <v>26.0</v>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="83">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -70,82 +70,79 @@
     <t>dp 100</t>
   </si>
   <si>
-    <t xml:space="preserve"> Aninditya Mulia</t>
+    <t>elni</t>
+  </si>
+  <si>
+    <t>Ade Evan</t>
+  </si>
+  <si>
+    <t>Graaduation</t>
+  </si>
+  <si>
+    <t>Cahya Juwita</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sabrina</t>
+  </si>
+  <si>
+    <t>Graduation premium</t>
   </si>
   <si>
     <t>AL</t>
   </si>
   <si>
-    <t>elni</t>
+    <t>Desti Ika c</t>
+  </si>
+  <si>
+    <t>Graduation Premium</t>
+  </si>
+  <si>
+    <t>Afrindanti</t>
+  </si>
+  <si>
+    <t>cantika</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tuti Priyani</t>
+  </si>
+  <si>
+    <t>Wisnu Pamungkas</t>
+  </si>
+  <si>
+    <t>Audi nisa</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Claresta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fadila</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Rahayu Purnama</t>
+  </si>
+  <si>
+    <t>Graduatiom</t>
+  </si>
+  <si>
+    <t>Qotrunnada Maulidia</t>
+  </si>
+  <si>
+    <t>Nasywaa</t>
+  </si>
+  <si>
+    <t>Dian</t>
   </si>
   <si>
     <t>Mufti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduation </t>
-  </si>
-  <si>
-    <t>Ade Evan</t>
-  </si>
-  <si>
-    <t>Graaduation</t>
-  </si>
-  <si>
-    <t>Cahya Juwita</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sabrina</t>
-  </si>
-  <si>
-    <t>Graduation premium</t>
-  </si>
-  <si>
-    <t>Desti Ika c</t>
-  </si>
-  <si>
-    <t>Graduation Premium</t>
-  </si>
-  <si>
-    <t>Afrindanti</t>
-  </si>
-  <si>
-    <t>cantika</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuti Priyani</t>
-  </si>
-  <si>
-    <t>Wisnu Pamungkas</t>
-  </si>
-  <si>
-    <t>Audi nisa</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Claresta</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fadila</t>
-  </si>
-  <si>
-    <t>Rani</t>
-  </si>
-  <si>
-    <t>Rahayu Purnama</t>
-  </si>
-  <si>
-    <t>Graduatiom</t>
-  </si>
-  <si>
-    <t>Qotrunnada Maulidia</t>
-  </si>
-  <si>
-    <t>Nasywaa</t>
-  </si>
-  <si>
-    <t>Dian</t>
   </si>
   <si>
     <t>Ilut</t>
@@ -363,7 +360,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +413,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
         <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -593,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,12 +671,15 @@
     <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -689,14 +695,20 @@
     <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -734,13 +746,13 @@
     <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -749,20 +761,17 @@
     <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -772,13 +781,13 @@
     <xf borderId="12" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="12" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -806,7 +815,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -834,7 +843,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -862,7 +871,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -890,7 +899,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -918,7 +927,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -946,7 +955,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1738,30 +1747,22 @@
       <c r="F18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="21">
         <v>7.0</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="22">
         <v>0.5</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="28" t="s">
         <v>17</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23">
-        <v>7.0</v>
-      </c>
-      <c r="N18" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>19</v>
       </c>
       <c r="P18" s="25" t="s">
         <v>14</v>
@@ -1772,34 +1773,26 @@
       <c r="R18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S18" s="26">
+      <c r="S18" s="21">
         <v>7.0</v>
       </c>
-      <c r="T18" s="27">
+      <c r="T18" s="22">
         <v>0.5</v>
       </c>
-      <c r="U18" s="26"/>
-      <c r="V18" s="26"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="23">
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21">
         <v>7.0</v>
       </c>
-      <c r="Z18" s="24">
+      <c r="Z18" s="22">
         <v>0.5</v>
       </c>
-      <c r="AA18" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB18" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC18" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD18" s="25" t="s">
-        <v>16</v>
-      </c>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
+      <c r="AC18" s="26"/>
+      <c r="AD18" s="26"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="23">
@@ -1809,10 +1802,10 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>15</v>
@@ -1820,14 +1813,14 @@
       <c r="F19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <v>8.0</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="30">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="30" t="s">
-        <v>24</v>
+      <c r="I19" s="31" t="s">
+        <v>20</v>
       </c>
       <c r="J19" s="25" t="s">
         <v>14</v>
@@ -1844,14 +1837,14 @@
       <c r="N19" s="24">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="31" t="s">
-        <v>25</v>
+      <c r="O19" s="32" t="s">
+        <v>21</v>
       </c>
       <c r="P19" s="25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R19" s="25" t="s">
         <v>16</v>
@@ -1862,28 +1855,28 @@
       <c r="T19" s="24">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="V19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="W19" s="32" t="s">
+      <c r="U19" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="V19" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="W19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="X19" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y19" s="33">
+      <c r="X19" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y19" s="34">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="34">
+      <c r="Z19" s="35">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="35"/>
+      <c r="AA19" s="36"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="36"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="23">
@@ -1893,7 +1886,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D20" s="25" t="s">
         <v>14</v>
@@ -1904,32 +1897,32 @@
       <c r="F20" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="37">
         <v>9.0</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="38">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="26"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="37"/>
       <c r="M20" s="23">
         <v>9.0</v>
       </c>
       <c r="N20" s="24">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="P20" s="37" t="s">
+      <c r="O20" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="Q20" s="37" t="s">
+      <c r="Q20" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="37" t="s">
+      <c r="R20" s="40" t="s">
         <v>16</v>
       </c>
       <c r="S20" s="23">
@@ -1939,13 +1932,13 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="U20" s="25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V20" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W20" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X20" s="25" t="s">
         <v>16</v>
@@ -1957,10 +1950,10 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="AA20" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB20" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC20" s="25" t="s">
         <v>15</v>
@@ -1970,22 +1963,22 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="38">
+      <c r="A21" s="41">
         <v>10.0</v>
       </c>
-      <c r="B21" s="39">
+      <c r="B21" s="42">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="38" t="s">
+      <c r="C21" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="38" t="s">
+      <c r="E21" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="23">
@@ -1994,32 +1987,32 @@
       <c r="H21" s="24">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="38" t="s">
+      <c r="I21" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="38" t="s">
+      <c r="L21" s="41" t="s">
         <v>16</v>
       </c>
       <c r="M21" s="23">
         <v>10.0</v>
       </c>
-      <c r="N21" s="40">
+      <c r="N21" s="43">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="42" t="s">
+      <c r="O21" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" s="45" t="s">
         <v>14</v>
       </c>
       <c r="Q21" s="25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R21" s="25" t="s">
         <v>16</v>
@@ -2030,28 +2023,28 @@
       <c r="T21" s="24">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="V21" s="43" t="s">
+      <c r="U21" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="V21" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="W21" s="43" t="s">
+      <c r="W21" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="26">
+      <c r="X21" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="37">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="27">
+      <c r="Z21" s="38">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
+      <c r="AA21" s="37"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="37"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="23">
@@ -2061,13 +2054,13 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F22" s="25" t="s">
         <v>16</v>
@@ -2079,7 +2072,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J22" s="25" t="s">
         <v>14</v>
@@ -2093,13 +2086,13 @@
       <c r="M22" s="23">
         <v>11.0</v>
       </c>
-      <c r="N22" s="40">
+      <c r="N22" s="43">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="P22" s="42" t="s">
+      <c r="O22" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="P22" s="45" t="s">
         <v>14</v>
       </c>
       <c r="Q22" s="25" t="s">
@@ -2114,28 +2107,36 @@
       <c r="T22" s="24">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="V22" s="25" t="s">
+      <c r="U22" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="V22" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="W22" s="25" t="s">
+      <c r="W22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="X22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y22" s="26">
+      <c r="X22" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y22" s="23">
         <v>11.0</v>
       </c>
-      <c r="Z22" s="27">
+      <c r="Z22" s="24">
         <v>0.5694444444444444</v>
       </c>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="26"/>
-      <c r="AC22" s="26"/>
-      <c r="AD22" s="26"/>
+      <c r="AA22" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC22" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD22" s="25" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="23">
@@ -2145,13 +2146,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C23" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>44</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="23">
@@ -2161,13 +2162,13 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="48" t="s">
         <v>14</v>
       </c>
       <c r="K23" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L23" s="25" t="s">
         <v>16</v>
@@ -2175,17 +2176,17 @@
       <c r="M23" s="23">
         <v>12.0</v>
       </c>
-      <c r="N23" s="40">
+      <c r="N23" s="43">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="42" t="s">
+      <c r="O23" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="45" t="s">
         <v>14</v>
       </c>
       <c r="Q23" s="25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R23" s="25" t="s">
         <v>16</v>
@@ -2197,27 +2198,27 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="U23" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V23" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W23" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X23" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="Y23" s="26">
+      <c r="Y23" s="37">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="27">
+      <c r="Z23" s="38">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-      <c r="AC23" s="26"/>
-      <c r="AD23" s="26"/>
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="37"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="23">
@@ -2227,13 +2228,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" s="25"/>
       <c r="G24" s="23">
@@ -2243,13 +2244,13 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L24" s="25" t="s">
         <v>16</v>
@@ -2260,11 +2261,11 @@
       <c r="N24" s="24">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="47" t="s">
-        <v>50</v>
+      <c r="O24" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="P24" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q24" s="25" t="s">
         <v>15</v>
@@ -2279,27 +2280,27 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>14</v>
       </c>
       <c r="W24" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X24" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="37">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="27">
+      <c r="Z24" s="38">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="26"/>
-      <c r="AD24" s="26"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="23">
@@ -2309,10 +2310,10 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>15</v>
@@ -2327,13 +2328,13 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L25" s="25" t="s">
         <v>16</v>
@@ -2345,27 +2346,27 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="Q25" s="25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R25" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S25" s="26">
+      <c r="S25" s="37">
         <v>14.0</v>
       </c>
-      <c r="T25" s="27">
+      <c r="T25" s="38">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="26"/>
-      <c r="V25" s="26"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="26"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
       <c r="Y25" s="23">
         <v>14.0</v>
       </c>
@@ -2373,13 +2374,13 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="AA25" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD25" s="25" t="s">
         <v>16</v>
@@ -2393,7 +2394,7 @@
         <v>0.625</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D26" s="25" t="s">
         <v>14</v>
@@ -2411,13 +2412,13 @@
         <v>0.625</v>
       </c>
       <c r="I26" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="J26" s="25" t="s">
-        <v>57</v>
-      </c>
       <c r="K26" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L26" s="25" t="s">
         <v>16</v>
@@ -2429,27 +2430,27 @@
         <v>0.625</v>
       </c>
       <c r="O26" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P26" s="23" t="s">
         <v>14</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="26">
+        <v>31</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="37">
         <v>15.0</v>
       </c>
-      <c r="T26" s="27">
+      <c r="T26" s="38">
         <v>0.625</v>
       </c>
-      <c r="U26" s="26"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="26"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="37"/>
       <c r="Y26" s="23">
         <v>15.0</v>
       </c>
@@ -2457,13 +2458,13 @@
         <v>0.625</v>
       </c>
       <c r="AA26" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AB26" s="25" t="s">
         <v>14</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD26" s="25" t="s">
         <v>16</v>
@@ -2477,13 +2478,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>16</v>
@@ -2495,13 +2496,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J27" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K27" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L27" s="25" t="s">
         <v>16</v>
@@ -2513,27 +2514,27 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P27" s="25" t="s">
         <v>14</v>
       </c>
       <c r="Q27" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R27" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S27" s="48">
+      <c r="S27" s="51">
         <v>16.0</v>
       </c>
-      <c r="T27" s="49">
+      <c r="T27" s="52">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="50"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="51"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="53"/>
       <c r="Y27" s="23">
         <v>16.0</v>
       </c>
@@ -2541,13 +2542,13 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="AA27" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB27" s="25" t="s">
         <v>14</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD27" s="25" t="s">
         <v>16</v>
@@ -2560,8 +2561,8 @@
       <c r="B28" s="24">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="51" t="s">
-        <v>64</v>
+      <c r="C28" s="54" t="s">
+        <v>63</v>
       </c>
       <c r="D28" s="25" t="s">
         <v>14</v>
@@ -2579,10 +2580,10 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K28" s="25" t="s">
         <v>15</v>
@@ -2597,7 +2598,7 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="O28" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P28" s="25" t="s">
         <v>14</v>
@@ -2608,32 +2609,32 @@
       <c r="R28" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S28" s="26">
+      <c r="S28" s="37">
         <v>17.0</v>
       </c>
-      <c r="T28" s="27">
+      <c r="T28" s="38">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="26"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="26"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
       <c r="Y28" s="23">
         <v>17.0</v>
       </c>
       <c r="Z28" s="24">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB28" s="38" t="s">
+      <c r="AA28" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB28" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="AC28" s="38" t="s">
+      <c r="AC28" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="52" t="s">
+      <c r="AD28" s="55" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2645,7 +2646,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D29" s="25" t="s">
         <v>14</v>
@@ -2663,7 +2664,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J29" s="25" t="s">
         <v>14</v>
@@ -2681,27 +2682,27 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P29" s="25" t="s">
         <v>14</v>
       </c>
       <c r="Q29" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R29" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S29" s="26">
+      <c r="S29" s="37">
         <v>18.0</v>
       </c>
-      <c r="T29" s="27">
+      <c r="T29" s="38">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
       <c r="Y29" s="23">
         <v>18.0</v>
       </c>
@@ -2709,7 +2710,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AA29" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB29" s="25" t="s">
         <v>14</v>
@@ -2729,7 +2730,7 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="25" t="s">
         <v>14</v>
@@ -2747,45 +2748,45 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J30" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K30" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L30" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="53">
+      <c r="M30" s="56">
         <v>19.0</v>
       </c>
-      <c r="N30" s="54">
+      <c r="N30" s="57">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="55" t="s">
+      <c r="O30" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="59"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="41">
+        <v>19.0</v>
+      </c>
+      <c r="T30" s="42">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="U30" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="57"/>
-      <c r="S30" s="38">
-        <v>19.0</v>
-      </c>
-      <c r="T30" s="39">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="U30" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="V30" s="38" t="s">
+      <c r="V30" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="W30" s="38" t="s">
+      <c r="W30" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="X30" s="38" t="s">
+      <c r="X30" s="41" t="s">
         <v>16</v>
       </c>
       <c r="Y30" s="23">
@@ -2795,7 +2796,7 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="AA30" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AB30" s="25" t="s">
         <v>14</v>
@@ -2815,7 +2816,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="25" t="s">
         <v>14</v>
@@ -2833,39 +2834,39 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J31" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K31" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L31" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M31" s="53">
+      <c r="M31" s="56">
         <v>20.0</v>
       </c>
-      <c r="N31" s="54">
+      <c r="N31" s="57">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="56"/>
-      <c r="R31" s="57"/>
-      <c r="S31" s="26">
+      <c r="O31" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P31" s="59"/>
+      <c r="Q31" s="59"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="37">
         <v>20.0</v>
       </c>
-      <c r="T31" s="27">
+      <c r="T31" s="38">
         <v>0.6944444444444444</v>
       </c>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="37"/>
       <c r="Y31" s="23">
         <v>20.0</v>
       </c>
@@ -2873,13 +2874,13 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="AA31" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB31" s="25" t="s">
         <v>14</v>
       </c>
       <c r="AC31" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD31" s="25" t="s">
         <v>16</v>
@@ -2893,7 +2894,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" s="25" t="s">
         <v>14</v>
@@ -2910,22 +2911,22 @@
       <c r="H32" s="22">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="58"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
       <c r="L32" s="21"/>
-      <c r="M32" s="53">
+      <c r="M32" s="56">
         <v>21.0</v>
       </c>
-      <c r="N32" s="54">
+      <c r="N32" s="57">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="56"/>
-      <c r="R32" s="57"/>
+      <c r="O32" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P32" s="59"/>
+      <c r="Q32" s="59"/>
+      <c r="R32" s="60"/>
       <c r="S32" s="21">
         <v>21.0</v>
       </c>
@@ -2955,13 +2956,13 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="25" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F33" s="25" t="s">
         <v>16</v>
@@ -2976,18 +2977,18 @@
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
-      <c r="M33" s="53">
+      <c r="M33" s="56">
         <v>22.0</v>
       </c>
-      <c r="N33" s="54">
+      <c r="N33" s="57">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="56"/>
-      <c r="R33" s="57"/>
+      <c r="O33" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P33" s="59"/>
+      <c r="Q33" s="59"/>
+      <c r="R33" s="60"/>
       <c r="S33" s="21">
         <v>22.0</v>
       </c>
@@ -3005,7 +3006,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
@@ -3032,18 +3033,18 @@
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
-      <c r="M34" s="53">
+      <c r="M34" s="56">
         <v>23.0</v>
       </c>
-      <c r="N34" s="54">
+      <c r="N34" s="57">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="57"/>
+      <c r="O34" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="60"/>
       <c r="S34" s="21">
         <v>23.0</v>
       </c>
@@ -3086,18 +3087,18 @@
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="53">
+      <c r="M35" s="56">
         <v>24.0</v>
       </c>
-      <c r="N35" s="54">
+      <c r="N35" s="57">
         <v>0.75</v>
       </c>
-      <c r="O35" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="56"/>
-      <c r="R35" s="57"/>
+      <c r="O35" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="59"/>
+      <c r="R35" s="60"/>
       <c r="S35" s="21">
         <v>24.0</v>
       </c>
@@ -3140,18 +3141,18 @@
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
-      <c r="M36" s="53">
+      <c r="M36" s="56">
         <v>25.0</v>
       </c>
-      <c r="N36" s="54">
+      <c r="N36" s="57">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="56"/>
-      <c r="R36" s="57"/>
+      <c r="O36" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="59"/>
+      <c r="R36" s="60"/>
       <c r="S36" s="21">
         <v>25.0</v>
       </c>
@@ -3191,29 +3192,29 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J37" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K37" s="25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L37" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M37" s="53">
+      <c r="M37" s="56">
         <v>26.0</v>
       </c>
-      <c r="N37" s="54">
+      <c r="N37" s="57">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="57"/>
+      <c r="O37" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
+      <c r="R37" s="60"/>
       <c r="S37" s="21">
         <v>26.0</v>
       </c>
@@ -3256,18 +3257,18 @@
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
-      <c r="M38" s="53">
+      <c r="M38" s="56">
         <v>27.0</v>
       </c>
-      <c r="N38" s="54">
+      <c r="N38" s="57">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="57"/>
+      <c r="O38" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="59"/>
+      <c r="R38" s="60"/>
       <c r="S38" s="21">
         <v>27.0</v>
       </c>
@@ -3310,18 +3311,18 @@
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
-      <c r="M39" s="53">
+      <c r="M39" s="56">
         <v>28.0</v>
       </c>
-      <c r="N39" s="54">
+      <c r="N39" s="57">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="57"/>
+      <c r="O39" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P39" s="59"/>
+      <c r="Q39" s="59"/>
+      <c r="R39" s="60"/>
       <c r="S39" s="21">
         <v>28.0</v>
       </c>
@@ -3341,7 +3342,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="59"/>
+      <c r="AD39" s="61"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3364,18 +3365,18 @@
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
-      <c r="M40" s="53">
+      <c r="M40" s="56">
         <v>29.0</v>
       </c>
-      <c r="N40" s="54">
+      <c r="N40" s="57">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="56"/>
-      <c r="R40" s="57"/>
+      <c r="O40" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P40" s="59"/>
+      <c r="Q40" s="59"/>
+      <c r="R40" s="60"/>
       <c r="S40" s="21">
         <v>29.0</v>
       </c>
@@ -3395,7 +3396,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="59"/>
+      <c r="AD40" s="61"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3418,18 +3419,18 @@
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
-      <c r="M41" s="53">
+      <c r="M41" s="56">
         <v>30.0</v>
       </c>
-      <c r="N41" s="54">
+      <c r="N41" s="57">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P41" s="56"/>
-      <c r="Q41" s="56"/>
-      <c r="R41" s="57"/>
+      <c r="O41" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
+      <c r="R41" s="60"/>
       <c r="S41" s="21">
         <v>30.0</v>
       </c>
@@ -3449,7 +3450,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="59"/>
+      <c r="AD41" s="61"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3472,18 +3473,18 @@
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
-      <c r="M42" s="53">
+      <c r="M42" s="56">
         <v>31.0</v>
       </c>
-      <c r="N42" s="54">
+      <c r="N42" s="57">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="56"/>
-      <c r="R42" s="57"/>
+      <c r="O42" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="P42" s="59"/>
+      <c r="Q42" s="59"/>
+      <c r="R42" s="60"/>
       <c r="S42" s="21">
         <v>31.0</v>
       </c>
@@ -3503,61 +3504,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="59"/>
+      <c r="AD42" s="61"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="60">
+      <c r="A43" s="62">
         <v>32.0</v>
       </c>
-      <c r="B43" s="61">
+      <c r="B43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60">
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="62">
         <v>32.0</v>
       </c>
-      <c r="H43" s="61">
+      <c r="H43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="62">
+      <c r="I43" s="62"/>
+      <c r="J43" s="62"/>
+      <c r="K43" s="62"/>
+      <c r="L43" s="62"/>
+      <c r="M43" s="64">
         <v>32.0</v>
       </c>
-      <c r="N43" s="63">
+      <c r="N43" s="65">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="66"/>
-      <c r="S43" s="60">
+      <c r="O43" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="62">
         <v>32.0</v>
       </c>
-      <c r="T43" s="61">
+      <c r="T43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="60"/>
-      <c r="V43" s="60"/>
-      <c r="W43" s="60"/>
-      <c r="X43" s="60"/>
-      <c r="Y43" s="60">
+      <c r="U43" s="62"/>
+      <c r="V43" s="62"/>
+      <c r="W43" s="62"/>
+      <c r="X43" s="62"/>
+      <c r="Y43" s="62">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="61">
+      <c r="Z43" s="63">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="60"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="67"/>
+      <c r="AA43" s="62"/>
+      <c r="AB43" s="62"/>
+      <c r="AC43" s="62"/>
+      <c r="AD43" s="69"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -73,196 +73,190 @@
     <t>elni</t>
   </si>
   <si>
+    <t xml:space="preserve"> Sabrina</t>
+  </si>
+  <si>
+    <t>Graduation premium</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Afrindanti</t>
+  </si>
+  <si>
+    <t>cantika</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tuti Priyani</t>
+  </si>
+  <si>
+    <t>Wisnu Pamungkas</t>
+  </si>
+  <si>
+    <t>Graduation Premium</t>
+  </si>
+  <si>
+    <t>Audi nisa</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Claresta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fadila</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Rahayu Purnama</t>
+  </si>
+  <si>
+    <t>Graduatiom</t>
+  </si>
+  <si>
+    <t>Qotrunnada Maulidia</t>
+  </si>
+  <si>
+    <t>Nasywaa</t>
+  </si>
+  <si>
+    <t>Mufti</t>
+  </si>
+  <si>
+    <t>Ilut</t>
+  </si>
+  <si>
+    <t>nabila hasna</t>
+  </si>
+  <si>
+    <t>Logi</t>
+  </si>
+  <si>
+    <t>Aulia Hani</t>
+  </si>
+  <si>
+    <t>Windi</t>
+  </si>
+  <si>
+    <t>Shabrina Amalia</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>Wafi Wafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tika Dwi</t>
+  </si>
+  <si>
+    <t>Devinta Khoerunnisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> oktriana</t>
+  </si>
+  <si>
+    <t>N. A. Salsabila</t>
+  </si>
+  <si>
+    <t>Gandring Guste Puand</t>
+  </si>
+  <si>
+    <t>Graduatio prem</t>
+  </si>
+  <si>
+    <t>Afifah</t>
+  </si>
+  <si>
+    <t>Zaidan Ariefyandi</t>
+  </si>
+  <si>
+    <t>Sandlyra Anastasya</t>
+  </si>
+  <si>
+    <t>helmi</t>
+  </si>
+  <si>
+    <t>Reynaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> widyaloka</t>
+  </si>
+  <si>
+    <t>Amelia Nur</t>
+  </si>
+  <si>
+    <t>Syifa Zulfa</t>
+  </si>
+  <si>
+    <t>Niko</t>
+  </si>
+  <si>
+    <t>Wahyu Setianingsih</t>
+  </si>
+  <si>
+    <t>Karlina</t>
+  </si>
+  <si>
+    <t>Nabilla</t>
+  </si>
+  <si>
+    <t>Tiffani Agil</t>
+  </si>
+  <si>
+    <t>Nina Dwi Suryani</t>
+  </si>
+  <si>
+    <t>Mahendra Putra Wardhana</t>
+  </si>
+  <si>
+    <t>Afita Khoerunnisa</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>Dita</t>
+  </si>
+  <si>
+    <t>Sifa</t>
+  </si>
+  <si>
+    <t>Hanifa</t>
+  </si>
+  <si>
+    <t>Akhmad binangun</t>
+  </si>
+  <si>
+    <t>lala</t>
+  </si>
+  <si>
+    <t>sabrina</t>
+  </si>
+  <si>
+    <t>Cahya Juwita</t>
+  </si>
+  <si>
+    <t>Desti Ika c</t>
+  </si>
+  <si>
+    <t>Utia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Ade Evan</t>
   </si>
   <si>
     <t>Graaduation</t>
-  </si>
-  <si>
-    <t>Cahya Juwita</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sabrina</t>
-  </si>
-  <si>
-    <t>Graduation premium</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>Desti Ika c</t>
-  </si>
-  <si>
-    <t>Graduation Premium</t>
-  </si>
-  <si>
-    <t>Afrindanti</t>
-  </si>
-  <si>
-    <t>cantika</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuti Priyani</t>
-  </si>
-  <si>
-    <t>Wisnu Pamungkas</t>
-  </si>
-  <si>
-    <t>Audi nisa</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Claresta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduation </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fadila</t>
-  </si>
-  <si>
-    <t>Rani</t>
-  </si>
-  <si>
-    <t>Rahayu Purnama</t>
-  </si>
-  <si>
-    <t>Graduatiom</t>
-  </si>
-  <si>
-    <t>Qotrunnada Maulidia</t>
-  </si>
-  <si>
-    <t>Nasywaa</t>
-  </si>
-  <si>
-    <t>Dian</t>
-  </si>
-  <si>
-    <t>Mufti</t>
-  </si>
-  <si>
-    <t>Ilut</t>
-  </si>
-  <si>
-    <t>By. IN</t>
-  </si>
-  <si>
-    <t>nabila hasna</t>
-  </si>
-  <si>
-    <t>Logi</t>
-  </si>
-  <si>
-    <t>Aulia Hani</t>
-  </si>
-  <si>
-    <t>Windi</t>
-  </si>
-  <si>
-    <t>Shabrina Amalia</t>
-  </si>
-  <si>
-    <t>Nana</t>
-  </si>
-  <si>
-    <t>Wafi Wafa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tika Dwi</t>
-  </si>
-  <si>
-    <t>Devinta Khoerunnisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> oktriana</t>
-  </si>
-  <si>
-    <t>N. A. Salsabila</t>
-  </si>
-  <si>
-    <t>Gandring Guste Puand</t>
-  </si>
-  <si>
-    <t>Graduatio prem</t>
-  </si>
-  <si>
-    <t>Afifah</t>
-  </si>
-  <si>
-    <t>Zaidan Ariefyandi</t>
-  </si>
-  <si>
-    <t>Sandlyra Anastasya</t>
-  </si>
-  <si>
-    <t>helmi</t>
-  </si>
-  <si>
-    <t>Reynaldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> widyaloka</t>
-  </si>
-  <si>
-    <t>Amelia Nur</t>
-  </si>
-  <si>
-    <t>Syifa Zulfa</t>
-  </si>
-  <si>
-    <t>Niko</t>
-  </si>
-  <si>
-    <t>Wahyu Setianingsih</t>
-  </si>
-  <si>
-    <t>Karlina</t>
-  </si>
-  <si>
-    <t>Nabilla</t>
-  </si>
-  <si>
-    <t>Tiffani Agil</t>
-  </si>
-  <si>
-    <t>Nina Dwi Suryani</t>
-  </si>
-  <si>
-    <t>Mahendra Putra Wardhana</t>
-  </si>
-  <si>
-    <t>Afita Khoerunnisa</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>Dita</t>
-  </si>
-  <si>
-    <t>Sifa</t>
-  </si>
-  <si>
-    <t>Hanifa</t>
-  </si>
-  <si>
-    <t>Akhmad binangun</t>
-  </si>
-  <si>
-    <t>- lala</t>
-  </si>
-  <si>
-    <t>sabrina</t>
-  </si>
-  <si>
-    <t>Utia</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve"> Uji</t>
@@ -411,14 +405,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FFFF"/>
-        <bgColor rgb="FF00FFFF"/>
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -429,8 +423,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -596,7 +590,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -674,76 +668,88 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="7" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="13" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -755,23 +761,23 @@
     <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="12" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="12" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -781,13 +787,13 @@
     <xf borderId="12" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="12" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -815,7 +821,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -843,7 +849,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -871,7 +877,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -899,7 +905,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -927,7 +933,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -955,7 +961,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1757,11 +1763,13 @@
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="27">
+      <c r="M18" s="25">
+        <v>7.0</v>
+      </c>
+      <c r="N18" s="24">
         <v>0.5</v>
       </c>
-      <c r="O18" s="28" t="s">
+      <c r="O18" s="25" t="s">
         <v>17</v>
       </c>
       <c r="P18" s="25" t="s">
@@ -1795,134 +1803,110 @@
       <c r="AD18" s="26"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="23">
+      <c r="A19" s="21">
         <v>8.0</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="22">
         <v>0.5208333333333334</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="29">
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="27">
         <v>8.0</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="28">
         <v>0.5208333333333334</v>
       </c>
-      <c r="I19" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" s="25" t="s">
-        <v>16</v>
-      </c>
+      <c r="I19" s="29"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
       <c r="M19" s="23">
         <v>8.0</v>
       </c>
       <c r="N19" s="24">
         <v>0.5208333333333334</v>
       </c>
-      <c r="O19" s="32" t="s">
-        <v>21</v>
+      <c r="O19" s="30" t="s">
+        <v>18</v>
       </c>
       <c r="P19" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S19" s="23">
+        <v>19</v>
+      </c>
+      <c r="Q19" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="S19" s="21">
         <v>8.0</v>
       </c>
-      <c r="T19" s="24">
+      <c r="T19" s="22">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="V19" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="W19" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="X19" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y19" s="34">
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="33">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="35">
+      <c r="Z19" s="34">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="36"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="36"/>
-      <c r="AD19" s="36"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="23">
+      <c r="A20" s="36">
         <v>9.0</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="37">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="37">
+      <c r="F20" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="39">
         <v>9.0</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="40">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="23">
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="41">
         <v>9.0</v>
       </c>
-      <c r="N20" s="24">
+      <c r="N20" s="42">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="40" t="s">
+      <c r="O20" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="Q20" s="40" t="s">
+      <c r="Q20" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="40" t="s">
+      <c r="R20" s="44" t="s">
         <v>16</v>
       </c>
       <c r="S20" s="23">
@@ -1931,16 +1915,16 @@
       <c r="T20" s="24">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="V20" s="25" t="s">
+      <c r="U20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="V20" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="W20" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="X20" s="25" t="s">
+      <c r="W20" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="X20" s="38" t="s">
         <v>16</v>
       </c>
       <c r="Y20" s="23">
@@ -1950,7 +1934,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="AA20" s="25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AB20" s="25" t="s">
         <v>25</v>
@@ -1958,63 +1942,63 @@
       <c r="AC20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="25" t="s">
+      <c r="AD20" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="41">
+      <c r="A21" s="45">
         <v>10.0</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="46">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="36">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="37">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="36">
+        <v>10.0</v>
+      </c>
+      <c r="N21" s="47">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="O21" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="P21" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="N21" s="43">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="O21" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="P21" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="R21" s="25" t="s">
+      <c r="Q21" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="38" t="s">
         <v>16</v>
       </c>
       <c r="S21" s="23">
@@ -2023,920 +2007,932 @@
       <c r="T21" s="24">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="V21" s="46" t="s">
+      <c r="U21" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="W21" s="46" t="s">
+      <c r="W21" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="37">
+      <c r="X21" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="39">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="38">
+      <c r="Z21" s="40">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
+      <c r="AA21" s="39"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="39"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="23">
+      <c r="A22" s="36">
         <v>11.0</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="37">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="36">
+        <v>11.0</v>
+      </c>
+      <c r="H22" s="37">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="36">
+        <v>11.0</v>
+      </c>
+      <c r="N22" s="47">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="O22" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="R22" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="39">
+        <v>11.0</v>
+      </c>
+      <c r="T22" s="40">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="36">
+        <v>11.0</v>
+      </c>
+      <c r="Z22" s="37">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="AA22" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="H22" s="24">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="N22" s="43">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="O22" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="P22" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="R22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S22" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="T22" s="24">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="U22" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="V22" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="W22" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="X22" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y22" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="Z22" s="24">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="AA22" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB22" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC22" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD22" s="25" t="s">
+      <c r="AB22" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC22" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD22" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="23">
+      <c r="A23" s="36">
         <v>12.0</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="37">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23">
+      <c r="E23" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="36">
         <v>12.0</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="37">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="48" t="s">
+      <c r="I23" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="23">
+      <c r="K23" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="36">
         <v>12.0</v>
       </c>
-      <c r="N23" s="43">
+      <c r="N23" s="47">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="P23" s="45" t="s">
+      <c r="O23" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="Q23" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="R23" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S23" s="23">
+      <c r="Q23" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S23" s="36">
         <v>12.0</v>
       </c>
-      <c r="T23" s="24">
+      <c r="T23" s="37">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="V23" s="25" t="s">
+      <c r="U23" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="V23" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="W23" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="X23" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y23" s="37">
+      <c r="W23" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="X23" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y23" s="39">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="38">
+      <c r="Z23" s="40">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="37"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="37"/>
-      <c r="AD23" s="37"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="23">
+      <c r="A24" s="36">
         <v>13.0</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="37">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="25" t="s">
+      <c r="C24" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="36">
+        <v>13.0</v>
+      </c>
+      <c r="H24" s="37">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="36">
+        <v>13.0</v>
+      </c>
+      <c r="N24" s="37">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="O24" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="23">
+      <c r="P24" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S24" s="36">
         <v>13.0</v>
       </c>
-      <c r="H24" s="24">
+      <c r="T24" s="37">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="25" t="s">
+      <c r="U24" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="V24" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K24" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="23">
+      <c r="W24" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="X24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y24" s="39">
         <v>13.0</v>
       </c>
-      <c r="N24" s="24">
+      <c r="Z24" s="40">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="P24" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S24" s="23">
-        <v>13.0</v>
-      </c>
-      <c r="T24" s="24">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="U24" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="V24" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="W24" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="X24" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y24" s="37">
-        <v>13.0</v>
-      </c>
-      <c r="Z24" s="38">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="37"/>
-      <c r="AD24" s="37"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="23">
+      <c r="A25" s="36">
         <v>14.0</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="37">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="25" t="s">
+      <c r="C25" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="23">
+      <c r="F25" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="36">
         <v>14.0</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="37">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="25" t="s">
+      <c r="I25" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="23">
+      <c r="K25" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="36">
         <v>14.0</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="37">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="P25" s="25" t="s">
+      <c r="O25" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="P25" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Q25" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="R25" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S25" s="37">
+      <c r="Q25" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S25" s="39">
         <v>14.0</v>
       </c>
-      <c r="T25" s="38">
+      <c r="T25" s="40">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="37"/>
-      <c r="V25" s="37"/>
-      <c r="W25" s="37"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="23">
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="36">
         <v>14.0</v>
       </c>
-      <c r="Z25" s="24">
+      <c r="Z25" s="37">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB25" s="25" t="s">
+      <c r="AA25" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB25" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC25" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD25" s="25" t="s">
+      <c r="AC25" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD25" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="23">
+      <c r="A26" s="36">
         <v>15.0</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="37">
         <v>0.625</v>
       </c>
-      <c r="C26" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="25" t="s">
+      <c r="C26" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="23">
+      <c r="F26" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="36">
         <v>15.0</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="37">
         <v>0.625</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="23">
+      <c r="I26" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="36">
         <v>15.0</v>
       </c>
-      <c r="N26" s="24">
+      <c r="N26" s="37">
         <v>0.625</v>
       </c>
-      <c r="O26" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="P26" s="23" t="s">
+      <c r="O26" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="P26" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="Q26" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="37">
+      <c r="Q26" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="R26" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="39">
         <v>15.0</v>
       </c>
-      <c r="T26" s="38">
+      <c r="T26" s="40">
         <v>0.625</v>
       </c>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="23">
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="36">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="24">
+      <c r="Z26" s="37">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB26" s="25" t="s">
+      <c r="AA26" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB26" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC26" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD26" s="25" t="s">
+      <c r="AC26" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD26" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="23">
+      <c r="A27" s="36">
         <v>16.0</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="37">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="25" t="s">
+      <c r="C27" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="23">
+      <c r="E27" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="36">
         <v>16.0</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="37">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="J27" s="25" t="s">
+      <c r="I27" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="23">
+      <c r="K27" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="36">
         <v>16.0</v>
       </c>
-      <c r="N27" s="24">
+      <c r="N27" s="37">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="P27" s="25" t="s">
+      <c r="O27" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Q27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="R27" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S27" s="51">
+      <c r="Q27" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S27" s="55">
         <v>16.0</v>
       </c>
-      <c r="T27" s="52">
+      <c r="T27" s="56">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="51"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="23">
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="36">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="24">
+      <c r="Z27" s="37">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB27" s="25" t="s">
+      <c r="AA27" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD27" s="25" t="s">
+      <c r="AC27" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD27" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="23">
+      <c r="A28" s="36">
         <v>17.0</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="37">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="25" t="s">
+      <c r="C28" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="23">
+      <c r="F28" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="36">
         <v>17.0</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="37">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="J28" s="25" t="s">
+      <c r="I28" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="J28" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="25" t="s">
+      <c r="K28" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="23">
+      <c r="L28" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="36">
         <v>17.0</v>
       </c>
-      <c r="N28" s="24">
+      <c r="N28" s="37">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="P28" s="25" t="s">
+      <c r="O28" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="P28" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Q28" s="25" t="s">
+      <c r="Q28" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S28" s="37">
+      <c r="R28" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S28" s="39">
         <v>17.0</v>
       </c>
-      <c r="T28" s="38">
+      <c r="T28" s="40">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="23">
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="36">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="24">
+      <c r="Z28" s="37">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB28" s="41" t="s">
+      <c r="AA28" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB28" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="AC28" s="41" t="s">
+      <c r="AC28" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="AD28" s="55" t="s">
+      <c r="AD28" s="59" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="23">
+      <c r="A29" s="36">
         <v>18.0</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="37">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="25" t="s">
+      <c r="C29" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="23">
+      <c r="F29" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="36">
         <v>18.0</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="37">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="J29" s="25" t="s">
+      <c r="I29" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="J29" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K29" s="25" t="s">
+      <c r="K29" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L29" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="23">
+      <c r="L29" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="36">
         <v>18.0</v>
       </c>
-      <c r="N29" s="24">
+      <c r="N29" s="37">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="P29" s="25" t="s">
+      <c r="O29" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="P29" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Q29" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="R29" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="37">
+      <c r="Q29" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="S29" s="39">
         <v>18.0</v>
       </c>
-      <c r="T29" s="38">
+      <c r="T29" s="40">
         <v>0.6666666666666666</v>
       </c>
-      <c r="U29" s="37"/>
-      <c r="V29" s="37"/>
-      <c r="W29" s="37"/>
-      <c r="X29" s="37"/>
-      <c r="Y29" s="23">
+      <c r="U29" s="39"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="36">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="24">
+      <c r="Z29" s="37">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB29" s="25" t="s">
+      <c r="AA29" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB29" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC29" s="25" t="s">
+      <c r="AC29" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AD29" s="25" t="s">
+      <c r="AD29" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="23">
+      <c r="A30" s="36">
         <v>19.0</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="37">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="25" t="s">
+      <c r="C30" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="23">
+      <c r="F30" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="36">
         <v>19.0</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="37">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="25" t="s">
+      <c r="I30" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="J30" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K30" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="56">
+      <c r="K30" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="41">
         <v>19.0</v>
       </c>
-      <c r="N30" s="57">
+      <c r="N30" s="42">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="59"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="41">
+      <c r="O30" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="45">
         <v>19.0</v>
       </c>
-      <c r="T30" s="42">
+      <c r="T30" s="46">
         <v>0.6805555555555556</v>
       </c>
-      <c r="U30" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="V30" s="41" t="s">
+      <c r="U30" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="V30" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="W30" s="41" t="s">
+      <c r="W30" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="X30" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y30" s="23">
+      <c r="X30" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y30" s="36">
         <v>19.0</v>
       </c>
-      <c r="Z30" s="24">
+      <c r="Z30" s="37">
         <v>0.6805555555555556</v>
       </c>
-      <c r="AA30" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB30" s="25" t="s">
+      <c r="AA30" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB30" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC30" s="25" t="s">
+      <c r="AC30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AD30" s="25" t="s">
+      <c r="AD30" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="23">
+      <c r="A31" s="36">
         <v>20.0</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="37">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="25" t="s">
+      <c r="C31" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" s="23">
+      <c r="F31" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="36">
         <v>20.0</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="37">
         <v>0.6944444444444444</v>
       </c>
-      <c r="I31" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J31" s="25" t="s">
+      <c r="I31" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K31" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="56">
+      <c r="K31" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="41">
         <v>20.0</v>
       </c>
-      <c r="N31" s="57">
+      <c r="N31" s="42">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="59"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="37">
+      <c r="O31" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="39">
         <v>20.0</v>
       </c>
-      <c r="T31" s="38">
+      <c r="T31" s="40">
         <v>0.6944444444444444</v>
       </c>
-      <c r="U31" s="37"/>
-      <c r="V31" s="37"/>
-      <c r="W31" s="37"/>
-      <c r="X31" s="37"/>
-      <c r="Y31" s="23">
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="36">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="24">
+      <c r="Z31" s="37">
         <v>0.6944444444444444</v>
       </c>
-      <c r="AA31" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB31" s="25" t="s">
+      <c r="AA31" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB31" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC31" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD31" s="25" t="s">
+      <c r="AC31" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD31" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="23">
+      <c r="A32" s="36">
         <v>21.0</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="37">
         <v>0.7083333333333334</v>
       </c>
-      <c r="C32" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="25" t="s">
+      <c r="C32" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="21">
+      <c r="F32" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="36">
         <v>21.0</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="37">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="56">
+      <c r="I32" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="41">
         <v>21.0</v>
       </c>
-      <c r="N32" s="57">
+      <c r="N32" s="42">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P32" s="59"/>
-      <c r="Q32" s="59"/>
-      <c r="R32" s="60"/>
-      <c r="S32" s="21">
+      <c r="O32" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="36">
         <v>21.0</v>
       </c>
-      <c r="T32" s="22">
+      <c r="T32" s="37">
         <v>0.7083333333333334</v>
       </c>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
+      <c r="U32" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="V32" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="W32" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="X32" s="64" t="s">
+        <v>16</v>
+      </c>
       <c r="Y32" s="21">
         <v>21.0</v>
       </c>
@@ -2949,22 +2945,22 @@
       <c r="AD32" s="21"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="23">
+      <c r="A33" s="36">
         <v>22.0</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="37">
         <v>0.7222222222222222</v>
       </c>
-      <c r="C33" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="25" t="s">
+      <c r="C33" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="25" t="s">
+      <c r="E33" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="38" t="s">
         <v>16</v>
       </c>
       <c r="G33" s="21">
@@ -2977,18 +2973,18 @@
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
-      <c r="M33" s="56">
+      <c r="M33" s="41">
         <v>22.0</v>
       </c>
-      <c r="N33" s="57">
+      <c r="N33" s="42">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P33" s="59"/>
-      <c r="Q33" s="59"/>
-      <c r="R33" s="60"/>
+      <c r="O33" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="62"/>
       <c r="S33" s="21">
         <v>22.0</v>
       </c>
@@ -3006,25 +3002,33 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
       <c r="AD33" s="21"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="21">
+      <c r="A34" s="36">
         <v>23.0</v>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="37">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="C34" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>16</v>
+      </c>
       <c r="G34" s="21">
-        <v>23.0</v>
+        <v>7.0</v>
       </c>
       <c r="H34" s="22">
         <v>0.7361111111111112</v>
@@ -3033,18 +3037,18 @@
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
-      <c r="M34" s="56">
+      <c r="M34" s="41">
         <v>23.0</v>
       </c>
-      <c r="N34" s="57">
+      <c r="N34" s="42">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="60"/>
+      <c r="O34" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="62"/>
       <c r="S34" s="21">
         <v>23.0</v>
       </c>
@@ -3087,18 +3091,18 @@
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="56">
+      <c r="M35" s="41">
         <v>24.0</v>
       </c>
-      <c r="N35" s="57">
+      <c r="N35" s="42">
         <v>0.75</v>
       </c>
-      <c r="O35" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P35" s="59"/>
-      <c r="Q35" s="59"/>
-      <c r="R35" s="60"/>
+      <c r="O35" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="62"/>
       <c r="S35" s="21">
         <v>24.0</v>
       </c>
@@ -3141,18 +3145,18 @@
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
-      <c r="M36" s="56">
+      <c r="M36" s="41">
         <v>25.0</v>
       </c>
-      <c r="N36" s="57">
+      <c r="N36" s="42">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="59"/>
-      <c r="R36" s="60"/>
+      <c r="O36" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="62"/>
       <c r="S36" s="21">
         <v>25.0</v>
       </c>
@@ -3185,36 +3189,36 @@
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="23">
+      <c r="G37" s="36">
         <v>26.0</v>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="37">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="J37" s="25" t="s">
+      <c r="I37" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="56">
+      <c r="K37" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="41">
         <v>26.0</v>
       </c>
-      <c r="N37" s="57">
+      <c r="N37" s="42">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P37" s="59"/>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="60"/>
+      <c r="O37" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="62"/>
       <c r="S37" s="21">
         <v>26.0</v>
       </c>
@@ -3257,18 +3261,18 @@
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
-      <c r="M38" s="56">
+      <c r="M38" s="41">
         <v>27.0</v>
       </c>
-      <c r="N38" s="57">
+      <c r="N38" s="42">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="59"/>
-      <c r="R38" s="60"/>
+      <c r="O38" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="62"/>
       <c r="S38" s="21">
         <v>27.0</v>
       </c>
@@ -3311,18 +3315,18 @@
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
-      <c r="M39" s="56">
+      <c r="M39" s="41">
         <v>28.0</v>
       </c>
-      <c r="N39" s="57">
+      <c r="N39" s="42">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="59"/>
-      <c r="R39" s="60"/>
+      <c r="O39" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="62"/>
       <c r="S39" s="21">
         <v>28.0</v>
       </c>
@@ -3342,7 +3346,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="61"/>
+      <c r="AD39" s="65"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3365,18 +3369,18 @@
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
-      <c r="M40" s="56">
+      <c r="M40" s="41">
         <v>29.0</v>
       </c>
-      <c r="N40" s="57">
+      <c r="N40" s="42">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P40" s="59"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="60"/>
+      <c r="O40" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="62"/>
       <c r="S40" s="21">
         <v>29.0</v>
       </c>
@@ -3396,7 +3400,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="61"/>
+      <c r="AD40" s="65"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3419,18 +3423,18 @@
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
-      <c r="M41" s="56">
+      <c r="M41" s="41">
         <v>30.0</v>
       </c>
-      <c r="N41" s="57">
+      <c r="N41" s="42">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="59"/>
-      <c r="R41" s="60"/>
+      <c r="O41" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="62"/>
       <c r="S41" s="21">
         <v>30.0</v>
       </c>
@@ -3450,7 +3454,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="61"/>
+      <c r="AD41" s="65"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3473,18 +3477,18 @@
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
-      <c r="M42" s="56">
+      <c r="M42" s="41">
         <v>31.0</v>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="42">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="P42" s="59"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="60"/>
+      <c r="O42" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="62"/>
       <c r="S42" s="21">
         <v>31.0</v>
       </c>
@@ -3504,61 +3508,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="61"/>
+      <c r="AD42" s="65"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="66">
         <v>32.0</v>
       </c>
-      <c r="B43" s="63">
+      <c r="B43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62">
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66">
         <v>32.0</v>
       </c>
-      <c r="H43" s="63">
+      <c r="H43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="62"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="62"/>
-      <c r="L43" s="62"/>
-      <c r="M43" s="64">
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="68">
         <v>32.0</v>
       </c>
-      <c r="N43" s="65">
+      <c r="N43" s="69">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
-      <c r="R43" s="68"/>
-      <c r="S43" s="62">
+      <c r="O43" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="P43" s="71"/>
+      <c r="Q43" s="71"/>
+      <c r="R43" s="72"/>
+      <c r="S43" s="66">
         <v>32.0</v>
       </c>
-      <c r="T43" s="63">
+      <c r="T43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="62"/>
-      <c r="V43" s="62"/>
-      <c r="W43" s="62"/>
-      <c r="X43" s="62"/>
-      <c r="Y43" s="62">
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="66"/>
+      <c r="X43" s="66"/>
+      <c r="Y43" s="66">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="63">
+      <c r="Z43" s="67">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="62"/>
-      <c r="AB43" s="62"/>
-      <c r="AC43" s="62"/>
-      <c r="AD43" s="69"/>
+      <c r="AA43" s="66"/>
+      <c r="AB43" s="66"/>
+      <c r="AC43" s="66"/>
+      <c r="AD43" s="73"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -103,147 +103,144 @@
     <t>AD</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fadila</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Qotrunnada Maulidia</t>
+  </si>
+  <si>
+    <t>Nasywaa</t>
+  </si>
+  <si>
+    <t>Mufti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduation </t>
+  </si>
+  <si>
+    <t>Ilut</t>
+  </si>
+  <si>
+    <t>nabila hasna</t>
+  </si>
+  <si>
+    <t>Logi</t>
+  </si>
+  <si>
+    <t>Aulia Hani</t>
+  </si>
+  <si>
+    <t>Windi</t>
+  </si>
+  <si>
+    <t>Shabrina Amalia</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>Wafi Wafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tika Dwi</t>
+  </si>
+  <si>
+    <t>Devinta Khoerunnisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> oktriana</t>
+  </si>
+  <si>
+    <t>N. A. Salsabila</t>
+  </si>
+  <si>
+    <t>Rahayu Purnama</t>
+  </si>
+  <si>
+    <t>Graduatiom</t>
+  </si>
+  <si>
+    <t>Gandring Guste Puand</t>
+  </si>
+  <si>
+    <t>Graduatio prem</t>
+  </si>
+  <si>
+    <t>Afifah</t>
+  </si>
+  <si>
+    <t>Zaidan Ariefyandi</t>
+  </si>
+  <si>
+    <t>Sandlyra Anastasya</t>
+  </si>
+  <si>
+    <t>helmi</t>
+  </si>
+  <si>
+    <t>Reynaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> widyaloka</t>
+  </si>
+  <si>
+    <t>Amelia Nur</t>
+  </si>
+  <si>
+    <t>calresta</t>
+  </si>
+  <si>
+    <t>Niko</t>
+  </si>
+  <si>
+    <t>Wahyu Setianingsih</t>
+  </si>
+  <si>
+    <t>Karlina</t>
+  </si>
+  <si>
+    <t>Nabilla</t>
+  </si>
+  <si>
+    <t>Tiffani Agil</t>
+  </si>
+  <si>
+    <t>Nina Dwi Suryani</t>
+  </si>
+  <si>
+    <t>Mahendra Putra Wardhana</t>
+  </si>
+  <si>
+    <t>Afita Khoerunnisa</t>
+  </si>
+  <si>
+    <t>Dita</t>
+  </si>
+  <si>
+    <t>Sifa</t>
+  </si>
+  <si>
+    <t>Hanifa</t>
+  </si>
+  <si>
+    <t>Akhmad binangun</t>
+  </si>
+  <si>
+    <t>lala</t>
+  </si>
+  <si>
+    <t>sabrina</t>
+  </si>
+  <si>
     <t>Claresta</t>
   </si>
   <si>
-    <t xml:space="preserve">Graduation </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fadila</t>
-  </si>
-  <si>
-    <t>Rani</t>
-  </si>
-  <si>
-    <t>Rahayu Purnama</t>
-  </si>
-  <si>
-    <t>Graduatiom</t>
-  </si>
-  <si>
-    <t>Qotrunnada Maulidia</t>
-  </si>
-  <si>
-    <t>Nasywaa</t>
-  </si>
-  <si>
-    <t>Mufti</t>
-  </si>
-  <si>
-    <t>Ilut</t>
-  </si>
-  <si>
-    <t>nabila hasna</t>
-  </si>
-  <si>
-    <t>Logi</t>
-  </si>
-  <si>
-    <t>Aulia Hani</t>
-  </si>
-  <si>
-    <t>Windi</t>
-  </si>
-  <si>
-    <t>Shabrina Amalia</t>
-  </si>
-  <si>
-    <t>Nana</t>
-  </si>
-  <si>
-    <t>Wafi Wafa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tika Dwi</t>
-  </si>
-  <si>
-    <t>Devinta Khoerunnisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> oktriana</t>
-  </si>
-  <si>
-    <t>N. A. Salsabila</t>
-  </si>
-  <si>
-    <t>Gandring Guste Puand</t>
-  </si>
-  <si>
-    <t>Graduatio prem</t>
-  </si>
-  <si>
-    <t>Afifah</t>
-  </si>
-  <si>
-    <t>Zaidan Ariefyandi</t>
-  </si>
-  <si>
-    <t>Sandlyra Anastasya</t>
-  </si>
-  <si>
-    <t>helmi</t>
-  </si>
-  <si>
-    <t>Reynaldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> widyaloka</t>
-  </si>
-  <si>
-    <t>Amelia Nur</t>
-  </si>
-  <si>
-    <t>Syifa Zulfa</t>
-  </si>
-  <si>
-    <t>Niko</t>
-  </si>
-  <si>
-    <t>Wahyu Setianingsih</t>
-  </si>
-  <si>
-    <t>Karlina</t>
-  </si>
-  <si>
-    <t>Nabilla</t>
-  </si>
-  <si>
-    <t>Tiffani Agil</t>
-  </si>
-  <si>
-    <t>Nina Dwi Suryani</t>
-  </si>
-  <si>
-    <t>Mahendra Putra Wardhana</t>
-  </si>
-  <si>
-    <t>Afita Khoerunnisa</t>
-  </si>
-  <si>
     <t>CLOSED</t>
   </si>
   <si>
-    <t>Dita</t>
-  </si>
-  <si>
-    <t>Sifa</t>
-  </si>
-  <si>
-    <t>Hanifa</t>
-  </si>
-  <si>
-    <t>Akhmad binangun</t>
-  </si>
-  <si>
-    <t>lala</t>
-  </si>
-  <si>
-    <t>sabrina</t>
-  </si>
-  <si>
-    <t>Cahya Juwita</t>
-  </si>
-  <si>
     <t>Desti Ika c</t>
   </si>
   <si>
@@ -257,6 +254,9 @@
   </si>
   <si>
     <t>Graaduation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indah </t>
   </si>
   <si>
     <t xml:space="preserve"> Uji</t>
@@ -411,14 +411,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -428,7 +428,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border/>
     <border>
       <right style="thin">
@@ -535,6 +535,11 @@
       </bottom>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
       <top style="dotted">
         <color rgb="FF000000"/>
       </top>
@@ -590,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="84">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -680,125 +685,155 @@
     <xf borderId="6" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="12" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="11" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="9" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="12" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="12" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -821,7 +856,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -877,7 +912,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -905,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -933,7 +968,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -961,7 +996,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1835,10 +1870,10 @@
       <c r="P19" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="Q19" s="31" t="s">
+      <c r="Q19" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="R19" s="31" t="s">
+      <c r="R19" s="25" t="s">
         <v>16</v>
       </c>
       <c r="S19" s="21">
@@ -1847,66 +1882,66 @@
       <c r="T19" s="22">
         <v>0.5208333333333334</v>
       </c>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="33">
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="32">
         <v>8.0</v>
       </c>
-      <c r="Z19" s="34">
+      <c r="Z19" s="33">
         <v>0.5208333333333334</v>
       </c>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="35"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="34"/>
+      <c r="AC19" s="34"/>
+      <c r="AD19" s="34"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="36">
+      <c r="A20" s="35">
         <v>9.0</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="36">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="38" t="s">
+      <c r="D20" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="39">
+      <c r="F20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="38">
         <v>9.0</v>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="39">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="41">
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="35">
         <v>9.0</v>
       </c>
-      <c r="N20" s="42">
+      <c r="N20" s="36">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="43" t="s">
+      <c r="O20" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="P20" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="44" t="s">
+      <c r="P20" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="44" t="s">
+      <c r="R20" s="41" t="s">
         <v>16</v>
       </c>
       <c r="S20" s="23">
@@ -1915,16 +1950,16 @@
       <c r="T20" s="24">
         <v>0.5416666666666666</v>
       </c>
-      <c r="U20" s="38" t="s">
+      <c r="U20" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="V20" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="W20" s="38" t="s">
+      <c r="V20" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="W20" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="X20" s="38" t="s">
+      <c r="X20" s="25" t="s">
         <v>16</v>
       </c>
       <c r="Y20" s="23">
@@ -1942,63 +1977,55 @@
       <c r="AC20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AD20" s="38" t="s">
+      <c r="AD20" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="45">
+      <c r="A21" s="42">
         <v>10.0</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="43">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="45" t="s">
+      <c r="D21" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="36">
+      <c r="F21" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="38">
         <v>10.0</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="39">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="45" t="s">
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="35">
+        <v>10.0</v>
+      </c>
+      <c r="N21" s="45">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="O21" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="36">
-        <v>10.0</v>
-      </c>
-      <c r="N21" s="47">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="O21" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="38" t="s">
+      <c r="P21" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="R21" s="38" t="s">
+      <c r="R21" s="37" t="s">
         <v>16</v>
       </c>
       <c r="S21" s="23">
@@ -2007,994 +2034,1022 @@
       <c r="T21" s="24">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="V21" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" s="50" t="s">
+      <c r="U21" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="V21" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="W21" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="39">
+      <c r="X21" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="38">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="40">
+      <c r="Z21" s="39">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="39"/>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="39"/>
+      <c r="AA21" s="38"/>
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="38"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="36">
+      <c r="A22" s="21">
         <v>11.0</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="22">
         <v>0.5694444444444444</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="H22" s="24">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="N22" s="50">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="O22" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="R22" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="38">
+        <v>11.0</v>
+      </c>
+      <c r="T22" s="39">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="Z22" s="24">
+        <v>0.5694444444444444</v>
+      </c>
+      <c r="AA22" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="AB22" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="AC22" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="H22" s="37">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="N22" s="47">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="O22" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="P22" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="R22" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S22" s="39">
-        <v>11.0</v>
-      </c>
-      <c r="T22" s="40">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="Z22" s="37">
-        <v>0.5694444444444444</v>
-      </c>
-      <c r="AA22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB22" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC22" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD22" s="38" t="s">
+      <c r="AD22" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="36">
+      <c r="A23" s="23">
         <v>12.0</v>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="24">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="23">
+        <v>12.0</v>
+      </c>
+      <c r="H23" s="24">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="35">
+        <v>12.0</v>
+      </c>
+      <c r="N23" s="45">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="O23" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="S23" s="35">
+        <v>12.0</v>
+      </c>
+      <c r="T23" s="36">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="U23" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="36">
+      <c r="V23" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="W23" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="X23" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y23" s="38">
         <v>12.0</v>
       </c>
-      <c r="H23" s="37">
+      <c r="Z23" s="39">
         <v>0.5833333333333334</v>
       </c>
-      <c r="I23" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="36">
-        <v>12.0</v>
-      </c>
-      <c r="N23" s="47">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="O23" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="P23" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S23" s="36">
-        <v>12.0</v>
-      </c>
-      <c r="T23" s="37">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="U23" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="V23" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="X23" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y23" s="39">
-        <v>12.0</v>
-      </c>
-      <c r="Z23" s="40">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="AA23" s="39"/>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="39"/>
-      <c r="AD23" s="39"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="38"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="36">
+      <c r="A24" s="35">
         <v>13.0</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="36">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="35">
+        <v>13.0</v>
+      </c>
+      <c r="H24" s="36">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="35">
+        <v>13.0</v>
+      </c>
+      <c r="N24" s="36">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="O24" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="S24" s="23">
+        <v>13.0</v>
+      </c>
+      <c r="T24" s="24">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="U24" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="36">
+      <c r="V24" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="W24" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="X24" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y24" s="38">
         <v>13.0</v>
       </c>
-      <c r="H24" s="37">
+      <c r="Z24" s="39">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="36">
-        <v>13.0</v>
-      </c>
-      <c r="N24" s="37">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="O24" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="P24" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S24" s="36">
-        <v>13.0</v>
-      </c>
-      <c r="T24" s="37">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="U24" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="W24" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="X24" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y24" s="39">
-        <v>13.0</v>
-      </c>
-      <c r="Z24" s="40">
-        <v>0.5972222222222222</v>
-      </c>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
+      <c r="AA24" s="38"/>
+      <c r="AB24" s="38"/>
+      <c r="AC24" s="38"/>
+      <c r="AD24" s="38"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="36">
+      <c r="A25" s="57">
         <v>14.0</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="58">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="57">
+        <v>14.0</v>
+      </c>
+      <c r="H25" s="58">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="I25" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="N25" s="24">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="O25" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="S25" s="38">
+        <v>14.0</v>
+      </c>
+      <c r="T25" s="39">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="38"/>
+      <c r="Y25" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="Z25" s="24">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AA25" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="36">
-        <v>14.0</v>
-      </c>
-      <c r="H25" s="37">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="38" t="s">
+      <c r="AB25" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC25" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="36">
-        <v>14.0</v>
-      </c>
-      <c r="N25" s="37">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="O25" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="P25" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S25" s="39">
-        <v>14.0</v>
-      </c>
-      <c r="T25" s="40">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="U25" s="39"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="39"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="36">
-        <v>14.0</v>
-      </c>
-      <c r="Z25" s="37">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="AA25" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB25" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC25" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD25" s="38" t="s">
+      <c r="AD25" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="36">
+      <c r="A26" s="23">
         <v>15.0</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="24">
         <v>0.625</v>
       </c>
-      <c r="C26" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="36">
+      <c r="C26" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="57">
         <v>15.0</v>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="58">
         <v>0.625</v>
       </c>
-      <c r="I26" s="38" t="s">
+      <c r="I26" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="J26" s="38" t="s">
+      <c r="K26" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="57">
+        <v>15.0</v>
+      </c>
+      <c r="N26" s="58">
+        <v>0.625</v>
+      </c>
+      <c r="O26" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="38" t="s">
+      <c r="P26" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="R26" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="38">
+        <v>15.0</v>
+      </c>
+      <c r="T26" s="39">
+        <v>0.625</v>
+      </c>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="57">
+        <v>15.0</v>
+      </c>
+      <c r="Z26" s="58">
+        <v>0.625</v>
+      </c>
+      <c r="AA26" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB26" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="36">
-        <v>15.0</v>
-      </c>
-      <c r="N26" s="37">
-        <v>0.625</v>
-      </c>
-      <c r="O26" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="P26" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="R26" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="39">
-        <v>15.0</v>
-      </c>
-      <c r="T26" s="40">
-        <v>0.625</v>
-      </c>
-      <c r="U26" s="39"/>
-      <c r="V26" s="39"/>
-      <c r="W26" s="39"/>
-      <c r="X26" s="39"/>
-      <c r="Y26" s="36">
-        <v>15.0</v>
-      </c>
-      <c r="Z26" s="37">
-        <v>0.625</v>
-      </c>
-      <c r="AA26" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB26" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC26" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD26" s="38" t="s">
+      <c r="AD26" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="36">
+      <c r="A27" s="57">
         <v>16.0</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="58">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="57">
+        <v>16.0</v>
+      </c>
+      <c r="H27" s="58">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="I27" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="38" t="s">
+      <c r="J27" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="36">
+      <c r="L27" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="23">
         <v>16.0</v>
       </c>
-      <c r="H27" s="37">
+      <c r="N27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="38" t="s">
+      <c r="O27" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="38" t="s">
+      <c r="P27" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="36">
+      <c r="R27" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="S27" s="44">
         <v>16.0</v>
       </c>
-      <c r="N27" s="37">
+      <c r="T27" s="60">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="38" t="s">
+      <c r="U27" s="44"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="44"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="57">
+        <v>16.0</v>
+      </c>
+      <c r="Z27" s="58">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AA27" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="P27" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="38" t="s">
+      <c r="AB27" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S27" s="55">
-        <v>16.0</v>
-      </c>
-      <c r="T27" s="56">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="U27" s="55"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="57"/>
-      <c r="Y27" s="36">
-        <v>16.0</v>
-      </c>
-      <c r="Z27" s="37">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="AA27" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB27" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC27" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD27" s="38" t="s">
+      <c r="AD27" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="36">
+      <c r="A28" s="57">
         <v>17.0</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="58">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="57">
+        <v>17.0</v>
+      </c>
+      <c r="H28" s="58">
+        <v>0.6527777777777778</v>
+      </c>
+      <c r="I28" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="38" t="s">
+      <c r="J28" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="36">
+      <c r="L28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="57">
         <v>17.0</v>
       </c>
-      <c r="H28" s="37">
+      <c r="N28" s="58">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="38" t="s">
+      <c r="O28" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="J28" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="38" t="s">
+      <c r="P28" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="36">
+      <c r="R28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="S28" s="38">
         <v>17.0</v>
       </c>
-      <c r="N28" s="37">
+      <c r="T28" s="39">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="38" t="s">
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="57">
+        <v>17.0</v>
+      </c>
+      <c r="Z28" s="58">
+        <v>0.6527777777777778</v>
+      </c>
+      <c r="AA28" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="P28" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="38" t="s">
+      <c r="AB28" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC28" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S28" s="39">
-        <v>17.0</v>
-      </c>
-      <c r="T28" s="40">
-        <v>0.6527777777777778</v>
-      </c>
-      <c r="U28" s="39"/>
-      <c r="V28" s="39"/>
-      <c r="W28" s="39"/>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="36">
-        <v>17.0</v>
-      </c>
-      <c r="Z28" s="37">
-        <v>0.6527777777777778</v>
-      </c>
-      <c r="AA28" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB28" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD28" s="59" t="s">
+      <c r="AD28" s="64" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="36">
+      <c r="A29" s="57">
         <v>18.0</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="57">
+        <v>18.0</v>
+      </c>
+      <c r="H29" s="58">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I29" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="38" t="s">
+      <c r="J29" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="36">
+      <c r="L29" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="57">
         <v>18.0</v>
       </c>
-      <c r="H29" s="37">
+      <c r="N29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="38" t="s">
+      <c r="O29" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" s="38" t="s">
+      <c r="P29" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="S29" s="38">
+        <v>18.0</v>
+      </c>
+      <c r="T29" s="39">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="57">
+        <v>18.0</v>
+      </c>
+      <c r="Z29" s="58">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA29" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB29" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC29" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="L29" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="36">
-        <v>18.0</v>
-      </c>
-      <c r="N29" s="37">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O29" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="P29" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="R29" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="39">
-        <v>18.0</v>
-      </c>
-      <c r="T29" s="40">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U29" s="39"/>
-      <c r="V29" s="39"/>
-      <c r="W29" s="39"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="36">
-        <v>18.0</v>
-      </c>
-      <c r="Z29" s="37">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA29" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB29" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC29" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD29" s="38" t="s">
+      <c r="AD29" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="36">
+      <c r="A30" s="57">
         <v>19.0</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="58">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="H30" s="58">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="I30" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="38" t="s">
+      <c r="J30" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="N30" s="58">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="O30" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="36">
+      <c r="R30" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="S30" s="63">
         <v>19.0</v>
       </c>
-      <c r="H30" s="37">
+      <c r="T30" s="67">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="38" t="s">
+      <c r="U30" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="J30" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="41">
+      <c r="V30" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="W30" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="X30" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y30" s="57">
         <v>19.0</v>
       </c>
-      <c r="N30" s="42">
+      <c r="Z30" s="58">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="60" t="s">
+      <c r="AA30" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="62"/>
-      <c r="S30" s="45">
-        <v>19.0</v>
-      </c>
-      <c r="T30" s="46">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="U30" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="V30" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="W30" s="45" t="s">
+      <c r="AB30" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC30" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="X30" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y30" s="36">
-        <v>19.0</v>
-      </c>
-      <c r="Z30" s="37">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="AA30" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB30" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC30" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD30" s="38" t="s">
+      <c r="AD30" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="36">
+      <c r="A31" s="57">
         <v>20.0</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="58">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="57">
+        <v>20.0</v>
+      </c>
+      <c r="H31" s="58">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="I31" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="57">
+        <v>20.0</v>
+      </c>
+      <c r="N31" s="58">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="O31" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R31" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="38">
+        <v>20.0</v>
+      </c>
+      <c r="T31" s="39">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="57">
+        <v>20.0</v>
+      </c>
+      <c r="Z31" s="58">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AA31" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" s="36">
-        <v>20.0</v>
-      </c>
-      <c r="H31" s="37">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="38" t="s">
+      <c r="AB31" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC31" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="41">
-        <v>20.0</v>
-      </c>
-      <c r="N31" s="42">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="O31" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="39">
-        <v>20.0</v>
-      </c>
-      <c r="T31" s="40">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="U31" s="39"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="39"/>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="36">
-        <v>20.0</v>
-      </c>
-      <c r="Z31" s="37">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="AA31" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB31" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC31" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD31" s="38" t="s">
+      <c r="AD31" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="36">
+      <c r="A32" s="57">
         <v>21.0</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="58">
         <v>0.7083333333333334</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="57">
+        <v>21.0</v>
+      </c>
+      <c r="H32" s="58">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="I32" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="K32" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="38">
+        <v>21.0</v>
+      </c>
+      <c r="N32" s="39">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O32" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="38" t="s">
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
+      <c r="R32" s="71"/>
+      <c r="S32" s="57">
+        <v>21.0</v>
+      </c>
+      <c r="T32" s="58">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="U32" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="V32" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="W32" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="36">
+      <c r="X32" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y32" s="57">
         <v>21.0</v>
       </c>
-      <c r="H32" s="37">
+      <c r="Z32" s="58">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="38" t="s">
+      <c r="AA32" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB32" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC32" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="41">
-        <v>21.0</v>
-      </c>
-      <c r="N32" s="42">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="62"/>
-      <c r="S32" s="36">
-        <v>21.0</v>
-      </c>
-      <c r="T32" s="37">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="U32" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="V32" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="W32" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="X32" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y32" s="21">
-        <v>21.0</v>
-      </c>
-      <c r="Z32" s="22">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
+      <c r="AD32" s="53" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="36">
+      <c r="A33" s="57">
         <v>22.0</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="C33" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="38" t="s">
+      <c r="C33" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="21">
+      <c r="F33" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="57">
         <v>22.0</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="41">
+      <c r="I33" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="35">
         <v>22.0</v>
       </c>
-      <c r="N33" s="42">
+      <c r="N33" s="36">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P33" s="61"/>
-      <c r="Q33" s="61"/>
-      <c r="R33" s="62"/>
-      <c r="S33" s="21">
+      <c r="O33" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="57">
         <v>22.0</v>
       </c>
-      <c r="T33" s="22">
+      <c r="T33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
+      <c r="U33" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="V33" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="W33" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="X33" s="53" t="s">
+        <v>16</v>
+      </c>
       <c r="Y33" s="21">
         <v>22.0</v>
       </c>
@@ -3002,29 +3057,29 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
       <c r="AD33" s="21"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="36">
+      <c r="A34" s="57">
         <v>23.0</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="58">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="F34" s="53" t="s">
         <v>16</v>
       </c>
       <c r="G34" s="21">
@@ -3037,18 +3092,18 @@
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
-      <c r="M34" s="41">
+      <c r="M34" s="35">
         <v>23.0</v>
       </c>
-      <c r="N34" s="42">
+      <c r="N34" s="36">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="62"/>
+      <c r="O34" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
+      <c r="R34" s="71"/>
       <c r="S34" s="21">
         <v>23.0</v>
       </c>
@@ -3077,10 +3132,10 @@
       <c r="B35" s="22">
         <v>0.75</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
       <c r="G35" s="21">
         <v>24.0</v>
       </c>
@@ -3091,18 +3146,18 @@
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="41">
+      <c r="M35" s="35">
         <v>24.0</v>
       </c>
-      <c r="N35" s="42">
+      <c r="N35" s="36">
         <v>0.75</v>
       </c>
-      <c r="O35" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="62"/>
+      <c r="O35" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="71"/>
       <c r="S35" s="21">
         <v>24.0</v>
       </c>
@@ -3125,16 +3180,24 @@
       <c r="AD35" s="21"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="21">
+      <c r="A36" s="57">
         <v>25.0</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="58">
         <v>0.7638888888888888</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>16</v>
+      </c>
       <c r="G36" s="21">
         <v>25.0</v>
       </c>
@@ -3145,18 +3208,18 @@
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
-      <c r="M36" s="41">
+      <c r="M36" s="35">
         <v>25.0</v>
       </c>
-      <c r="N36" s="42">
+      <c r="N36" s="36">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="61"/>
-      <c r="R36" s="62"/>
+      <c r="O36" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="71"/>
       <c r="S36" s="21">
         <v>25.0</v>
       </c>
@@ -3189,36 +3252,36 @@
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="36">
+      <c r="G37" s="57">
         <v>26.0</v>
       </c>
-      <c r="H37" s="37">
+      <c r="H37" s="58">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="38" t="s">
+      <c r="I37" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="J37" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="38" t="s">
+      <c r="J37" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="L37" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="41">
+      <c r="L37" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="35">
         <v>26.0</v>
       </c>
-      <c r="N37" s="42">
+      <c r="N37" s="36">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="62"/>
+      <c r="O37" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="71"/>
       <c r="S37" s="21">
         <v>26.0</v>
       </c>
@@ -3261,18 +3324,18 @@
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
-      <c r="M38" s="41">
+      <c r="M38" s="35">
         <v>27.0</v>
       </c>
-      <c r="N38" s="42">
+      <c r="N38" s="36">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="62"/>
+      <c r="O38" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="71"/>
       <c r="S38" s="21">
         <v>27.0</v>
       </c>
@@ -3315,18 +3378,18 @@
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
-      <c r="M39" s="41">
+      <c r="M39" s="35">
         <v>28.0</v>
       </c>
-      <c r="N39" s="42">
+      <c r="N39" s="36">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="62"/>
+      <c r="O39" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="71"/>
       <c r="S39" s="21">
         <v>28.0</v>
       </c>
@@ -3346,7 +3409,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="65"/>
+      <c r="AD39" s="75"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3369,18 +3432,18 @@
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
-      <c r="M40" s="41">
+      <c r="M40" s="35">
         <v>29.0</v>
       </c>
-      <c r="N40" s="42">
+      <c r="N40" s="36">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="62"/>
+      <c r="O40" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="71"/>
       <c r="S40" s="21">
         <v>29.0</v>
       </c>
@@ -3400,7 +3463,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="65"/>
+      <c r="AD40" s="75"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3423,18 +3486,18 @@
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
-      <c r="M41" s="41">
+      <c r="M41" s="35">
         <v>30.0</v>
       </c>
-      <c r="N41" s="42">
+      <c r="N41" s="36">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P41" s="61"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="62"/>
+      <c r="O41" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="71"/>
       <c r="S41" s="21">
         <v>30.0</v>
       </c>
@@ -3454,7 +3517,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="65"/>
+      <c r="AD41" s="75"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3477,18 +3540,18 @@
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
-      <c r="M42" s="41">
+      <c r="M42" s="35">
         <v>31.0</v>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="36">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="62"/>
+      <c r="O42" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="P42" s="70"/>
+      <c r="Q42" s="70"/>
+      <c r="R42" s="71"/>
       <c r="S42" s="21">
         <v>31.0</v>
       </c>
@@ -3508,61 +3571,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="65"/>
+      <c r="AD42" s="75"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="66">
+      <c r="A43" s="76">
         <v>32.0</v>
       </c>
-      <c r="B43" s="67">
+      <c r="B43" s="77">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66">
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76">
         <v>32.0</v>
       </c>
-      <c r="H43" s="67">
+      <c r="H43" s="77">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="66"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="68">
+      <c r="I43" s="76"/>
+      <c r="J43" s="76"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="78">
         <v>32.0</v>
       </c>
-      <c r="N43" s="69">
+      <c r="N43" s="79">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="66">
+      <c r="O43" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="76">
         <v>32.0</v>
       </c>
-      <c r="T43" s="67">
+      <c r="T43" s="77">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="66"/>
-      <c r="V43" s="66"/>
-      <c r="W43" s="66"/>
-      <c r="X43" s="66"/>
-      <c r="Y43" s="66">
+      <c r="U43" s="76"/>
+      <c r="V43" s="76"/>
+      <c r="W43" s="76"/>
+      <c r="X43" s="76"/>
+      <c r="Y43" s="76">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="67">
+      <c r="Z43" s="77">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="66"/>
-      <c r="AB43" s="66"/>
-      <c r="AC43" s="66"/>
-      <c r="AD43" s="73"/>
+      <c r="AA43" s="76"/>
+      <c r="AB43" s="76"/>
+      <c r="AC43" s="76"/>
+      <c r="AD43" s="83"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -4522,7 +4585,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="53">
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="W10:W11"/>
     <mergeCell ref="X10:X11"/>
@@ -4571,8 +4634,6 @@
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="O33:R33"/>
     <mergeCell ref="O34:R34"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -856,7 +856,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -996,7 +996,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2404,10 +2404,10 @@
       <c r="F26" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="23">
         <v>15.0</v>
       </c>
-      <c r="H26" s="58">
+      <c r="H26" s="24">
         <v>0.625</v>
       </c>
       <c r="I26" s="53" t="s">

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -595,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -751,9 +751,6 @@
     <xf borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -761,6 +758,9 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -809,6 +809,9 @@
     </xf>
     <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -856,7 +859,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -968,7 +971,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2143,13 +2146,13 @@
       <c r="C23" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G23" s="23">
@@ -2161,7 +2164,7 @@
       <c r="I23" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="54" t="s">
+      <c r="J23" s="53" t="s">
         <v>14</v>
       </c>
       <c r="K23" s="25" t="s">
@@ -2176,7 +2179,7 @@
       <c r="N23" s="45">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="55" t="s">
+      <c r="O23" s="54" t="s">
         <v>36</v>
       </c>
       <c r="P23" s="47" t="s">
@@ -2260,7 +2263,7 @@
       <c r="N24" s="36">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="56" t="s">
+      <c r="O24" s="55" t="s">
         <v>40</v>
       </c>
       <c r="P24" s="37" t="s">
@@ -2281,13 +2284,13 @@
       <c r="U24" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="V24" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="W24" s="53" t="s">
+      <c r="V24" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="W24" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="X24" s="53" t="s">
+      <c r="X24" s="56" t="s">
         <v>16</v>
       </c>
       <c r="Y24" s="38">
@@ -2308,16 +2311,16 @@
       <c r="B25" s="58">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G25" s="57">
@@ -2326,16 +2329,16 @@
       <c r="H25" s="58">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="53" t="s">
+      <c r="I25" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="53" t="s">
+      <c r="J25" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="53" t="s">
+      <c r="L25" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M25" s="23">
@@ -2344,16 +2347,16 @@
       <c r="N25" s="24">
         <v>0.6111111111111112</v>
       </c>
-      <c r="O25" s="53" t="s">
+      <c r="O25" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="P25" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="53" t="s">
+      <c r="P25" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="R25" s="53" t="s">
+      <c r="R25" s="56" t="s">
         <v>16</v>
       </c>
       <c r="S25" s="38">
@@ -2372,16 +2375,16 @@
       <c r="Z25" s="24">
         <v>0.6111111111111112</v>
       </c>
-      <c r="AA25" s="53" t="s">
+      <c r="AA25" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="AB25" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC25" s="53" t="s">
+      <c r="AB25" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC25" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AD25" s="53" t="s">
+      <c r="AD25" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2392,16 +2395,16 @@
       <c r="B26" s="24">
         <v>0.625</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="53" t="s">
+      <c r="F26" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="23">
@@ -2410,16 +2413,16 @@
       <c r="H26" s="24">
         <v>0.625</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="J26" s="53" t="s">
+      <c r="J26" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="K26" s="53" t="s">
+      <c r="K26" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="53" t="s">
+      <c r="L26" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M26" s="57">
@@ -2450,22 +2453,22 @@
       <c r="V26" s="38"/>
       <c r="W26" s="38"/>
       <c r="X26" s="38"/>
-      <c r="Y26" s="57">
+      <c r="Y26" s="23">
         <v>15.0</v>
       </c>
-      <c r="Z26" s="58">
+      <c r="Z26" s="24">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="53" t="s">
+      <c r="AA26" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="AB26" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC26" s="53" t="s">
+      <c r="AB26" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AD26" s="53" t="s">
+      <c r="AD26" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2476,16 +2479,16 @@
       <c r="B27" s="58">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="53" t="s">
+      <c r="D27" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="53" t="s">
+      <c r="F27" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="57">
@@ -2494,16 +2497,16 @@
       <c r="H27" s="58">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="53" t="s">
+      <c r="I27" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="J27" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="53" t="s">
+      <c r="J27" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="53" t="s">
+      <c r="L27" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M27" s="23">
@@ -2512,16 +2515,16 @@
       <c r="N27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="53" t="s">
+      <c r="O27" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="P27" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="53" t="s">
+      <c r="P27" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="53" t="s">
+      <c r="R27" s="56" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="44">
@@ -2540,16 +2543,16 @@
       <c r="Z27" s="58">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="53" t="s">
+      <c r="AA27" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="AB27" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC27" s="53" t="s">
+      <c r="AB27" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AD27" s="53" t="s">
+      <c r="AD27" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2563,13 +2566,13 @@
       <c r="C28" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="53" t="s">
+      <c r="D28" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="53" t="s">
+      <c r="F28" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="57">
@@ -2578,16 +2581,16 @@
       <c r="H28" s="58">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="53" t="s">
+      <c r="I28" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="53" t="s">
+      <c r="J28" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="53" t="s">
+      <c r="L28" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M28" s="57">
@@ -2596,16 +2599,16 @@
       <c r="N28" s="58">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="53" t="s">
+      <c r="O28" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="P28" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="53" t="s">
+      <c r="P28" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="53" t="s">
+      <c r="R28" s="56" t="s">
         <v>16</v>
       </c>
       <c r="S28" s="38">
@@ -2644,16 +2647,16 @@
       <c r="B29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="53" t="s">
+      <c r="D29" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="57">
@@ -2662,16 +2665,16 @@
       <c r="H29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="53" t="s">
+      <c r="I29" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="J29" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" s="53" t="s">
+      <c r="J29" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="L29" s="53" t="s">
+      <c r="L29" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M29" s="57">
@@ -2680,16 +2683,16 @@
       <c r="N29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="53" t="s">
+      <c r="O29" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="P29" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="53" t="s">
+      <c r="P29" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="R29" s="53" t="s">
+      <c r="R29" s="56" t="s">
         <v>16</v>
       </c>
       <c r="S29" s="38">
@@ -2708,16 +2711,16 @@
       <c r="Z29" s="58">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="53" t="s">
+      <c r="AA29" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="AB29" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC29" s="53" t="s">
+      <c r="AB29" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC29" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="AD29" s="53" t="s">
+      <c r="AD29" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2728,16 +2731,16 @@
       <c r="B30" s="58">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="53" t="s">
+      <c r="D30" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="57">
@@ -2746,16 +2749,16 @@
       <c r="H30" s="58">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="53" t="s">
+      <c r="I30" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="J30" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="53" t="s">
+      <c r="J30" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L30" s="53" t="s">
+      <c r="L30" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M30" s="57">
@@ -2800,16 +2803,16 @@
       <c r="Z30" s="58">
         <v>0.6805555555555556</v>
       </c>
-      <c r="AA30" s="53" t="s">
+      <c r="AA30" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="AB30" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC30" s="53" t="s">
+      <c r="AB30" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC30" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="AD30" s="53" t="s">
+      <c r="AD30" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2820,16 +2823,16 @@
       <c r="B31" s="58">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="53" t="s">
+      <c r="D31" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="53" t="s">
+      <c r="F31" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="57">
@@ -2838,16 +2841,16 @@
       <c r="H31" s="58">
         <v>0.6944444444444444</v>
       </c>
-      <c r="I31" s="53" t="s">
+      <c r="I31" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="53" t="s">
+      <c r="J31" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="53" t="s">
+      <c r="L31" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M31" s="57">
@@ -2862,10 +2865,10 @@
       <c r="P31" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="Q31" s="53" t="s">
+      <c r="Q31" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="R31" s="53" t="s">
+      <c r="R31" s="56" t="s">
         <v>16</v>
       </c>
       <c r="S31" s="38">
@@ -2884,16 +2887,16 @@
       <c r="Z31" s="58">
         <v>0.6944444444444444</v>
       </c>
-      <c r="AA31" s="53" t="s">
+      <c r="AA31" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="AB31" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC31" s="53" t="s">
+      <c r="AB31" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC31" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AD31" s="53" t="s">
+      <c r="AD31" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2904,16 +2907,16 @@
       <c r="B32" s="58">
         <v>0.7083333333333334</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="53" t="s">
+      <c r="D32" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G32" s="57">
@@ -2970,16 +2973,16 @@
       <c r="Z32" s="58">
         <v>0.7083333333333334</v>
       </c>
-      <c r="AA32" s="53" t="s">
+      <c r="AA32" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="AB32" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC32" s="53" t="s">
+      <c r="AB32" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC32" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="AD32" s="53" t="s">
+      <c r="AD32" s="56" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2990,16 +2993,16 @@
       <c r="B33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="53" t="s">
+      <c r="D33" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G33" s="57">
@@ -3008,16 +3011,16 @@
       <c r="H33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="I33" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33" s="53" t="s">
+      <c r="J33" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="53" t="s">
+      <c r="L33" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M33" s="35">
@@ -3038,16 +3041,16 @@
       <c r="T33" s="58">
         <v>0.7222222222222222</v>
       </c>
-      <c r="U33" s="53" t="s">
+      <c r="U33" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="V33" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="W33" s="53" t="s">
+      <c r="V33" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="W33" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="X33" s="53" t="s">
+      <c r="X33" s="56" t="s">
         <v>16</v>
       </c>
       <c r="Y33" s="21">
@@ -3070,28 +3073,36 @@
       <c r="B34" s="58">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="21">
+      <c r="F34" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="57">
         <v>7.0</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="58">
         <v>0.7361111111111112</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="I34" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" s="56" t="s">
+        <v>16</v>
+      </c>
       <c r="M34" s="35">
         <v>23.0</v>
       </c>
@@ -3152,7 +3163,7 @@
       <c r="N35" s="36">
         <v>0.75</v>
       </c>
-      <c r="O35" s="74" t="s">
+      <c r="O35" s="75" t="s">
         <v>79</v>
       </c>
       <c r="P35" s="70"/>
@@ -3186,16 +3197,16 @@
       <c r="B36" s="58">
         <v>0.7638888888888888</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="53" t="s">
+      <c r="D36" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="21">
@@ -3258,16 +3269,16 @@
       <c r="H37" s="58">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="53" t="s">
+      <c r="I37" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="J37" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="53" t="s">
+      <c r="J37" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L37" s="53" t="s">
+      <c r="L37" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M37" s="35">
@@ -3409,7 +3420,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="75"/>
+      <c r="AD39" s="76"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3463,7 +3474,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="75"/>
+      <c r="AD40" s="76"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3517,7 +3528,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="75"/>
+      <c r="AD41" s="76"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3571,61 +3582,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="75"/>
+      <c r="AD42" s="76"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="76">
+      <c r="A43" s="77">
         <v>32.0</v>
       </c>
-      <c r="B43" s="77">
+      <c r="B43" s="78">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76">
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77">
         <v>32.0</v>
       </c>
-      <c r="H43" s="77">
+      <c r="H43" s="78">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="76"/>
-      <c r="J43" s="76"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78">
+      <c r="I43" s="77"/>
+      <c r="J43" s="77"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="77"/>
+      <c r="M43" s="79">
         <v>32.0</v>
       </c>
-      <c r="N43" s="79">
+      <c r="N43" s="80">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="80" t="s">
+      <c r="O43" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="P43" s="81"/>
-      <c r="Q43" s="81"/>
-      <c r="R43" s="82"/>
-      <c r="S43" s="76">
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="77">
         <v>32.0</v>
       </c>
-      <c r="T43" s="77">
+      <c r="T43" s="78">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="76"/>
-      <c r="V43" s="76"/>
-      <c r="W43" s="76"/>
-      <c r="X43" s="76"/>
-      <c r="Y43" s="76">
+      <c r="U43" s="77"/>
+      <c r="V43" s="77"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="77"/>
+      <c r="Y43" s="77">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="77">
+      <c r="Z43" s="78">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="76"/>
-      <c r="AB43" s="76"/>
-      <c r="AC43" s="76"/>
-      <c r="AD43" s="83"/>
+      <c r="AA43" s="77"/>
+      <c r="AB43" s="77"/>
+      <c r="AC43" s="77"/>
+      <c r="AD43" s="84"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="81">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -859,7 +859,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -887,7 +887,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -915,7 +915,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -971,7 +971,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -999,7 +999,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2284,13 +2284,13 @@
       <c r="U24" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="V24" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="W24" s="56" t="s">
+      <c r="V24" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="W24" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="X24" s="56" t="s">
+      <c r="X24" s="25" t="s">
         <v>16</v>
       </c>
       <c r="Y24" s="38">
@@ -2305,40 +2305,40 @@
       <c r="AD24" s="38"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="57">
+      <c r="A25" s="35">
         <v>14.0</v>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="36">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="56" t="s">
+      <c r="D25" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="57">
+      <c r="F25" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="35">
         <v>14.0</v>
       </c>
-      <c r="H25" s="58">
+      <c r="H25" s="36">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="56" t="s">
+      <c r="I25" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="56" t="s">
+      <c r="J25" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="56" t="s">
+      <c r="L25" s="37" t="s">
         <v>16</v>
       </c>
       <c r="M25" s="23">
@@ -3137,16 +3137,24 @@
       <c r="AD34" s="21"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21">
+      <c r="A35" s="57">
         <v>24.0</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="58">
         <v>0.75</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
+      <c r="C35" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="56" t="s">
+        <v>16</v>
+      </c>
       <c r="G35" s="21">
         <v>24.0</v>
       </c>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="80">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>Aulia Hani</t>
-  </si>
-  <si>
-    <t>Windi</t>
   </si>
   <si>
     <t>Shabrina Amalia</t>
@@ -766,11 +763,11 @@
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -887,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -915,7 +912,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -943,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -971,7 +968,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2182,13 +2179,13 @@
       <c r="O23" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="37" t="s">
+      <c r="P23" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="37" t="s">
+      <c r="R23" s="25" t="s">
         <v>16</v>
       </c>
       <c r="S23" s="35">
@@ -2221,24 +2218,16 @@
       <c r="AD23" s="38"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="35">
+      <c r="A24" s="38">
         <v>13.0</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="39">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>16</v>
-      </c>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="35">
         <v>13.0</v>
       </c>
@@ -2246,7 +2235,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J24" s="37" t="s">
         <v>14</v>
@@ -2264,15 +2253,15 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="O24" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="P24" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="P24" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="Q24" s="37" t="s">
+      <c r="Q24" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="37" t="s">
+      <c r="R24" s="25" t="s">
         <v>16</v>
       </c>
       <c r="S24" s="23">
@@ -2282,7 +2271,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>14</v>
@@ -2312,7 +2301,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>25</v>
@@ -2330,7 +2319,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J25" s="37" t="s">
         <v>14</v>
@@ -2348,15 +2337,15 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="P25" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="R25" s="56" t="s">
+      <c r="R25" s="25" t="s">
         <v>16</v>
       </c>
       <c r="S25" s="38">
@@ -2376,15 +2365,15 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="AA25" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB25" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC25" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB25" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC25" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AD25" s="56" t="s">
+      <c r="AD25" s="25" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2395,11 +2384,11 @@
       <c r="B26" s="24">
         <v>0.625</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>46</v>
-      </c>
-      <c r="D26" s="56" t="s">
-        <v>47</v>
       </c>
       <c r="E26" s="56" t="s">
         <v>20</v>
@@ -2413,11 +2402,11 @@
       <c r="H26" s="24">
         <v>0.625</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="56" t="s">
         <v>48</v>
-      </c>
-      <c r="J26" s="56" t="s">
-        <v>49</v>
       </c>
       <c r="K26" s="56" t="s">
         <v>20</v>
@@ -2425,14 +2414,14 @@
       <c r="L26" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="M26" s="57">
+      <c r="M26" s="23">
         <v>15.0</v>
       </c>
-      <c r="N26" s="58">
+      <c r="N26" s="24">
         <v>0.625</v>
       </c>
-      <c r="O26" s="57" t="s">
-        <v>50</v>
+      <c r="O26" s="23" t="s">
+        <v>49</v>
       </c>
       <c r="P26" s="57" t="s">
         <v>14</v>
@@ -2440,7 +2429,7 @@
       <c r="Q26" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="59" t="s">
+      <c r="R26" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S26" s="38">
@@ -2459,8 +2448,8 @@
       <c r="Z26" s="24">
         <v>0.625</v>
       </c>
-      <c r="AA26" s="56" t="s">
-        <v>51</v>
+      <c r="AA26" s="25" t="s">
+        <v>50</v>
       </c>
       <c r="AB26" s="56" t="s">
         <v>14</v>
@@ -2476,11 +2465,11 @@
       <c r="A27" s="57">
         <v>16.0</v>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="59">
         <v>0.6388888888888888</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="56" t="s">
         <v>14</v>
@@ -2494,11 +2483,11 @@
       <c r="G27" s="57">
         <v>16.0</v>
       </c>
-      <c r="H27" s="58">
+      <c r="H27" s="59">
         <v>0.6388888888888888</v>
       </c>
       <c r="I27" s="56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J27" s="56" t="s">
         <v>14</v>
@@ -2516,7 +2505,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="O27" s="56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P27" s="56" t="s">
         <v>14</v>
@@ -2540,11 +2529,11 @@
       <c r="Y27" s="57">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="58">
+      <c r="Z27" s="59">
         <v>0.6388888888888888</v>
       </c>
       <c r="AA27" s="56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB27" s="56" t="s">
         <v>14</v>
@@ -2560,11 +2549,11 @@
       <c r="A28" s="57">
         <v>17.0</v>
       </c>
-      <c r="B28" s="58">
+      <c r="B28" s="59">
         <v>0.6527777777777778</v>
       </c>
       <c r="C28" s="62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="56" t="s">
         <v>14</v>
@@ -2578,11 +2567,11 @@
       <c r="G28" s="57">
         <v>17.0</v>
       </c>
-      <c r="H28" s="58">
+      <c r="H28" s="59">
         <v>0.6527777777777778</v>
       </c>
       <c r="I28" s="56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J28" s="56" t="s">
         <v>25</v>
@@ -2596,11 +2585,11 @@
       <c r="M28" s="57">
         <v>17.0</v>
       </c>
-      <c r="N28" s="58">
+      <c r="N28" s="59">
         <v>0.6527777777777778</v>
       </c>
       <c r="O28" s="56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P28" s="56" t="s">
         <v>14</v>
@@ -2624,11 +2613,11 @@
       <c r="Y28" s="57">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="58">
+      <c r="Z28" s="59">
         <v>0.6527777777777778</v>
       </c>
       <c r="AA28" s="63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AB28" s="63" t="s">
         <v>14</v>
@@ -2644,11 +2633,11 @@
       <c r="A29" s="57">
         <v>18.0</v>
       </c>
-      <c r="B29" s="58">
+      <c r="B29" s="59">
         <v>0.6666666666666666</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29" s="56" t="s">
         <v>14</v>
@@ -2662,11 +2651,11 @@
       <c r="G29" s="57">
         <v>18.0</v>
       </c>
-      <c r="H29" s="58">
+      <c r="H29" s="59">
         <v>0.6666666666666666</v>
       </c>
       <c r="I29" s="56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J29" s="56" t="s">
         <v>14</v>
@@ -2680,11 +2669,11 @@
       <c r="M29" s="57">
         <v>18.0</v>
       </c>
-      <c r="N29" s="58">
+      <c r="N29" s="59">
         <v>0.6666666666666666</v>
       </c>
       <c r="O29" s="56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P29" s="56" t="s">
         <v>14</v>
@@ -2708,11 +2697,11 @@
       <c r="Y29" s="57">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="58">
+      <c r="Z29" s="59">
         <v>0.6666666666666666</v>
       </c>
       <c r="AA29" s="56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB29" s="56" t="s">
         <v>14</v>
@@ -2728,11 +2717,11 @@
       <c r="A30" s="57">
         <v>19.0</v>
       </c>
-      <c r="B30" s="58">
+      <c r="B30" s="59">
         <v>0.6805555555555556</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" s="56" t="s">
         <v>14</v>
@@ -2746,11 +2735,11 @@
       <c r="G30" s="57">
         <v>19.0</v>
       </c>
-      <c r="H30" s="58">
+      <c r="H30" s="59">
         <v>0.6805555555555556</v>
       </c>
       <c r="I30" s="56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J30" s="56" t="s">
         <v>14</v>
@@ -2764,7 +2753,7 @@
       <c r="M30" s="57">
         <v>19.0</v>
       </c>
-      <c r="N30" s="58">
+      <c r="N30" s="59">
         <v>0.6805555555555556</v>
       </c>
       <c r="O30" s="65" t="s">
@@ -2786,7 +2775,7 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="U30" s="63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V30" s="63" t="s">
         <v>14</v>
@@ -2800,11 +2789,11 @@
       <c r="Y30" s="57">
         <v>19.0</v>
       </c>
-      <c r="Z30" s="58">
+      <c r="Z30" s="59">
         <v>0.6805555555555556</v>
       </c>
       <c r="AA30" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB30" s="56" t="s">
         <v>14</v>
@@ -2820,11 +2809,11 @@
       <c r="A31" s="57">
         <v>20.0</v>
       </c>
-      <c r="B31" s="58">
+      <c r="B31" s="59">
         <v>0.6944444444444444</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" s="56" t="s">
         <v>14</v>
@@ -2838,11 +2827,11 @@
       <c r="G31" s="57">
         <v>20.0</v>
       </c>
-      <c r="H31" s="58">
+      <c r="H31" s="59">
         <v>0.6944444444444444</v>
       </c>
       <c r="I31" s="56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J31" s="56" t="s">
         <v>14</v>
@@ -2856,10 +2845,10 @@
       <c r="M31" s="57">
         <v>20.0</v>
       </c>
-      <c r="N31" s="58">
+      <c r="N31" s="59">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="59" t="s">
+      <c r="O31" s="58" t="s">
         <v>28</v>
       </c>
       <c r="P31" s="68" t="s">
@@ -2884,11 +2873,11 @@
       <c r="Y31" s="57">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="58">
+      <c r="Z31" s="59">
         <v>0.6944444444444444</v>
       </c>
       <c r="AA31" s="56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB31" s="56" t="s">
         <v>14</v>
@@ -2904,11 +2893,11 @@
       <c r="A32" s="57">
         <v>21.0</v>
       </c>
-      <c r="B32" s="58">
+      <c r="B32" s="59">
         <v>0.7083333333333334</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" s="56" t="s">
         <v>14</v>
@@ -2922,11 +2911,11 @@
       <c r="G32" s="57">
         <v>21.0</v>
       </c>
-      <c r="H32" s="58">
+      <c r="H32" s="59">
         <v>0.7083333333333334</v>
       </c>
       <c r="I32" s="63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J32" s="63" t="s">
         <v>33</v>
@@ -2944,7 +2933,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="O32" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P32" s="70"/>
       <c r="Q32" s="70"/>
@@ -2952,11 +2941,11 @@
       <c r="S32" s="57">
         <v>21.0</v>
       </c>
-      <c r="T32" s="58">
+      <c r="T32" s="59">
         <v>0.7083333333333334</v>
       </c>
       <c r="U32" s="72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V32" s="72" t="s">
         <v>25</v>
@@ -2970,7 +2959,7 @@
       <c r="Y32" s="57">
         <v>21.0</v>
       </c>
-      <c r="Z32" s="58">
+      <c r="Z32" s="59">
         <v>0.7083333333333334</v>
       </c>
       <c r="AA32" s="56" t="s">
@@ -2990,11 +2979,11 @@
       <c r="A33" s="57">
         <v>22.0</v>
       </c>
-      <c r="B33" s="58">
+      <c r="B33" s="59">
         <v>0.7222222222222222</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="56" t="s">
         <v>14</v>
@@ -3008,11 +2997,11 @@
       <c r="G33" s="57">
         <v>22.0</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="59">
         <v>0.7222222222222222</v>
       </c>
       <c r="I33" s="56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J33" s="56" t="s">
         <v>14</v>
@@ -3030,7 +3019,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="O33" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P33" s="70"/>
       <c r="Q33" s="70"/>
@@ -3038,7 +3027,7 @@
       <c r="S33" s="57">
         <v>22.0</v>
       </c>
-      <c r="T33" s="58">
+      <c r="T33" s="59">
         <v>0.7222222222222222</v>
       </c>
       <c r="U33" s="56" t="s">
@@ -3060,7 +3049,7 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="AA33" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
@@ -3070,14 +3059,14 @@
       <c r="A34" s="57">
         <v>23.0</v>
       </c>
-      <c r="B34" s="58">
+      <c r="B34" s="59">
         <v>0.7361111111111112</v>
       </c>
       <c r="C34" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="56" t="s">
         <v>77</v>
-      </c>
-      <c r="D34" s="56" t="s">
-        <v>78</v>
       </c>
       <c r="E34" s="56" t="s">
         <v>15</v>
@@ -3088,11 +3077,11 @@
       <c r="G34" s="57">
         <v>7.0</v>
       </c>
-      <c r="H34" s="58">
+      <c r="H34" s="59">
         <v>0.7361111111111112</v>
       </c>
       <c r="I34" s="74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J34" s="56" t="s">
         <v>25</v>
@@ -3110,7 +3099,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="O34" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P34" s="70"/>
       <c r="Q34" s="70"/>
@@ -3140,11 +3129,11 @@
       <c r="A35" s="57">
         <v>24.0</v>
       </c>
-      <c r="B35" s="58">
+      <c r="B35" s="59">
         <v>0.75</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="56" t="s">
         <v>25</v>
@@ -3155,16 +3144,24 @@
       <c r="F35" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="57">
         <v>24.0</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="59">
         <v>0.75</v>
       </c>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="I35" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="56" t="s">
+        <v>16</v>
+      </c>
       <c r="M35" s="35">
         <v>24.0</v>
       </c>
@@ -3172,7 +3169,7 @@
         <v>0.75</v>
       </c>
       <c r="O35" s="75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P35" s="70"/>
       <c r="Q35" s="70"/>
@@ -3202,7 +3199,7 @@
       <c r="A36" s="57">
         <v>25.0</v>
       </c>
-      <c r="B36" s="58">
+      <c r="B36" s="59">
         <v>0.7638888888888888</v>
       </c>
       <c r="C36" s="56" t="s">
@@ -3234,7 +3231,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="O36" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P36" s="70"/>
       <c r="Q36" s="70"/>
@@ -3274,11 +3271,11 @@
       <c r="G37" s="57">
         <v>26.0</v>
       </c>
-      <c r="H37" s="58">
+      <c r="H37" s="59">
         <v>0.7777777777777778</v>
       </c>
       <c r="I37" s="56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J37" s="56" t="s">
         <v>14</v>
@@ -3296,7 +3293,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O37" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P37" s="70"/>
       <c r="Q37" s="70"/>
@@ -3350,7 +3347,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="O38" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P38" s="70"/>
       <c r="Q38" s="70"/>
@@ -3404,7 +3401,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="O39" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P39" s="70"/>
       <c r="Q39" s="70"/>
@@ -3458,7 +3455,7 @@
         <v>0.8194444444444444</v>
       </c>
       <c r="O40" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P40" s="70"/>
       <c r="Q40" s="70"/>
@@ -3512,7 +3509,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="O41" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P41" s="70"/>
       <c r="Q41" s="70"/>
@@ -3566,7 +3563,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="O42" s="73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P42" s="70"/>
       <c r="Q42" s="70"/>
@@ -3620,7 +3617,7 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="O43" s="81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P43" s="82"/>
       <c r="Q43" s="82"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -884,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -912,7 +912,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -968,7 +968,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -996,7 +996,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2405,13 +2405,13 @@
       <c r="I26" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="J26" s="56" t="s">
+      <c r="J26" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="K26" s="56" t="s">
+      <c r="K26" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="56" t="s">
+      <c r="L26" s="25" t="s">
         <v>16</v>
       </c>
       <c r="M26" s="23">
@@ -2546,10 +2546,10 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="57">
+      <c r="A28" s="23">
         <v>17.0</v>
       </c>
-      <c r="B28" s="59">
+      <c r="B28" s="24">
         <v>0.6527777777777778</v>
       </c>
       <c r="C28" s="62" t="s">

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="79">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -166,7 +166,7 @@
     <t>Graduatio prem</t>
   </si>
   <si>
-    <t>Afifah</t>
+    <t>Fafif</t>
   </si>
   <si>
     <t>Zaidan Ariefyandi</t>
@@ -193,58 +193,55 @@
     <t>Niko</t>
   </si>
   <si>
+    <t>Karlina</t>
+  </si>
+  <si>
+    <t>Nabilla</t>
+  </si>
+  <si>
+    <t>Tiffani Agil</t>
+  </si>
+  <si>
+    <t>Nina Dwi Suryani</t>
+  </si>
+  <si>
+    <t>Mahendra Putra Wardhana</t>
+  </si>
+  <si>
+    <t>Afita Khoerunnisa</t>
+  </si>
+  <si>
+    <t>Dita</t>
+  </si>
+  <si>
+    <t>Sifa</t>
+  </si>
+  <si>
+    <t>Hanifa</t>
+  </si>
+  <si>
+    <t>Akhmad binangun</t>
+  </si>
+  <si>
+    <t>lala</t>
+  </si>
+  <si>
+    <t>sabrina</t>
+  </si>
+  <si>
+    <t>Claresta</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>Desti Ika c</t>
+  </si>
+  <si>
+    <t>Utia</t>
+  </si>
+  <si>
     <t>Wahyu Setianingsih</t>
-  </si>
-  <si>
-    <t>Karlina</t>
-  </si>
-  <si>
-    <t>Nabilla</t>
-  </si>
-  <si>
-    <t>Tiffani Agil</t>
-  </si>
-  <si>
-    <t>Nina Dwi Suryani</t>
-  </si>
-  <si>
-    <t>Mahendra Putra Wardhana</t>
-  </si>
-  <si>
-    <t>Afita Khoerunnisa</t>
-  </si>
-  <si>
-    <t>Dita</t>
-  </si>
-  <si>
-    <t>Sifa</t>
-  </si>
-  <si>
-    <t>Hanifa</t>
-  </si>
-  <si>
-    <t>Akhmad binangun</t>
-  </si>
-  <si>
-    <t>lala</t>
-  </si>
-  <si>
-    <t>sabrina</t>
-  </si>
-  <si>
-    <t>Claresta</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>Desti Ika c</t>
-  </si>
-  <si>
-    <t>Utia</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Ade Evan</t>
@@ -592,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -760,38 +757,38 @@
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="9" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -806,6 +803,9 @@
     </xf>
     <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -856,7 +856,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -884,7 +884,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -912,7 +912,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +940,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -968,7 +968,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -996,7 +996,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2387,13 +2387,13 @@
       <c r="C26" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="56" t="s">
+      <c r="E26" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="56" t="s">
+      <c r="F26" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="23">
@@ -2420,16 +2420,16 @@
       <c r="N26" s="24">
         <v>0.625</v>
       </c>
-      <c r="O26" s="23" t="s">
+      <c r="O26" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="P26" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="57" t="s">
+      <c r="P26" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="R26" s="58" t="s">
+      <c r="R26" s="51" t="s">
         <v>16</v>
       </c>
       <c r="S26" s="38">
@@ -2451,24 +2451,24 @@
       <c r="AA26" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="AB26" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC26" s="56" t="s">
+      <c r="AB26" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC26" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AD26" s="56" t="s">
+      <c r="AD26" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="57">
+      <c r="A27" s="23">
         <v>16.0</v>
       </c>
-      <c r="B27" s="59">
+      <c r="B27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="56" t="s">
@@ -2480,13 +2480,13 @@
       <c r="F27" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="57">
+      <c r="G27" s="23">
         <v>16.0</v>
       </c>
-      <c r="H27" s="59">
+      <c r="H27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="I27" s="56" t="s">
+      <c r="I27" s="25" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="56" t="s">
@@ -2504,44 +2504,44 @@
       <c r="N27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="O27" s="56" t="s">
+      <c r="O27" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="P27" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="56" t="s">
+      <c r="P27" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="56" t="s">
+      <c r="R27" s="25" t="s">
         <v>16</v>
       </c>
       <c r="S27" s="44">
         <v>16.0</v>
       </c>
-      <c r="T27" s="60">
+      <c r="T27" s="57">
         <v>0.6388888888888888</v>
       </c>
       <c r="U27" s="44"/>
       <c r="V27" s="44"/>
       <c r="W27" s="44"/>
-      <c r="X27" s="61"/>
-      <c r="Y27" s="57">
+      <c r="X27" s="58"/>
+      <c r="Y27" s="35">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="59">
+      <c r="Z27" s="36">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="56" t="s">
+      <c r="AA27" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="AB27" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC27" s="56" t="s">
+      <c r="AB27" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="AD27" s="56" t="s">
+      <c r="AD27" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       <c r="B28" s="24">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="59" t="s">
         <v>55</v>
       </c>
       <c r="D28" s="56" t="s">
@@ -2564,31 +2564,31 @@
       <c r="F28" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="57">
+      <c r="G28" s="35">
         <v>17.0</v>
       </c>
-      <c r="H28" s="59">
+      <c r="H28" s="36">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="56" t="s">
+      <c r="I28" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="J28" s="56" t="s">
+      <c r="J28" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="56" t="s">
+      <c r="K28" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="57">
+      <c r="L28" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="23">
         <v>17.0</v>
       </c>
-      <c r="N28" s="59">
+      <c r="N28" s="24">
         <v>0.6527777777777778</v>
       </c>
-      <c r="O28" s="56" t="s">
+      <c r="O28" s="25" t="s">
         <v>57</v>
       </c>
       <c r="P28" s="56" t="s">
@@ -2610,34 +2610,26 @@
       <c r="V28" s="38"/>
       <c r="W28" s="38"/>
       <c r="X28" s="38"/>
-      <c r="Y28" s="57">
+      <c r="Y28" s="38">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="59">
+      <c r="Z28" s="39">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB28" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD28" s="64" t="s">
-        <v>16</v>
-      </c>
+      <c r="AA28" s="44"/>
+      <c r="AB28" s="44"/>
+      <c r="AC28" s="44"/>
+      <c r="AD28" s="60"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="57">
+      <c r="A29" s="61">
         <v>18.0</v>
       </c>
-      <c r="B29" s="59">
+      <c r="B29" s="62">
         <v>0.6666666666666666</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" s="56" t="s">
         <v>14</v>
@@ -2648,14 +2640,14 @@
       <c r="F29" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="57">
+      <c r="G29" s="61">
         <v>18.0</v>
       </c>
-      <c r="H29" s="59">
+      <c r="H29" s="62">
         <v>0.6666666666666666</v>
       </c>
       <c r="I29" s="56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J29" s="56" t="s">
         <v>14</v>
@@ -2666,14 +2658,14 @@
       <c r="L29" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="M29" s="57">
+      <c r="M29" s="61">
         <v>18.0</v>
       </c>
-      <c r="N29" s="59">
+      <c r="N29" s="62">
         <v>0.6666666666666666</v>
       </c>
       <c r="O29" s="56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P29" s="56" t="s">
         <v>14</v>
@@ -2694,14 +2686,14 @@
       <c r="V29" s="38"/>
       <c r="W29" s="38"/>
       <c r="X29" s="38"/>
-      <c r="Y29" s="57">
+      <c r="Y29" s="23">
         <v>18.0</v>
       </c>
-      <c r="Z29" s="59">
+      <c r="Z29" s="24">
         <v>0.6666666666666666</v>
       </c>
       <c r="AA29" s="56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AB29" s="56" t="s">
         <v>14</v>
@@ -2714,14 +2706,14 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="57">
+      <c r="A30" s="61">
         <v>19.0</v>
       </c>
-      <c r="B30" s="59">
+      <c r="B30" s="62">
         <v>0.6805555555555556</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="56" t="s">
         <v>14</v>
@@ -2732,14 +2724,14 @@
       <c r="F30" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="57">
+      <c r="G30" s="23">
         <v>19.0</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="24">
         <v>0.6805555555555556</v>
       </c>
       <c r="I30" s="56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J30" s="56" t="s">
         <v>14</v>
@@ -2750,50 +2742,50 @@
       <c r="L30" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="57">
+      <c r="M30" s="61">
         <v>19.0</v>
       </c>
-      <c r="N30" s="59">
+      <c r="N30" s="62">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="65" t="s">
+      <c r="O30" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="66" t="s">
+      <c r="P30" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q30" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="S30" s="63">
+      <c r="R30" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="S30" s="65">
         <v>19.0</v>
       </c>
-      <c r="T30" s="67">
+      <c r="T30" s="66">
         <v>0.6805555555555556</v>
       </c>
-      <c r="U30" s="63" t="s">
+      <c r="U30" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="V30" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="W30" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="X30" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y30" s="61">
+        <v>19.0</v>
+      </c>
+      <c r="Z30" s="62">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AA30" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="V30" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="W30" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="X30" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y30" s="57">
-        <v>19.0</v>
-      </c>
-      <c r="Z30" s="59">
-        <v>0.6805555555555556</v>
-      </c>
-      <c r="AA30" s="56" t="s">
-        <v>66</v>
       </c>
       <c r="AB30" s="56" t="s">
         <v>14</v>
@@ -2806,14 +2798,14 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="57">
+      <c r="A31" s="61">
         <v>20.0</v>
       </c>
-      <c r="B31" s="59">
+      <c r="B31" s="62">
         <v>0.6944444444444444</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D31" s="56" t="s">
         <v>14</v>
@@ -2824,14 +2816,14 @@
       <c r="F31" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="57">
+      <c r="G31" s="23">
         <v>20.0</v>
       </c>
-      <c r="H31" s="59">
+      <c r="H31" s="24">
         <v>0.6944444444444444</v>
       </c>
       <c r="I31" s="56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J31" s="56" t="s">
         <v>14</v>
@@ -2842,13 +2834,13 @@
       <c r="L31" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="M31" s="57">
+      <c r="M31" s="61">
         <v>20.0</v>
       </c>
-      <c r="N31" s="59">
+      <c r="N31" s="62">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="58" t="s">
+      <c r="O31" s="67" t="s">
         <v>28</v>
       </c>
       <c r="P31" s="68" t="s">
@@ -2870,14 +2862,14 @@
       <c r="V31" s="38"/>
       <c r="W31" s="38"/>
       <c r="X31" s="38"/>
-      <c r="Y31" s="57">
+      <c r="Y31" s="61">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="59">
+      <c r="Z31" s="62">
         <v>0.6944444444444444</v>
       </c>
       <c r="AA31" s="56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB31" s="56" t="s">
         <v>14</v>
@@ -2890,14 +2882,14 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="57">
+      <c r="A32" s="61">
         <v>21.0</v>
       </c>
-      <c r="B32" s="59">
+      <c r="B32" s="62">
         <v>0.7083333333333334</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D32" s="56" t="s">
         <v>14</v>
@@ -2908,22 +2900,22 @@
       <c r="F32" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="57">
+      <c r="G32" s="61">
         <v>21.0</v>
       </c>
-      <c r="H32" s="59">
+      <c r="H32" s="62">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="J32" s="63" t="s">
+      <c r="I32" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="J32" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="63" t="s">
+      <c r="K32" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="63" t="s">
+      <c r="L32" s="65" t="s">
         <v>16</v>
       </c>
       <c r="M32" s="38">
@@ -2933,19 +2925,19 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="O32" s="69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P32" s="70"/>
       <c r="Q32" s="70"/>
       <c r="R32" s="71"/>
-      <c r="S32" s="57">
+      <c r="S32" s="61">
         <v>21.0</v>
       </c>
-      <c r="T32" s="59">
+      <c r="T32" s="62">
         <v>0.7083333333333334</v>
       </c>
       <c r="U32" s="72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V32" s="72" t="s">
         <v>25</v>
@@ -2956,10 +2948,10 @@
       <c r="X32" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="Y32" s="57">
+      <c r="Y32" s="61">
         <v>21.0</v>
       </c>
-      <c r="Z32" s="59">
+      <c r="Z32" s="62">
         <v>0.7083333333333334</v>
       </c>
       <c r="AA32" s="56" t="s">
@@ -2976,14 +2968,14 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="57">
+      <c r="A33" s="61">
         <v>22.0</v>
       </c>
-      <c r="B33" s="59">
+      <c r="B33" s="62">
         <v>0.7222222222222222</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="56" t="s">
         <v>14</v>
@@ -2994,10 +2986,10 @@
       <c r="F33" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="57">
+      <c r="G33" s="61">
         <v>22.0</v>
       </c>
-      <c r="H33" s="59">
+      <c r="H33" s="62">
         <v>0.7222222222222222</v>
       </c>
       <c r="I33" s="56" t="s">
@@ -3019,15 +3011,15 @@
         <v>0.7222222222222222</v>
       </c>
       <c r="O33" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P33" s="70"/>
       <c r="Q33" s="70"/>
       <c r="R33" s="71"/>
-      <c r="S33" s="57">
+      <c r="S33" s="61">
         <v>22.0</v>
       </c>
-      <c r="T33" s="59">
+      <c r="T33" s="62">
         <v>0.7222222222222222</v>
       </c>
       <c r="U33" s="56" t="s">
@@ -3042,31 +3034,37 @@
       <c r="X33" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="Y33" s="21">
+      <c r="Y33" s="61">
         <v>22.0</v>
       </c>
-      <c r="Z33" s="22">
+      <c r="Z33" s="62">
         <v>0.7222222222222222</v>
       </c>
-      <c r="AA33" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
+      <c r="AA33" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB33" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC33" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD33" s="74" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="57">
+      <c r="A34" s="61">
         <v>23.0</v>
       </c>
-      <c r="B34" s="59">
+      <c r="B34" s="62">
         <v>0.7361111111111112</v>
       </c>
       <c r="C34" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="56" t="s">
         <v>76</v>
-      </c>
-      <c r="D34" s="56" t="s">
-        <v>77</v>
       </c>
       <c r="E34" s="56" t="s">
         <v>15</v>
@@ -3074,13 +3072,13 @@
       <c r="F34" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="57">
+      <c r="G34" s="61">
         <v>7.0</v>
       </c>
-      <c r="H34" s="59">
+      <c r="H34" s="62">
         <v>0.7361111111111112</v>
       </c>
-      <c r="I34" s="74" t="s">
+      <c r="I34" s="75" t="s">
         <v>39</v>
       </c>
       <c r="J34" s="56" t="s">
@@ -3099,7 +3097,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="O34" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P34" s="70"/>
       <c r="Q34" s="70"/>
@@ -3114,22 +3112,30 @@
       <c r="V34" s="21"/>
       <c r="W34" s="21"/>
       <c r="X34" s="21"/>
-      <c r="Y34" s="21">
+      <c r="Y34" s="61">
         <v>23.0</v>
       </c>
-      <c r="Z34" s="22">
+      <c r="Z34" s="62">
         <v>0.7361111111111112</v>
       </c>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="21"/>
-      <c r="AD34" s="21"/>
+      <c r="AA34" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB34" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC34" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD34" s="56" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="57">
+      <c r="A35" s="61">
         <v>24.0</v>
       </c>
-      <c r="B35" s="59">
+      <c r="B35" s="62">
         <v>0.75</v>
       </c>
       <c r="C35" s="56" t="s">
@@ -3144,10 +3150,10 @@
       <c r="F35" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="57">
+      <c r="G35" s="61">
         <v>24.0</v>
       </c>
-      <c r="H35" s="59">
+      <c r="H35" s="62">
         <v>0.75</v>
       </c>
       <c r="I35" s="56" t="s">
@@ -3168,8 +3174,8 @@
       <c r="N35" s="36">
         <v>0.75</v>
       </c>
-      <c r="O35" s="75" t="s">
-        <v>78</v>
+      <c r="O35" s="76" t="s">
+        <v>77</v>
       </c>
       <c r="P35" s="70"/>
       <c r="Q35" s="70"/>
@@ -3196,10 +3202,10 @@
       <c r="AD35" s="21"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="57">
+      <c r="A36" s="61">
         <v>25.0</v>
       </c>
-      <c r="B36" s="59">
+      <c r="B36" s="62">
         <v>0.7638888888888888</v>
       </c>
       <c r="C36" s="56" t="s">
@@ -3231,7 +3237,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="O36" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P36" s="70"/>
       <c r="Q36" s="70"/>
@@ -3268,14 +3274,14 @@
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="57">
+      <c r="G37" s="61">
         <v>26.0</v>
       </c>
-      <c r="H37" s="59">
+      <c r="H37" s="62">
         <v>0.7777777777777778</v>
       </c>
       <c r="I37" s="56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J37" s="56" t="s">
         <v>14</v>
@@ -3293,7 +3299,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O37" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P37" s="70"/>
       <c r="Q37" s="70"/>
@@ -3347,7 +3353,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="O38" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P38" s="70"/>
       <c r="Q38" s="70"/>
@@ -3401,7 +3407,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="O39" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P39" s="70"/>
       <c r="Q39" s="70"/>
@@ -3425,7 +3431,7 @@
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
       <c r="AC39" s="21"/>
-      <c r="AD39" s="76"/>
+      <c r="AD39" s="77"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3455,7 +3461,7 @@
         <v>0.8194444444444444</v>
       </c>
       <c r="O40" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P40" s="70"/>
       <c r="Q40" s="70"/>
@@ -3479,7 +3485,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="76"/>
+      <c r="AD40" s="77"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3509,7 +3515,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="O41" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P41" s="70"/>
       <c r="Q41" s="70"/>
@@ -3533,7 +3539,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="76"/>
+      <c r="AD41" s="77"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3563,7 +3569,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="O42" s="73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P42" s="70"/>
       <c r="Q42" s="70"/>
@@ -3587,61 +3593,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="76"/>
+      <c r="AD42" s="77"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="77">
+      <c r="A43" s="78">
         <v>32.0</v>
       </c>
-      <c r="B43" s="78">
+      <c r="B43" s="79">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77">
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78">
         <v>32.0</v>
       </c>
-      <c r="H43" s="78">
+      <c r="H43" s="79">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="77"/>
-      <c r="J43" s="77"/>
-      <c r="K43" s="77"/>
-      <c r="L43" s="77"/>
-      <c r="M43" s="79">
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="80">
         <v>32.0</v>
       </c>
-      <c r="N43" s="80">
+      <c r="N43" s="81">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="81" t="s">
-        <v>72</v>
-      </c>
-      <c r="P43" s="82"/>
-      <c r="Q43" s="82"/>
-      <c r="R43" s="83"/>
-      <c r="S43" s="77">
+      <c r="O43" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="P43" s="83"/>
+      <c r="Q43" s="83"/>
+      <c r="R43" s="84"/>
+      <c r="S43" s="78">
         <v>32.0</v>
       </c>
-      <c r="T43" s="78">
+      <c r="T43" s="79">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="77"/>
-      <c r="V43" s="77"/>
-      <c r="W43" s="77"/>
-      <c r="X43" s="77"/>
-      <c r="Y43" s="77">
+      <c r="U43" s="78"/>
+      <c r="V43" s="78"/>
+      <c r="W43" s="78"/>
+      <c r="X43" s="78"/>
+      <c r="Y43" s="78">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="78">
+      <c r="Z43" s="79">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="77"/>
-      <c r="AB43" s="77"/>
-      <c r="AC43" s="77"/>
-      <c r="AD43" s="84"/>
+      <c r="AA43" s="78"/>
+      <c r="AB43" s="78"/>
+      <c r="AC43" s="78"/>
+      <c r="AD43" s="85"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="78">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -82,64 +82,160 @@
     <t>AL</t>
   </si>
   <si>
+    <t xml:space="preserve"> Tuti Priyani</t>
+  </si>
+  <si>
+    <t>Wisnu Pamungkas</t>
+  </si>
+  <si>
+    <t>Graduation Premium</t>
+  </si>
+  <si>
+    <t>Audi nisa</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Qotrunnada Maulidia</t>
+  </si>
+  <si>
+    <t>Nasywaa</t>
+  </si>
+  <si>
+    <t>Mufti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduation </t>
+  </si>
+  <si>
+    <t>Ilut</t>
+  </si>
+  <si>
+    <t>nabila hasna</t>
+  </si>
+  <si>
+    <t>Logi</t>
+  </si>
+  <si>
+    <t>Wafi Wafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> oktriana</t>
+  </si>
+  <si>
+    <t>N. A. Salsabila</t>
+  </si>
+  <si>
+    <t>Rahayu Purnama</t>
+  </si>
+  <si>
+    <t>Graduatiom</t>
+  </si>
+  <si>
+    <t>Gandring Guste Puand</t>
+  </si>
+  <si>
+    <t>Graduatio prem</t>
+  </si>
+  <si>
+    <t>Fafif</t>
+  </si>
+  <si>
+    <t>Zaidan Ariefyandi</t>
+  </si>
+  <si>
+    <t>Sandlyra Anastasya</t>
+  </si>
+  <si>
+    <t>helmi</t>
+  </si>
+  <si>
+    <t>Reynaldo</t>
+  </si>
+  <si>
+    <t>Amelia Nur</t>
+  </si>
+  <si>
+    <t>Niko</t>
+  </si>
+  <si>
+    <t>Nabilla</t>
+  </si>
+  <si>
+    <t>Tiffani Agil</t>
+  </si>
+  <si>
+    <t>Nina Dwi Suryani</t>
+  </si>
+  <si>
+    <t>Mahendra Putra Wardhana</t>
+  </si>
+  <si>
+    <t>Afita Khoerunnisa</t>
+  </si>
+  <si>
+    <t>cantika</t>
+  </si>
+  <si>
+    <t>Dita</t>
+  </si>
+  <si>
+    <t>Hanifa</t>
+  </si>
+  <si>
+    <t>Akhmad binangun</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fadila</t>
+  </si>
+  <si>
+    <t>lala</t>
+  </si>
+  <si>
+    <t>sabrina</t>
+  </si>
+  <si>
+    <t>Claresta</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dwi</t>
+  </si>
+  <si>
     <t>Afrindanti</t>
   </si>
   <si>
-    <t>cantika</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tuti Priyani</t>
-  </si>
-  <si>
-    <t>Wisnu Pamungkas</t>
-  </si>
-  <si>
-    <t>Graduation Premium</t>
-  </si>
-  <si>
-    <t>Audi nisa</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fadila</t>
-  </si>
-  <si>
-    <t>Rani</t>
-  </si>
-  <si>
-    <t>Qotrunnada Maulidia</t>
-  </si>
-  <si>
-    <t>Nasywaa</t>
-  </si>
-  <si>
-    <t>Mufti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduation </t>
-  </si>
-  <si>
-    <t>Ilut</t>
-  </si>
-  <si>
-    <t>nabila hasna</t>
-  </si>
-  <si>
-    <t>Logi</t>
+    <t>Utia</t>
+  </si>
+  <si>
+    <t>Shabrina Amalia</t>
   </si>
   <si>
     <t>Aulia Hani</t>
   </si>
   <si>
-    <t>Shabrina Amalia</t>
+    <t>Wahyu Setianingsih</t>
+  </si>
+  <si>
+    <t>Ade Evan</t>
+  </si>
+  <si>
+    <t>Graaduation</t>
   </si>
   <si>
     <t>Nana</t>
   </si>
   <si>
-    <t>Wafi Wafa</t>
+    <t>Karlina</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> widyaloka</t>
   </si>
   <si>
     <t xml:space="preserve"> Tika Dwi</t>
@@ -148,112 +244,13 @@
     <t>Devinta Khoerunnisa</t>
   </si>
   <si>
-    <t xml:space="preserve"> oktriana</t>
-  </si>
-  <si>
-    <t>N. A. Salsabila</t>
-  </si>
-  <si>
-    <t>Rahayu Purnama</t>
-  </si>
-  <si>
-    <t>Graduatiom</t>
-  </si>
-  <si>
-    <t>Gandring Guste Puand</t>
-  </si>
-  <si>
-    <t>Graduatio prem</t>
-  </si>
-  <si>
-    <t>Fafif</t>
-  </si>
-  <si>
-    <t>Zaidan Ariefyandi</t>
-  </si>
-  <si>
-    <t>Sandlyra Anastasya</t>
-  </si>
-  <si>
-    <t>helmi</t>
-  </si>
-  <si>
-    <t>Reynaldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> widyaloka</t>
-  </si>
-  <si>
-    <t>Amelia Nur</t>
-  </si>
-  <si>
-    <t>calresta</t>
-  </si>
-  <si>
-    <t>Niko</t>
-  </si>
-  <si>
-    <t>Karlina</t>
-  </si>
-  <si>
-    <t>Nabilla</t>
-  </si>
-  <si>
-    <t>Tiffani Agil</t>
-  </si>
-  <si>
-    <t>Nina Dwi Suryani</t>
-  </si>
-  <si>
-    <t>Mahendra Putra Wardhana</t>
-  </si>
-  <si>
-    <t>Afita Khoerunnisa</t>
-  </si>
-  <si>
-    <t>Dita</t>
+    <t xml:space="preserve"> Uji</t>
   </si>
   <si>
     <t>Sifa</t>
   </si>
   <si>
-    <t>Hanifa</t>
-  </si>
-  <si>
-    <t>Akhmad binangun</t>
-  </si>
-  <si>
-    <t>lala</t>
-  </si>
-  <si>
-    <t>sabrina</t>
-  </si>
-  <si>
-    <t>Claresta</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>Desti Ika c</t>
-  </si>
-  <si>
-    <t>Utia</t>
-  </si>
-  <si>
-    <t>Wahyu Setianingsih</t>
-  </si>
-  <si>
-    <t>Ade Evan</t>
-  </si>
-  <si>
-    <t>Graaduation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indah </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Uji</t>
+    <t>Syifa Zulfa</t>
   </si>
 </sst>
 </file>
@@ -348,7 +345,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +410,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9900"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -589,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -691,83 +700,127 @@
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="8" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="11" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="8" fillId="9" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -775,43 +828,8 @@
     <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="12" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -912,7 +930,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -940,7 +958,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -968,7 +986,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -996,7 +1014,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1246,7 +1264,7 @@
     <col customWidth="1" min="24" max="24" width="11.63"/>
     <col customWidth="1" min="25" max="25" width="11.13"/>
     <col customWidth="1" min="26" max="26" width="10.63"/>
-    <col customWidth="1" min="27" max="27" width="14.0"/>
+    <col customWidth="1" min="27" max="27" width="20.25"/>
     <col customWidth="1" min="28" max="30" width="11.63"/>
   </cols>
   <sheetData>
@@ -1898,52 +1916,36 @@
       <c r="AD19" s="34"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35">
+      <c r="A20" s="21">
         <v>9.0</v>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="22">
         <v>0.5416666666666666</v>
       </c>
-      <c r="C20" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="38">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="35">
         <v>9.0</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="36">
         <v>0.5416666666666666</v>
       </c>
       <c r="I20" s="34"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="35">
+      <c r="L20" s="35"/>
+      <c r="M20" s="21">
         <v>9.0</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="22">
         <v>0.5416666666666666</v>
       </c>
-      <c r="O20" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="P20" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="R20" s="41" t="s">
-        <v>16</v>
-      </c>
+      <c r="O20" s="37"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
       <c r="S20" s="23">
         <v>9.0</v>
       </c>
@@ -1951,7 +1953,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="U20" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V20" s="25" t="s">
         <v>14</v>
@@ -1969,10 +1971,10 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="AA20" s="25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB20" s="25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC20" s="25" t="s">
         <v>15</v>
@@ -1982,80 +1984,72 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="42">
+      <c r="A21" s="39">
         <v>10.0</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="40">
         <v>0.5555555555555556</v>
       </c>
-      <c r="C21" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="38">
+      <c r="E21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="35">
         <v>10.0</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="36">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="35">
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="21">
         <v>10.0</v>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="42">
         <v>0.5555555555555556</v>
       </c>
-      <c r="O21" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="R21" s="37" t="s">
-        <v>16</v>
-      </c>
+      <c r="O21" s="43"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
       <c r="S21" s="23">
         <v>10.0</v>
       </c>
       <c r="T21" s="24">
         <v>0.5555555555555556</v>
       </c>
-      <c r="U21" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="V21" s="48" t="s">
+      <c r="U21" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="V21" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="W21" s="48" t="s">
+      <c r="W21" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="38">
+      <c r="X21" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="35">
         <v>10.0</v>
       </c>
-      <c r="Z21" s="39">
+      <c r="Z21" s="36">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="38"/>
-      <c r="AD21" s="38"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="21">
@@ -2075,7 +2069,7 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J22" s="25" t="s">
         <v>14</v>
@@ -2089,13 +2083,13 @@
       <c r="M22" s="23">
         <v>11.0</v>
       </c>
-      <c r="N22" s="50">
+      <c r="N22" s="47">
         <v>0.5694444444444444</v>
       </c>
-      <c r="O22" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="P22" s="52" t="s">
+      <c r="O22" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="49" t="s">
         <v>14</v>
       </c>
       <c r="Q22" s="25" t="s">
@@ -2104,16 +2098,16 @@
       <c r="R22" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S22" s="38">
+      <c r="S22" s="21">
         <v>11.0</v>
       </c>
-      <c r="T22" s="39">
+      <c r="T22" s="22">
         <v>0.5694444444444444</v>
       </c>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="26"/>
       <c r="Y22" s="23">
         <v>11.0</v>
       </c>
@@ -2121,10 +2115,10 @@
         <v>0.5694444444444444</v>
       </c>
       <c r="AA22" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB22" s="25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AC22" s="25" t="s">
         <v>20</v>
@@ -2141,10 +2135,10 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>15</v>
@@ -2159,9 +2153,9 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="50" t="s">
         <v>14</v>
       </c>
       <c r="K23" s="25" t="s">
@@ -2170,100 +2164,76 @@
       <c r="L23" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="35">
+      <c r="M23" s="51">
         <v>12.0</v>
       </c>
-      <c r="N23" s="45">
+      <c r="N23" s="52">
         <v>0.5833333333333334</v>
       </c>
-      <c r="O23" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="P23" s="52" t="s">
+      <c r="O23" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="P23" s="49" t="s">
         <v>14</v>
       </c>
       <c r="Q23" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R23" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S23" s="35">
+      <c r="S23" s="21">
         <v>12.0</v>
       </c>
-      <c r="T23" s="36">
+      <c r="T23" s="22">
         <v>0.5833333333333334</v>
       </c>
-      <c r="U23" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="X23" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y23" s="38">
+      <c r="U23" s="26"/>
+      <c r="V23" s="26"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="26"/>
+      <c r="Y23" s="35">
         <v>12.0</v>
       </c>
-      <c r="Z23" s="39">
+      <c r="Z23" s="36">
         <v>0.5833333333333334</v>
       </c>
-      <c r="AA23" s="38"/>
-      <c r="AB23" s="38"/>
-      <c r="AC23" s="38"/>
-      <c r="AD23" s="38"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="38">
+      <c r="A24" s="21">
         <v>13.0</v>
       </c>
-      <c r="B24" s="39">
+      <c r="B24" s="22">
         <v>0.5972222222222222</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="21">
         <v>13.0</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="22">
         <v>0.5972222222222222</v>
       </c>
-      <c r="I24" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="35">
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="21">
         <v>13.0</v>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="22">
         <v>0.5972222222222222</v>
       </c>
-      <c r="O24" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="P24" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="25" t="s">
-        <v>16</v>
-      </c>
+      <c r="O24" s="54"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
       <c r="S24" s="23">
         <v>13.0</v>
       </c>
@@ -2271,7 +2241,7 @@
         <v>0.5972222222222222</v>
       </c>
       <c r="U24" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>14</v>
@@ -2282,54 +2252,38 @@
       <c r="X24" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="Y24" s="38">
+      <c r="Y24" s="35">
         <v>13.0</v>
       </c>
-      <c r="Z24" s="39">
+      <c r="Z24" s="36">
         <v>0.5972222222222222</v>
       </c>
-      <c r="AA24" s="38"/>
-      <c r="AB24" s="38"/>
-      <c r="AC24" s="38"/>
-      <c r="AD24" s="38"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="35"/>
+      <c r="AD24" s="35"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="21">
         <v>14.0</v>
       </c>
-      <c r="B25" s="36">
+      <c r="B25" s="22">
         <v>0.6111111111111112</v>
       </c>
-      <c r="C25" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="35">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="21">
         <v>14.0</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="22">
         <v>0.6111111111111112</v>
       </c>
-      <c r="I25" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="37" t="s">
-        <v>16</v>
-      </c>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
       <c r="M25" s="23">
         <v>14.0</v>
       </c>
@@ -2337,27 +2291,27 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P25" s="25" t="s">
         <v>14</v>
       </c>
       <c r="Q25" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R25" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S25" s="38">
+      <c r="S25" s="21">
         <v>14.0</v>
       </c>
-      <c r="T25" s="39">
+      <c r="T25" s="22">
         <v>0.6111111111111112</v>
       </c>
-      <c r="U25" s="38"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="38"/>
-      <c r="X25" s="38"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
       <c r="Y25" s="23">
         <v>14.0</v>
       </c>
@@ -2365,7 +2319,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="AA25" s="25" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB25" s="25" t="s">
         <v>14</v>
@@ -2385,10 +2339,10 @@
         <v>0.625</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>20</v>
@@ -2403,10 +2357,10 @@
         <v>0.625</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K26" s="25" t="s">
         <v>20</v>
@@ -2421,27 +2375,27 @@
         <v>0.625</v>
       </c>
       <c r="O26" s="25" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="P26" s="23" t="s">
         <v>14</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R26" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="38">
+        <v>25</v>
+      </c>
+      <c r="R26" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="S26" s="21">
         <v>15.0</v>
       </c>
-      <c r="T26" s="39">
+      <c r="T26" s="22">
         <v>0.625</v>
       </c>
-      <c r="U26" s="38"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="38"/>
-      <c r="X26" s="38"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
       <c r="Y26" s="23">
         <v>15.0</v>
       </c>
@@ -2449,7 +2403,7 @@
         <v>0.625</v>
       </c>
       <c r="AA26" s="25" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB26" s="25" t="s">
         <v>19</v>
@@ -2468,16 +2422,16 @@
       <c r="B27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="56" t="s">
+      <c r="C27" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="56" t="s">
+      <c r="E27" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="23">
@@ -2487,15 +2441,15 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K27" s="56" t="s">
+      <c r="K27" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="56" t="s">
+      <c r="L27" s="25" t="s">
         <v>16</v>
       </c>
       <c r="M27" s="23">
@@ -2505,7 +2459,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P27" s="25" t="s">
         <v>14</v>
@@ -2516,34 +2470,26 @@
       <c r="R27" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S27" s="44">
+      <c r="S27" s="56">
         <v>16.0</v>
       </c>
       <c r="T27" s="57">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="44"/>
-      <c r="V27" s="44"/>
-      <c r="W27" s="44"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="56"/>
       <c r="X27" s="58"/>
-      <c r="Y27" s="35">
+      <c r="Y27" s="21">
         <v>16.0</v>
       </c>
-      <c r="Z27" s="36">
+      <c r="Z27" s="22">
         <v>0.6388888888888888</v>
       </c>
-      <c r="AA27" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB27" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC27" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD27" s="37" t="s">
-        <v>16</v>
-      </c>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="23">
@@ -2553,35 +2499,27 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="C28" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="35">
+      <c r="F28" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="21">
         <v>17.0</v>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="22">
         <v>0.6527777777777778</v>
       </c>
-      <c r="I28" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" s="37" t="s">
-        <v>16</v>
-      </c>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
       <c r="M28" s="23">
         <v>17.0</v>
       </c>
@@ -2589,139 +2527,131 @@
         <v>0.6527777777777778</v>
       </c>
       <c r="O28" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="P28" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="P28" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="Q28" s="56" t="s">
+      <c r="Q28" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="R28" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="S28" s="38">
+      <c r="R28" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="S28" s="21">
         <v>17.0</v>
       </c>
-      <c r="T28" s="39">
+      <c r="T28" s="22">
         <v>0.6527777777777778</v>
       </c>
-      <c r="U28" s="38"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="38"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="38">
+      <c r="U28" s="21"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="35">
         <v>17.0</v>
       </c>
-      <c r="Z28" s="39">
+      <c r="Z28" s="36">
         <v>0.6527777777777778</v>
       </c>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
       <c r="AD28" s="60"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="61">
+      <c r="A29" s="21">
         <v>18.0</v>
       </c>
-      <c r="B29" s="62">
+      <c r="B29" s="22">
         <v>0.6666666666666666</v>
       </c>
-      <c r="C29" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="56" t="s">
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="35">
+        <v>18.0</v>
+      </c>
+      <c r="H29" s="36">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="K29" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="61">
+      <c r="L29" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="23">
         <v>18.0</v>
       </c>
-      <c r="H29" s="62">
+      <c r="N29" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I29" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="J29" s="56" t="s">
+      <c r="O29" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="P29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K29" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="61">
+      <c r="Q29" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="S29" s="21">
         <v>18.0</v>
       </c>
-      <c r="N29" s="62">
+      <c r="T29" s="22">
         <v>0.6666666666666666</v>
       </c>
-      <c r="O29" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="P29" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="R29" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="38">
-        <v>18.0</v>
-      </c>
-      <c r="T29" s="39">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U29" s="38"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
+      <c r="U29" s="21"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="21"/>
+      <c r="X29" s="21"/>
       <c r="Y29" s="23">
         <v>18.0</v>
       </c>
       <c r="Z29" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB29" s="56" t="s">
+      <c r="AA29" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AC29" s="56" t="s">
+      <c r="AC29" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AD29" s="56" t="s">
+      <c r="AD29" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="61">
+      <c r="A30" s="23">
         <v>19.0</v>
       </c>
-      <c r="B30" s="62">
+      <c r="B30" s="24">
         <v>0.6805555555555556</v>
       </c>
-      <c r="C30" s="56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="56" t="s">
+      <c r="C30" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="23">
@@ -2730,26 +2660,26 @@
       <c r="H30" s="24">
         <v>0.6805555555555556</v>
       </c>
-      <c r="I30" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="J30" s="56" t="s">
+      <c r="I30" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K30" s="56" t="s">
+      <c r="K30" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="L30" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="61">
+      <c r="L30" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="51">
         <v>19.0</v>
       </c>
       <c r="N30" s="62">
         <v>0.6805555555555556</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="P30" s="64" t="s">
         <v>14</v>
@@ -2760,60 +2690,52 @@
       <c r="R30" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="S30" s="65">
+      <c r="S30" s="39">
         <v>19.0</v>
       </c>
-      <c r="T30" s="66">
+      <c r="T30" s="40">
         <v>0.6805555555555556</v>
       </c>
-      <c r="U30" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="V30" s="65" t="s">
+      <c r="U30" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="V30" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W30" s="65" t="s">
+      <c r="W30" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="X30" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y30" s="61">
+      <c r="X30" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y30" s="35">
         <v>19.0</v>
       </c>
-      <c r="Z30" s="62">
+      <c r="Z30" s="36">
         <v>0.6805555555555556</v>
       </c>
-      <c r="AA30" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB30" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC30" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD30" s="56" t="s">
-        <v>16</v>
-      </c>
+      <c r="AA30" s="34"/>
+      <c r="AB30" s="34"/>
+      <c r="AC30" s="34"/>
+      <c r="AD30" s="34"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="61">
+      <c r="A31" s="23">
         <v>20.0</v>
       </c>
-      <c r="B31" s="62">
+      <c r="B31" s="24">
         <v>0.6944444444444444</v>
       </c>
-      <c r="C31" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="56" t="s">
+      <c r="C31" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="56" t="s">
+      <c r="E31" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="25" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="23">
@@ -2822,426 +2744,458 @@
       <c r="H31" s="24">
         <v>0.6944444444444444</v>
       </c>
-      <c r="I31" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="J31" s="56" t="s">
+      <c r="I31" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K31" s="56" t="s">
+      <c r="K31" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="61">
+      <c r="L31" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="23">
         <v>20.0</v>
       </c>
-      <c r="N31" s="62">
+      <c r="N31" s="24">
         <v>0.6944444444444444</v>
       </c>
-      <c r="O31" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="P31" s="68" t="s">
+      <c r="O31" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="P31" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="Q31" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="R31" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="S31" s="38">
+      <c r="Q31" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="35">
         <v>20.0</v>
       </c>
-      <c r="T31" s="39">
+      <c r="T31" s="36">
         <v>0.6944444444444444</v>
       </c>
-      <c r="U31" s="38"/>
-      <c r="V31" s="38"/>
-      <c r="W31" s="38"/>
-      <c r="X31" s="38"/>
-      <c r="Y31" s="61">
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="23">
         <v>20.0</v>
       </c>
-      <c r="Z31" s="62">
+      <c r="Z31" s="24">
         <v>0.6944444444444444</v>
       </c>
-      <c r="AA31" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB31" s="56" t="s">
+      <c r="AA31" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AC31" s="56" t="s">
+      <c r="AC31" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AD31" s="56" t="s">
+      <c r="AD31" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="61">
+      <c r="A32" s="35">
         <v>21.0</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="36">
         <v>0.7083333333333334</v>
       </c>
-      <c r="C32" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="56" t="s">
+      <c r="C32" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="61">
+      <c r="F32" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="35">
         <v>21.0</v>
       </c>
-      <c r="H32" s="62">
+      <c r="H32" s="36">
         <v>0.7083333333333334</v>
       </c>
-      <c r="I32" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="K32" s="65" t="s">
+      <c r="I32" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="J32" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="38">
+      <c r="L32" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="35">
         <v>21.0</v>
       </c>
-      <c r="N32" s="39">
+      <c r="N32" s="36">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="70"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="61">
+      <c r="O32" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="23">
         <v>21.0</v>
       </c>
-      <c r="T32" s="62">
+      <c r="T32" s="24">
         <v>0.7083333333333334</v>
       </c>
-      <c r="U32" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="V32" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="W32" s="72" t="s">
+      <c r="U32" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="V32" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="W32" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="X32" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y32" s="61">
+      <c r="X32" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y32" s="35">
         <v>21.0</v>
       </c>
-      <c r="Z32" s="62">
+      <c r="Z32" s="36">
         <v>0.7083333333333334</v>
       </c>
-      <c r="AA32" s="56" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB32" s="56" t="s">
+      <c r="AA32" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB32" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="AC32" s="56" t="s">
+      <c r="AC32" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="AD32" s="56" t="s">
+      <c r="AD32" s="34" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="61">
+      <c r="A33" s="23">
         <v>22.0</v>
       </c>
-      <c r="B33" s="62">
+      <c r="B33" s="24">
         <v>0.7222222222222222</v>
       </c>
-      <c r="C33" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="56" t="s">
+      <c r="C33" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="56" t="s">
+      <c r="E33" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="61">
+      <c r="F33" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="35">
         <v>22.0</v>
       </c>
-      <c r="H33" s="62">
+      <c r="H33" s="36">
         <v>0.7222222222222222</v>
       </c>
-      <c r="I33" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="J33" s="56" t="s">
+      <c r="I33" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="K33" s="56" t="s">
+      <c r="K33" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="35">
+      <c r="L33" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="51">
         <v>22.0</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="62">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="71"/>
-      <c r="S33" s="61">
+      <c r="O33" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P33" s="66"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="23">
         <v>22.0</v>
       </c>
-      <c r="T33" s="62">
+      <c r="T33" s="24">
         <v>0.7222222222222222</v>
       </c>
-      <c r="U33" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="V33" s="56" t="s">
+      <c r="U33" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="V33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="W33" s="56" t="s">
+      <c r="W33" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="X33" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y33" s="61">
+      <c r="X33" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y33" s="23">
         <v>22.0</v>
       </c>
-      <c r="Z33" s="62">
+      <c r="Z33" s="24">
         <v>0.7222222222222222</v>
       </c>
-      <c r="AA33" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB33" s="65" t="s">
+      <c r="AA33" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB33" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AC33" s="65" t="s">
+      <c r="AC33" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AD33" s="74" t="s">
+      <c r="AD33" s="70" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="61">
+      <c r="A34" s="51">
         <v>23.0</v>
       </c>
       <c r="B34" s="62">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="56" t="s">
+      <c r="C34" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="61">
+      <c r="F34" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="23">
         <v>7.0</v>
       </c>
-      <c r="H34" s="62">
+      <c r="H34" s="24">
         <v>0.7361111111111112</v>
       </c>
-      <c r="I34" s="75" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" s="56" t="s">
+      <c r="I34" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="L34" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="35">
+      <c r="L34" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" s="51">
         <v>23.0</v>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="62">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="73" t="s">
+      <c r="O34" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P34" s="66"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="51">
+        <v>23.0</v>
+      </c>
+      <c r="T34" s="62">
+        <v>0.7361111111111112</v>
+      </c>
+      <c r="U34" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="21">
+      <c r="V34" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="W34" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="X34" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y34" s="23">
         <v>23.0</v>
       </c>
-      <c r="T34" s="22">
+      <c r="Z34" s="24">
         <v>0.7361111111111112</v>
       </c>
-      <c r="U34" s="21"/>
-      <c r="V34" s="21"/>
-      <c r="W34" s="21"/>
-      <c r="X34" s="21"/>
-      <c r="Y34" s="61">
-        <v>23.0</v>
-      </c>
-      <c r="Z34" s="62">
-        <v>0.7361111111111112</v>
-      </c>
-      <c r="AA34" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB34" s="56" t="s">
+      <c r="AA34" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB34" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="AC34" s="56" t="s">
+      <c r="AC34" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="AD34" s="56" t="s">
+      <c r="AD34" s="73" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="61">
+      <c r="A35" s="23">
         <v>24.0</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="24">
         <v>0.75</v>
       </c>
-      <c r="C35" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="56" t="s">
+      <c r="C35" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35" s="61">
+      <c r="F35" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="74">
         <v>24.0</v>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="75">
         <v>0.75</v>
       </c>
-      <c r="I35" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" s="56" t="s">
+      <c r="I35" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="K35" s="56" t="s">
+      <c r="K35" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="35">
+      <c r="L35" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="51">
         <v>24.0</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="62">
         <v>0.75</v>
       </c>
-      <c r="O35" s="76" t="s">
-        <v>77</v>
-      </c>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="21">
+      <c r="O35" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P35" s="66"/>
+      <c r="Q35" s="66"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="23">
         <v>24.0</v>
       </c>
-      <c r="T35" s="22">
+      <c r="T35" s="24">
         <v>0.75</v>
       </c>
-      <c r="U35" s="21"/>
-      <c r="V35" s="21"/>
-      <c r="W35" s="21"/>
-      <c r="X35" s="21"/>
-      <c r="Y35" s="21">
+      <c r="U35" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="V35" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="W35" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="X35" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y35" s="23">
         <v>24.0</v>
       </c>
-      <c r="Z35" s="22">
+      <c r="Z35" s="24">
         <v>0.75</v>
       </c>
-      <c r="AA35" s="21"/>
-      <c r="AB35" s="21"/>
-      <c r="AC35" s="21"/>
-      <c r="AD35" s="21"/>
+      <c r="AA35" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB35" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC35" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD35" s="73" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="61">
+      <c r="A36" s="74">
         <v>25.0</v>
       </c>
-      <c r="B36" s="62">
+      <c r="B36" s="75">
         <v>0.7638888888888888</v>
       </c>
-      <c r="C36" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="56" t="s">
+      <c r="C36" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="21">
+      <c r="F36" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="74">
         <v>25.0</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="75">
         <v>0.7638888888888888</v>
       </c>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="35">
+      <c r="I36" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="M36" s="51">
         <v>25.0</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="62">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="71"/>
+      <c r="O36" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P36" s="66"/>
+      <c r="Q36" s="66"/>
+      <c r="R36" s="67"/>
       <c r="S36" s="21">
         <v>25.0</v>
       </c>
@@ -3274,36 +3228,28 @@
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="61">
+      <c r="G37" s="21">
         <v>26.0</v>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="22">
         <v>0.7777777777777778</v>
       </c>
-      <c r="I37" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="J37" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="35">
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="51">
         <v>26.0</v>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="62">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P37" s="70"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="71"/>
+      <c r="O37" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
       <c r="S37" s="21">
         <v>26.0</v>
       </c>
@@ -3326,111 +3272,111 @@
       <c r="AD37" s="21"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="21">
+      <c r="A38" s="77">
         <v>27.0</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="78">
         <v>0.7916666666666666</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21">
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77">
         <v>27.0</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="78">
         <v>0.7916666666666666</v>
       </c>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="35">
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="77"/>
+      <c r="M38" s="77">
         <v>27.0</v>
       </c>
-      <c r="N38" s="36">
+      <c r="N38" s="78">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="21">
+      <c r="O38" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="77">
         <v>27.0</v>
       </c>
-      <c r="T38" s="22">
+      <c r="T38" s="78">
         <v>0.7916666666666666</v>
       </c>
-      <c r="U38" s="21"/>
-      <c r="V38" s="21"/>
-      <c r="W38" s="21"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21">
+      <c r="U38" s="77"/>
+      <c r="V38" s="77"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="77"/>
+      <c r="Y38" s="77">
         <v>27.0</v>
       </c>
-      <c r="Z38" s="22">
+      <c r="Z38" s="78">
         <v>0.7916666666666666</v>
       </c>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="21"/>
-      <c r="AD38" s="21"/>
+      <c r="AA38" s="77"/>
+      <c r="AB38" s="77"/>
+      <c r="AC38" s="77"/>
+      <c r="AD38" s="77"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21">
+      <c r="A39" s="77">
         <v>28.0</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="78">
         <v>0.8055555555555556</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21">
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77">
         <v>28.0</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="78">
         <v>0.8055555555555556</v>
       </c>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="35">
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77">
         <v>28.0</v>
       </c>
-      <c r="N39" s="36">
+      <c r="N39" s="78">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P39" s="70"/>
-      <c r="Q39" s="70"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="21">
+      <c r="O39" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="P39" s="66"/>
+      <c r="Q39" s="66"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="77">
         <v>28.0</v>
       </c>
-      <c r="T39" s="22">
+      <c r="T39" s="78">
         <v>0.8055555555555556</v>
       </c>
-      <c r="U39" s="21"/>
-      <c r="V39" s="21"/>
-      <c r="W39" s="21"/>
-      <c r="X39" s="21"/>
-      <c r="Y39" s="21">
+      <c r="U39" s="77"/>
+      <c r="V39" s="77"/>
+      <c r="W39" s="77"/>
+      <c r="X39" s="77"/>
+      <c r="Y39" s="77">
         <v>28.0</v>
       </c>
-      <c r="Z39" s="22">
+      <c r="Z39" s="78">
         <v>0.8055555555555556</v>
       </c>
-      <c r="AA39" s="21"/>
-      <c r="AB39" s="21"/>
-      <c r="AC39" s="21"/>
+      <c r="AA39" s="77"/>
+      <c r="AB39" s="77"/>
+      <c r="AC39" s="77"/>
       <c r="AD39" s="77"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -3454,18 +3400,18 @@
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
-      <c r="M40" s="35">
+      <c r="M40" s="51">
         <v>29.0</v>
       </c>
-      <c r="N40" s="36">
+      <c r="N40" s="62">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="70"/>
-      <c r="R40" s="71"/>
+      <c r="O40" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P40" s="66"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
       <c r="S40" s="21">
         <v>29.0</v>
       </c>
@@ -3485,7 +3431,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="77"/>
+      <c r="AD40" s="80"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="21">
@@ -3508,18 +3454,18 @@
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
-      <c r="M41" s="35">
+      <c r="M41" s="51">
         <v>30.0</v>
       </c>
-      <c r="N41" s="36">
+      <c r="N41" s="62">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="71"/>
+      <c r="O41" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P41" s="66"/>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="67"/>
       <c r="S41" s="21">
         <v>30.0</v>
       </c>
@@ -3539,7 +3485,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="77"/>
+      <c r="AD41" s="80"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3562,18 +3508,18 @@
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
-      <c r="M42" s="35">
+      <c r="M42" s="51">
         <v>31.0</v>
       </c>
-      <c r="N42" s="36">
+      <c r="N42" s="62">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="71"/>
+      <c r="O42" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="67"/>
       <c r="S42" s="21">
         <v>31.0</v>
       </c>
@@ -3593,61 +3539,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="77"/>
+      <c r="AD42" s="80"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="78">
+      <c r="A43" s="81">
         <v>32.0</v>
       </c>
-      <c r="B43" s="79">
+      <c r="B43" s="82">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78">
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81">
         <v>32.0</v>
       </c>
-      <c r="H43" s="79">
+      <c r="H43" s="82">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
-      <c r="M43" s="80">
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="83">
         <v>32.0</v>
       </c>
-      <c r="N43" s="81">
+      <c r="N43" s="84">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="82" t="s">
-        <v>71</v>
-      </c>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-      <c r="R43" s="84"/>
-      <c r="S43" s="78">
+      <c r="O43" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
+      <c r="R43" s="87"/>
+      <c r="S43" s="81">
         <v>32.0</v>
       </c>
-      <c r="T43" s="79">
+      <c r="T43" s="82">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="78"/>
-      <c r="V43" s="78"/>
-      <c r="W43" s="78"/>
-      <c r="X43" s="78"/>
-      <c r="Y43" s="78">
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
+      <c r="Y43" s="81">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="79">
+      <c r="Z43" s="82">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="78"/>
-      <c r="AB43" s="78"/>
-      <c r="AC43" s="78"/>
-      <c r="AD43" s="85"/>
+      <c r="AA43" s="81"/>
+      <c r="AB43" s="81"/>
+      <c r="AC43" s="81"/>
+      <c r="AD43" s="88"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -4624,15 +4570,6 @@
     <mergeCell ref="U10:U11"/>
     <mergeCell ref="G5:L9"/>
     <mergeCell ref="M5:R9"/>
-    <mergeCell ref="S5:X9"/>
-    <mergeCell ref="Y5:AD9"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="A3:F4"/>
-    <mergeCell ref="G3:L4"/>
-    <mergeCell ref="M3:R4"/>
-    <mergeCell ref="S3:X4"/>
-    <mergeCell ref="Y3:AD4"/>
-    <mergeCell ref="A5:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
@@ -4661,6 +4598,15 @@
     <mergeCell ref="O34:R34"/>
     <mergeCell ref="O35:R35"/>
     <mergeCell ref="O36:R36"/>
+    <mergeCell ref="S3:X4"/>
+    <mergeCell ref="S5:X9"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A3:F4"/>
+    <mergeCell ref="G3:L4"/>
+    <mergeCell ref="M3:R4"/>
+    <mergeCell ref="Y3:AD4"/>
+    <mergeCell ref="A5:F9"/>
+    <mergeCell ref="Y5:AD9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="80">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>Syifa Zulfa</t>
+  </si>
+  <si>
+    <t>Arif</t>
+  </si>
+  <si>
+    <t>Couple  B</t>
   </si>
 </sst>
 </file>
@@ -811,9 +817,6 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -821,6 +824,9 @@
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -874,7 +880,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -902,7 +908,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -930,7 +936,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -986,7 +992,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1014,7 +1020,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3024,22 +3030,22 @@
       <c r="P34" s="66"/>
       <c r="Q34" s="66"/>
       <c r="R34" s="67"/>
-      <c r="S34" s="51">
+      <c r="S34" s="23">
         <v>23.0</v>
       </c>
-      <c r="T34" s="62">
+      <c r="T34" s="24">
         <v>0.7361111111111112</v>
       </c>
-      <c r="U34" s="71" t="s">
+      <c r="U34" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="V34" s="71" t="s">
+      <c r="V34" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="W34" s="71" t="s">
+      <c r="W34" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="X34" s="71" t="s">
+      <c r="X34" s="25" t="s">
         <v>16</v>
       </c>
       <c r="Y34" s="23">
@@ -3051,13 +3057,13 @@
       <c r="AA34" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="AB34" s="73" t="s">
+      <c r="AB34" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AC34" s="73" t="s">
+      <c r="AC34" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AD34" s="73" t="s">
+      <c r="AD34" s="25" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3071,31 +3077,31 @@
       <c r="C35" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="73" t="s">
+      <c r="D35" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="73" t="s">
+      <c r="E35" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35" s="74">
+      <c r="F35" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="51">
         <v>24.0</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="62">
         <v>0.75</v>
       </c>
-      <c r="I35" s="73" t="s">
+      <c r="I35" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="73" t="s">
+      <c r="J35" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="K35" s="73" t="s">
+      <c r="K35" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="73" t="s">
+      <c r="L35" s="71" t="s">
         <v>16</v>
       </c>
       <c r="M35" s="51">
@@ -3119,13 +3125,13 @@
       <c r="U35" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="V35" s="76" t="s">
+      <c r="V35" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W35" s="76" t="s">
+      <c r="W35" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="X35" s="76" t="s">
+      <c r="X35" s="39" t="s">
         <v>16</v>
       </c>
       <c r="Y35" s="23">
@@ -3134,54 +3140,54 @@
       <c r="Z35" s="24">
         <v>0.75</v>
       </c>
-      <c r="AA35" s="73" t="s">
+      <c r="AA35" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="AB35" s="73" t="s">
+      <c r="AB35" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AC35" s="73" t="s">
+      <c r="AC35" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AD35" s="73" t="s">
+      <c r="AD35" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="74">
+      <c r="A36" s="73">
         <v>25.0</v>
       </c>
-      <c r="B36" s="75">
+      <c r="B36" s="74">
         <v>0.7638888888888888</v>
       </c>
-      <c r="C36" s="73" t="s">
+      <c r="C36" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="73" t="s">
+      <c r="D36" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="E36" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="74">
+      <c r="F36" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="73">
         <v>25.0</v>
       </c>
-      <c r="H36" s="75">
+      <c r="H36" s="74">
         <v>0.7638888888888888</v>
       </c>
-      <c r="I36" s="73" t="s">
+      <c r="I36" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="73" t="s">
+      <c r="J36" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="K36" s="73" t="s">
+      <c r="K36" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="L36" s="73" t="s">
+      <c r="L36" s="76" t="s">
         <v>16</v>
       </c>
       <c r="M36" s="51">
@@ -3224,10 +3230,6 @@
       <c r="B37" s="22">
         <v>0.7777777777777778</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
       <c r="G37" s="21">
         <v>26.0</v>
       </c>
@@ -3434,16 +3436,22 @@
       <c r="AD40" s="80"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="21">
+      <c r="A41" s="73">
         <v>30.0</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="74">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
+      <c r="C41" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="73"/>
       <c r="G41" s="21">
         <v>30.0</v>
       </c>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -604,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -821,9 +821,6 @@
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -880,7 +877,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -908,7 +905,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -936,7 +933,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -964,7 +961,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -992,7 +989,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3154,40 +3151,32 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="73">
+      <c r="A36" s="21">
         <v>25.0</v>
       </c>
-      <c r="B36" s="74">
+      <c r="B36" s="22">
         <v>0.7638888888888888</v>
       </c>
-      <c r="C36" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="75" t="s">
-        <v>16</v>
-      </c>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
       <c r="G36" s="73">
         <v>25.0</v>
       </c>
       <c r="H36" s="74">
         <v>0.7638888888888888</v>
       </c>
-      <c r="I36" s="76" t="s">
+      <c r="I36" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="76" t="s">
+      <c r="J36" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="K36" s="76" t="s">
+      <c r="K36" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="L36" s="76" t="s">
+      <c r="L36" s="75" t="s">
         <v>16</v>
       </c>
       <c r="M36" s="51">
@@ -3274,112 +3263,112 @@
       <c r="AD37" s="21"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="77">
+      <c r="A38" s="76">
         <v>27.0</v>
       </c>
-      <c r="B38" s="78">
+      <c r="B38" s="77">
         <v>0.7916666666666666</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77">
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76">
         <v>27.0</v>
       </c>
-      <c r="H38" s="78">
+      <c r="H38" s="77">
         <v>0.7916666666666666</v>
       </c>
-      <c r="I38" s="77"/>
-      <c r="J38" s="77"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="77"/>
-      <c r="M38" s="77">
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76">
         <v>27.0</v>
       </c>
-      <c r="N38" s="78">
+      <c r="N38" s="77">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="79" t="s">
+      <c r="O38" s="78" t="s">
         <v>61</v>
       </c>
       <c r="P38" s="66"/>
       <c r="Q38" s="66"/>
       <c r="R38" s="67"/>
-      <c r="S38" s="77">
+      <c r="S38" s="76">
         <v>27.0</v>
       </c>
-      <c r="T38" s="78">
+      <c r="T38" s="77">
         <v>0.7916666666666666</v>
       </c>
-      <c r="U38" s="77"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="77"/>
-      <c r="X38" s="77"/>
-      <c r="Y38" s="77">
+      <c r="U38" s="76"/>
+      <c r="V38" s="76"/>
+      <c r="W38" s="76"/>
+      <c r="X38" s="76"/>
+      <c r="Y38" s="76">
         <v>27.0</v>
       </c>
-      <c r="Z38" s="78">
+      <c r="Z38" s="77">
         <v>0.7916666666666666</v>
       </c>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-      <c r="AC38" s="77"/>
-      <c r="AD38" s="77"/>
+      <c r="AA38" s="76"/>
+      <c r="AB38" s="76"/>
+      <c r="AC38" s="76"/>
+      <c r="AD38" s="76"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="77">
+      <c r="A39" s="76">
         <v>28.0</v>
       </c>
-      <c r="B39" s="78">
+      <c r="B39" s="77">
         <v>0.8055555555555556</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77">
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76">
         <v>28.0</v>
       </c>
-      <c r="H39" s="78">
+      <c r="H39" s="77">
         <v>0.8055555555555556</v>
       </c>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77">
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="76">
         <v>28.0</v>
       </c>
-      <c r="N39" s="78">
+      <c r="N39" s="77">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="79" t="s">
+      <c r="O39" s="78" t="s">
         <v>61</v>
       </c>
       <c r="P39" s="66"/>
       <c r="Q39" s="66"/>
       <c r="R39" s="67"/>
-      <c r="S39" s="77">
+      <c r="S39" s="76">
         <v>28.0</v>
       </c>
-      <c r="T39" s="78">
+      <c r="T39" s="77">
         <v>0.8055555555555556</v>
       </c>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
-      <c r="X39" s="77"/>
-      <c r="Y39" s="77">
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
+      <c r="W39" s="76"/>
+      <c r="X39" s="76"/>
+      <c r="Y39" s="76">
         <v>28.0</v>
       </c>
-      <c r="Z39" s="78">
+      <c r="Z39" s="77">
         <v>0.8055555555555556</v>
       </c>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-      <c r="AC39" s="77"/>
-      <c r="AD39" s="77"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="76"/>
+      <c r="AC39" s="76"/>
+      <c r="AD39" s="76"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3433,25 +3422,25 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="80"/>
+      <c r="AD40" s="79"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="73">
+      <c r="A41" s="23">
         <v>30.0</v>
       </c>
-      <c r="B41" s="74">
+      <c r="B41" s="24">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="76" t="s">
+      <c r="D41" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E41" s="76" t="s">
+      <c r="E41" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="73"/>
+      <c r="F41" s="23"/>
       <c r="G41" s="21">
         <v>30.0</v>
       </c>
@@ -3493,7 +3482,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="80"/>
+      <c r="AD41" s="79"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3547,61 +3536,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="80"/>
+      <c r="AD42" s="79"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="81">
+      <c r="A43" s="80">
         <v>32.0</v>
       </c>
-      <c r="B43" s="82">
+      <c r="B43" s="81">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81">
+      <c r="C43" s="80"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80">
         <v>32.0</v>
       </c>
-      <c r="H43" s="82">
+      <c r="H43" s="81">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="81"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
-      <c r="M43" s="83">
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="82">
         <v>32.0</v>
       </c>
-      <c r="N43" s="84">
+      <c r="N43" s="83">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="85" t="s">
+      <c r="O43" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="P43" s="86"/>
-      <c r="Q43" s="86"/>
-      <c r="R43" s="87"/>
-      <c r="S43" s="81">
+      <c r="P43" s="85"/>
+      <c r="Q43" s="85"/>
+      <c r="R43" s="86"/>
+      <c r="S43" s="80">
         <v>32.0</v>
       </c>
-      <c r="T43" s="82">
+      <c r="T43" s="81">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="81"/>
-      <c r="V43" s="81"/>
-      <c r="W43" s="81"/>
-      <c r="X43" s="81"/>
-      <c r="Y43" s="81">
+      <c r="U43" s="80"/>
+      <c r="V43" s="80"/>
+      <c r="W43" s="80"/>
+      <c r="X43" s="80"/>
+      <c r="Y43" s="80">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="82">
+      <c r="Z43" s="81">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="81"/>
-      <c r="AB43" s="81"/>
-      <c r="AC43" s="81"/>
-      <c r="AD43" s="88"/>
+      <c r="AA43" s="80"/>
+      <c r="AB43" s="80"/>
+      <c r="AC43" s="80"/>
+      <c r="AD43" s="87"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -4578,6 +4567,15 @@
     <mergeCell ref="U10:U11"/>
     <mergeCell ref="G5:L9"/>
     <mergeCell ref="M5:R9"/>
+    <mergeCell ref="S5:X9"/>
+    <mergeCell ref="Y5:AD9"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A3:F4"/>
+    <mergeCell ref="G3:L4"/>
+    <mergeCell ref="M3:R4"/>
+    <mergeCell ref="S3:X4"/>
+    <mergeCell ref="Y3:AD4"/>
+    <mergeCell ref="A5:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
@@ -4594,8 +4592,6 @@
     <mergeCell ref="N10:N11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
@@ -4606,15 +4602,8 @@
     <mergeCell ref="O34:R34"/>
     <mergeCell ref="O35:R35"/>
     <mergeCell ref="O36:R36"/>
-    <mergeCell ref="S3:X4"/>
-    <mergeCell ref="S5:X9"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="A3:F4"/>
-    <mergeCell ref="G3:L4"/>
-    <mergeCell ref="M3:R4"/>
-    <mergeCell ref="Y3:AD4"/>
-    <mergeCell ref="A5:F9"/>
-    <mergeCell ref="Y5:AD9"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -142,7 +142,7 @@
     <t>Graduatio prem</t>
   </si>
   <si>
-    <t>Fafif</t>
+    <t>Afifah</t>
   </si>
   <si>
     <t>Zaidan Ariefyandi</t>
@@ -351,7 +351,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,18 +422,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF4CCCC"/>
         <bgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAD1DC"/>
-        <bgColor rgb="FFEAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -604,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="83">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -766,9 +754,6 @@
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -783,9 +768,6 @@
     </xf>
     <xf borderId="5" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,15 +796,6 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -877,7 +850,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -905,7 +878,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -961,7 +934,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -989,7 +962,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1017,7 +990,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2425,7 +2398,7 @@
       <c r="B27" s="24">
         <v>0.6388888888888888</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D27" s="25" t="s">
@@ -2473,16 +2446,16 @@
       <c r="R27" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S27" s="56">
+      <c r="S27" s="55">
         <v>16.0</v>
       </c>
-      <c r="T27" s="57">
+      <c r="T27" s="56">
         <v>0.6388888888888888</v>
       </c>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="58"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="57"/>
       <c r="Y27" s="21">
         <v>16.0</v>
       </c>
@@ -2501,7 +2474,7 @@
       <c r="B28" s="24">
         <v>0.6527777777777778</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="58" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="25" t="s">
@@ -2560,7 +2533,7 @@
       <c r="AA28" s="41"/>
       <c r="AB28" s="41"/>
       <c r="AC28" s="41"/>
-      <c r="AD28" s="60"/>
+      <c r="AD28" s="59"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="21">
@@ -2625,7 +2598,7 @@
       <c r="Z29" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA29" s="61" t="s">
+      <c r="AA29" s="25" t="s">
         <v>50</v>
       </c>
       <c r="AB29" s="25" t="s">
@@ -2678,19 +2651,19 @@
       <c r="M30" s="51">
         <v>19.0</v>
       </c>
-      <c r="N30" s="62">
+      <c r="N30" s="60">
         <v>0.6805555555555556</v>
       </c>
-      <c r="O30" s="63" t="s">
+      <c r="O30" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="P30" s="64" t="s">
+      <c r="P30" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="Q30" s="64" t="s">
+      <c r="Q30" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="R30" s="64" t="s">
+      <c r="R30" s="62" t="s">
         <v>16</v>
       </c>
       <c r="S30" s="39">
@@ -2849,28 +2822,28 @@
       <c r="N32" s="36">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O32" s="65" t="s">
+      <c r="O32" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="67"/>
+      <c r="P32" s="64"/>
+      <c r="Q32" s="64"/>
+      <c r="R32" s="65"/>
       <c r="S32" s="23">
         <v>21.0</v>
       </c>
       <c r="T32" s="24">
         <v>0.7083333333333334</v>
       </c>
-      <c r="U32" s="68" t="s">
+      <c r="U32" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="V32" s="68" t="s">
+      <c r="V32" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="W32" s="68" t="s">
+      <c r="W32" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="X32" s="68" t="s">
+      <c r="X32" s="66" t="s">
         <v>16</v>
       </c>
       <c r="Y32" s="35">
@@ -2932,15 +2905,15 @@
       <c r="M33" s="51">
         <v>22.0</v>
       </c>
-      <c r="N33" s="62">
+      <c r="N33" s="60">
         <v>0.7222222222222222</v>
       </c>
-      <c r="O33" s="69" t="s">
+      <c r="O33" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="67"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="65"/>
       <c r="S33" s="23">
         <v>22.0</v>
       </c>
@@ -2974,7 +2947,7 @@
       <c r="AC33" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AD33" s="70" t="s">
+      <c r="AD33" s="68" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2982,19 +2955,19 @@
       <c r="A34" s="51">
         <v>23.0</v>
       </c>
-      <c r="B34" s="62">
+      <c r="B34" s="60">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="71" t="s">
+      <c r="C34" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="71" t="s">
+      <c r="D34" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="71" t="s">
+      <c r="E34" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="71" t="s">
+      <c r="F34" s="69" t="s">
         <v>16</v>
       </c>
       <c r="G34" s="23">
@@ -3003,7 +2976,7 @@
       <c r="H34" s="24">
         <v>0.7361111111111112</v>
       </c>
-      <c r="I34" s="72" t="s">
+      <c r="I34" s="70" t="s">
         <v>70</v>
       </c>
       <c r="J34" s="25" t="s">
@@ -3018,15 +2991,15 @@
       <c r="M34" s="51">
         <v>23.0</v>
       </c>
-      <c r="N34" s="62">
+      <c r="N34" s="60">
         <v>0.7361111111111112</v>
       </c>
-      <c r="O34" s="69" t="s">
+      <c r="O34" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="67"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="65"/>
       <c r="S34" s="23">
         <v>23.0</v>
       </c>
@@ -3086,33 +3059,33 @@
       <c r="G35" s="51">
         <v>24.0</v>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="60">
         <v>0.75</v>
       </c>
-      <c r="I35" s="71" t="s">
+      <c r="I35" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="71" t="s">
+      <c r="J35" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="K35" s="71" t="s">
+      <c r="K35" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="71" t="s">
+      <c r="L35" s="69" t="s">
         <v>16</v>
       </c>
       <c r="M35" s="51">
         <v>24.0</v>
       </c>
-      <c r="N35" s="62">
+      <c r="N35" s="60">
         <v>0.75</v>
       </c>
-      <c r="O35" s="69" t="s">
+      <c r="O35" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="67"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="64"/>
+      <c r="R35" s="65"/>
       <c r="S35" s="23">
         <v>24.0</v>
       </c>
@@ -3161,36 +3134,36 @@
       <c r="D36" s="38"/>
       <c r="E36" s="38"/>
       <c r="F36" s="38"/>
-      <c r="G36" s="73">
+      <c r="G36" s="35">
         <v>25.0</v>
       </c>
-      <c r="H36" s="74">
+      <c r="H36" s="36">
         <v>0.7638888888888888</v>
       </c>
-      <c r="I36" s="75" t="s">
+      <c r="I36" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="75" t="s">
+      <c r="J36" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="K36" s="75" t="s">
+      <c r="K36" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L36" s="75" t="s">
+      <c r="L36" s="34" t="s">
         <v>16</v>
       </c>
       <c r="M36" s="51">
         <v>25.0</v>
       </c>
-      <c r="N36" s="62">
+      <c r="N36" s="60">
         <v>0.7638888888888888</v>
       </c>
-      <c r="O36" s="69" t="s">
+      <c r="O36" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="67"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="64"/>
+      <c r="R36" s="65"/>
       <c r="S36" s="21">
         <v>25.0</v>
       </c>
@@ -3232,15 +3205,15 @@
       <c r="M37" s="51">
         <v>26.0</v>
       </c>
-      <c r="N37" s="62">
+      <c r="N37" s="60">
         <v>0.7777777777777778</v>
       </c>
-      <c r="O37" s="69" t="s">
+      <c r="O37" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P37" s="66"/>
-      <c r="Q37" s="66"/>
-      <c r="R37" s="67"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="65"/>
       <c r="S37" s="21">
         <v>26.0</v>
       </c>
@@ -3263,112 +3236,112 @@
       <c r="AD37" s="21"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="76">
+      <c r="A38" s="71">
         <v>27.0</v>
       </c>
-      <c r="B38" s="77">
+      <c r="B38" s="72">
         <v>0.7916666666666666</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76">
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71">
         <v>27.0</v>
       </c>
-      <c r="H38" s="77">
+      <c r="H38" s="72">
         <v>0.7916666666666666</v>
       </c>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76">
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71">
         <v>27.0</v>
       </c>
-      <c r="N38" s="77">
+      <c r="N38" s="72">
         <v>0.7916666666666666</v>
       </c>
-      <c r="O38" s="78" t="s">
+      <c r="O38" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="66"/>
-      <c r="R38" s="67"/>
-      <c r="S38" s="76">
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="71">
         <v>27.0</v>
       </c>
-      <c r="T38" s="77">
+      <c r="T38" s="72">
         <v>0.7916666666666666</v>
       </c>
-      <c r="U38" s="76"/>
-      <c r="V38" s="76"/>
-      <c r="W38" s="76"/>
-      <c r="X38" s="76"/>
-      <c r="Y38" s="76">
+      <c r="U38" s="71"/>
+      <c r="V38" s="71"/>
+      <c r="W38" s="71"/>
+      <c r="X38" s="71"/>
+      <c r="Y38" s="71">
         <v>27.0</v>
       </c>
-      <c r="Z38" s="77">
+      <c r="Z38" s="72">
         <v>0.7916666666666666</v>
       </c>
-      <c r="AA38" s="76"/>
-      <c r="AB38" s="76"/>
-      <c r="AC38" s="76"/>
-      <c r="AD38" s="76"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="71"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="71"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="76">
+      <c r="A39" s="71">
         <v>28.0</v>
       </c>
-      <c r="B39" s="77">
+      <c r="B39" s="72">
         <v>0.8055555555555556</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76">
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71">
         <v>28.0</v>
       </c>
-      <c r="H39" s="77">
+      <c r="H39" s="72">
         <v>0.8055555555555556</v>
       </c>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="76"/>
-      <c r="M39" s="76">
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71">
         <v>28.0</v>
       </c>
-      <c r="N39" s="77">
+      <c r="N39" s="72">
         <v>0.8055555555555556</v>
       </c>
-      <c r="O39" s="78" t="s">
+      <c r="O39" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="P39" s="66"/>
-      <c r="Q39" s="66"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="76">
+      <c r="P39" s="64"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="71">
         <v>28.0</v>
       </c>
-      <c r="T39" s="77">
+      <c r="T39" s="72">
         <v>0.8055555555555556</v>
       </c>
-      <c r="U39" s="76"/>
-      <c r="V39" s="76"/>
-      <c r="W39" s="76"/>
-      <c r="X39" s="76"/>
-      <c r="Y39" s="76">
+      <c r="U39" s="71"/>
+      <c r="V39" s="71"/>
+      <c r="W39" s="71"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71">
         <v>28.0</v>
       </c>
-      <c r="Z39" s="77">
+      <c r="Z39" s="72">
         <v>0.8055555555555556</v>
       </c>
-      <c r="AA39" s="76"/>
-      <c r="AB39" s="76"/>
-      <c r="AC39" s="76"/>
-      <c r="AD39" s="76"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="71"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21">
@@ -3394,15 +3367,15 @@
       <c r="M40" s="51">
         <v>29.0</v>
       </c>
-      <c r="N40" s="62">
+      <c r="N40" s="60">
         <v>0.8194444444444444</v>
       </c>
-      <c r="O40" s="69" t="s">
+      <c r="O40" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="67"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="64"/>
+      <c r="R40" s="65"/>
       <c r="S40" s="21">
         <v>29.0</v>
       </c>
@@ -3422,7 +3395,7 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
-      <c r="AD40" s="79"/>
+      <c r="AD40" s="74"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="23">
@@ -3454,15 +3427,15 @@
       <c r="M41" s="51">
         <v>30.0</v>
       </c>
-      <c r="N41" s="62">
+      <c r="N41" s="60">
         <v>0.8333333333333334</v>
       </c>
-      <c r="O41" s="69" t="s">
+      <c r="O41" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P41" s="66"/>
-      <c r="Q41" s="66"/>
-      <c r="R41" s="67"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="65"/>
       <c r="S41" s="21">
         <v>30.0</v>
       </c>
@@ -3482,7 +3455,7 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
-      <c r="AD41" s="79"/>
+      <c r="AD41" s="74"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21">
@@ -3508,15 +3481,15 @@
       <c r="M42" s="51">
         <v>31.0</v>
       </c>
-      <c r="N42" s="62">
+      <c r="N42" s="60">
         <v>0.8472222222222222</v>
       </c>
-      <c r="O42" s="69" t="s">
+      <c r="O42" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="P42" s="66"/>
-      <c r="Q42" s="66"/>
-      <c r="R42" s="67"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="65"/>
       <c r="S42" s="21">
         <v>31.0</v>
       </c>
@@ -3536,61 +3509,61 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="79"/>
+      <c r="AD42" s="74"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="80">
+      <c r="A43" s="75">
         <v>32.0</v>
       </c>
-      <c r="B43" s="81">
+      <c r="B43" s="76">
         <v>0.8611111111111112</v>
       </c>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80">
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="75">
         <v>32.0</v>
       </c>
-      <c r="H43" s="81">
+      <c r="H43" s="76">
         <v>0.8611111111111112</v>
       </c>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="80"/>
-      <c r="M43" s="82">
+      <c r="I43" s="75"/>
+      <c r="J43" s="75"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="77">
         <v>32.0</v>
       </c>
-      <c r="N43" s="83">
+      <c r="N43" s="78">
         <v>0.8611111111111112</v>
       </c>
-      <c r="O43" s="84" t="s">
+      <c r="O43" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-      <c r="R43" s="86"/>
-      <c r="S43" s="80">
+      <c r="P43" s="80"/>
+      <c r="Q43" s="80"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="75">
         <v>32.0</v>
       </c>
-      <c r="T43" s="81">
+      <c r="T43" s="76">
         <v>0.8611111111111112</v>
       </c>
-      <c r="U43" s="80"/>
-      <c r="V43" s="80"/>
-      <c r="W43" s="80"/>
-      <c r="X43" s="80"/>
-      <c r="Y43" s="80">
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="75"/>
+      <c r="X43" s="75"/>
+      <c r="Y43" s="75">
         <v>32.0</v>
       </c>
-      <c r="Z43" s="81">
+      <c r="Z43" s="76">
         <v>0.8611111111111112</v>
       </c>
-      <c r="AA43" s="80"/>
-      <c r="AB43" s="80"/>
-      <c r="AC43" s="80"/>
-      <c r="AD43" s="87"/>
+      <c r="AA43" s="75"/>
+      <c r="AB43" s="75"/>
+      <c r="AC43" s="75"/>
+      <c r="AD43" s="82"/>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="78">
   <si>
     <t xml:space="preserve">Graduation Schedule 
 </t>
@@ -221,12 +221,6 @@
   </si>
   <si>
     <t>Wahyu Setianingsih</t>
-  </si>
-  <si>
-    <t>Ade Evan</t>
-  </si>
-  <si>
-    <t>Graaduation</t>
   </si>
   <si>
     <t>Nana</t>
@@ -792,10 +786,10 @@
     <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -850,7 +844,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -878,7 +872,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -906,7 +900,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -934,7 +928,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -962,7 +956,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -990,7 +984,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2952,32 +2946,24 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="51">
+      <c r="A34" s="21">
         <v>23.0</v>
       </c>
-      <c r="B34" s="60">
+      <c r="B34" s="22">
         <v>0.7361111111111112</v>
       </c>
-      <c r="C34" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="69" t="s">
-        <v>16</v>
-      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
       <c r="G34" s="23">
         <v>7.0</v>
       </c>
       <c r="H34" s="24">
         <v>0.7361111111111112</v>
       </c>
-      <c r="I34" s="70" t="s">
-        <v>70</v>
+      <c r="I34" s="69" t="s">
+        <v>68</v>
       </c>
       <c r="J34" s="25" t="s">
         <v>23</v>
@@ -3007,7 +2993,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="U34" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V34" s="25" t="s">
         <v>14</v>
@@ -3025,7 +3011,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="AA34" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB34" s="25" t="s">
         <v>14</v>
@@ -3045,7 +3031,7 @@
         <v>0.75</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D35" s="25" t="s">
         <v>23</v>
@@ -3062,16 +3048,16 @@
       <c r="H35" s="60">
         <v>0.75</v>
       </c>
-      <c r="I35" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="J35" s="69" t="s">
+      <c r="I35" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="J35" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="K35" s="69" t="s">
+      <c r="K35" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="69" t="s">
+      <c r="L35" s="70" t="s">
         <v>16</v>
       </c>
       <c r="M35" s="51">
@@ -3093,7 +3079,7 @@
         <v>0.75</v>
       </c>
       <c r="U35" s="39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="V35" s="39" t="s">
         <v>14</v>
@@ -3111,7 +3097,7 @@
         <v>0.75</v>
       </c>
       <c r="AA35" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AB35" s="25" t="s">
         <v>14</v>
@@ -3141,7 +3127,7 @@
         <v>0.7638888888888888</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J36" s="34" t="s">
         <v>23</v>
@@ -3405,10 +3391,10 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>15</v>

--- a/file_wisuda_3okt.xlsx
+++ b/file_wisuda_3okt.xlsx
@@ -844,7 +844,7 @@
     <xdr:ext cx="2590800" cy="2590800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Gambar"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Gambar"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -872,7 +872,7 @@
     <xdr:ext cx="209550" cy="142875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
